--- a/03_今年度用/測定_20260818/測定_20260818_MCA.xlsx
+++ b/03_今年度用/測定_20260818/測定_20260818_MCA.xlsx
@@ -12,7 +12,7 @@
     <sheet name="チャンネル帯" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'スペクトル'!$A$1:$F$513</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'スペクトル'!$A$1:$G$513</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -102,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -126,22 +126,21 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -244,7 +243,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>計数率スペクトル（ch 1–80、ch0除外）</a:t>
+              <a:t>低ch（ch 1–80）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -315,6 +314,39 @@
           <yVal>
             <numRef>
               <f>'スペクトル'!$E$3:$E$82</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>管理棟2階_0819</v>
+          </tx>
+          <spPr>
+            <a:ln w="15000">
+              <a:solidFill>
+                <a:srgbClr val="2CA02C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'スペクトル'!$A$3:$A$82</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'スペクトル'!$G$3:$G$82</f>
             </numRef>
           </yVal>
         </ser>
@@ -440,7 +472,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>計数率スペクトル（全ch、対数）</a:t>
+              <a:t>全ch（対数）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -511,6 +543,39 @@
           <yVal>
             <numRef>
               <f>'スペクトル'!$E$2:$E$513</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>管理棟2階_0819</v>
+          </tx>
+          <spPr>
+            <a:ln w="12000">
+              <a:solidFill>
+                <a:srgbClr val="2CA02C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'スペクトル'!$A$2:$A$513</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'スペクトル'!$G$2:$G$513</f>
             </numRef>
           </yVal>
         </ser>
@@ -631,7 +696,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3600000"/>
@@ -653,7 +718,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3600000"/>
@@ -969,22 +1034,20 @@
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>今年度 MCA 測定（2026-08-18）</t>
+          <t>今年度 MCA 測定</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Amptek MCA8000D（シリアル 1715）。USB から複製。エネルギー較正なし。昨年9班の熱中性子／MeV領域の計数率とは窓定義が違うので直接比較しない。</t>
+          <t>Amptek MCA8000D。raw/*.mca と USB の未登録ファイルを自動検出。エネルギー較正なし。ROI はスペクトルから自動抽出。</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1069,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>比 (linac / 管理棟2F)</t>
+          <t>管理棟2階_0819</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1089,11 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-18〜08-19</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1044,7 +1111,11 @@
           <t>linac</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>管理棟2階_0819</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1062,7 +1133,11 @@
           <t>08/18/2026 16:19:46</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>08/18/2026 18:00:44</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1076,8 +1151,8 @@
       <c r="C8" s="8" t="n">
         <v>4208.884</v>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>3.151857992490448</v>
+      <c r="D8" s="8" t="n">
+        <v>52246.972</v>
       </c>
     </row>
     <row r="9">
@@ -1086,14 +1161,14 @@
           <t>Real time [s]</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="9" t="n">
         <v>1336.706</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="9" t="n">
         <v>4213.673</v>
       </c>
-      <c r="D9" s="11" t="n">
-        <v>3.152281055071197</v>
+      <c r="D9" s="9" t="n">
+        <v>52300.335</v>
       </c>
     </row>
     <row r="10">
@@ -1102,14 +1177,14 @@
           <t>Dead time [%]</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="10" t="n">
         <v>0.1002464266637526</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.1136538122440856</v>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>1.133744274250334</v>
+      <c r="D10" s="10" t="n">
+        <v>0.1020318512300111</v>
       </c>
     </row>
     <row r="11">
@@ -1118,14 +1193,14 @@
           <t>総カウント</t>
         </is>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="5" t="n">
         <v>87283</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="5" t="n">
         <v>302171</v>
       </c>
-      <c r="D11" s="11" t="n">
-        <v>3.461968539119874</v>
+      <c r="D11" s="5" t="n">
+        <v>3490462</v>
       </c>
     </row>
     <row r="12">
@@ -1134,14 +1209,14 @@
           <t>全体 計数率 [s⁻¹]</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="10" t="n">
         <v>65.36260470912094</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="10" t="n">
         <v>71.79361559976469</v>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>1.098389758475252</v>
+      <c r="D12" s="10" t="n">
+        <v>66.80697208634406</v>
       </c>
     </row>
     <row r="13">
@@ -1150,204 +1225,251 @@
           <t>ch0除く 計数率 [s⁻¹]</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="11" t="n">
         <v>33.14671782867019</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="11" t="n">
         <v>36.85038599305659</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>1.111735592752502</v>
+        <v>33.89231819979921</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>ROI (ch150–450) 計数率 [s⁻¹]</t>
+          <t>自動ROI</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>0.7436163568639609</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>0.1005017006883535</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>0.1351526223981912</v>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>314–366</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>311–362</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>314–366</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ch1–20 計数率 [s⁻¹]</t>
+          <t>ROI ピーク ch</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>25.52259081030968</v>
+        <v>343</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>27.82471553029259</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>1.090199491779376</v>
+        <v>341</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>342</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>最大ピーク ch（1–149）</t>
+          <t>自動ROI 計数率 [s⁻¹]</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>1</v>
+      <c r="B16" s="12" t="n">
+        <v>0.5683834993552329</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>0.07793039675125282</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>0.599881654385636</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>ch1–20 計数率 [s⁻¹]</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>25.52259081030968</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>27.82471553029259</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>25.93612506386016</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>低chピーク</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>装置</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>MCA8000D</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>MCA8000D</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>MCA8000D</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>ゲイン GAIA</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B20" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C20" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="D20" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>ボード温度 [°C]</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B21" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C21" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="D19" s="11" t="n">
-        <v>0.9069767441860465</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="D21" s="5" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>元ファイル</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>20260818_1552_管理棟2F.mca</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>20260818_1730_linac.mca</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>管理棟2階_0819.mca</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>今年度・全スペクトル（未較正）。ch0はADCオーバーフロー。昨年の熱/MeV窓とは別定義。</t>
+          <t>短時間。ch0はADCオーバーフロー。ROIは自動抽出。</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>今年度・全スペクトル（未較正）。ch0はADCオーバーフロー。昨年の熱/MeV窓とは別定義。</t>
+          <t>ch0はADCオーバーフロー。ROIは自動抽出。</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>終夜（18:00開始）。ROIは自動抽出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>注意</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>• これは今年度（2026-08-18）の測定である。前年9班の公開表とは別データ。</t>
+          <t>• raw/*.mca を列挙。USB に未登録の .mca があれば raw/ へコピーする。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>• ch0 が総カウントの約半分。ADC オーバーフローとして解析では除外するのが安全。</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>• 信号は ch 5–7 付近に集中。設定 ROI（ch150–450）のカウントはごく少ない。</t>
+          <t>• ROI は低ch連続成分を除いた高ch側ピークから自動抽出（ファイルの &lt;&lt;ROI&gt;&gt; は使わない）。</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>• フラックス（φ）はエネルギー窓と効率 ε, S が未確定のため空欄。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>• 生データ: 03_今年度用/測定_20260818/raw/　表: tables/*.csv</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-    </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1360,15 +1482,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F513"/>
+  <dimension ref="A1:G513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1379,27 +1502,32 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>counts_管理棟2F</t>
+          <t>counts_20260818_1552_kanri2f</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>cps_管理棟2F</t>
+          <t>cps_20260818_1552_kanri2f</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>counts_linac</t>
+          <t>counts_20260818_1730_linac</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>cps_linac</t>
+          <t>cps_20260818_1730_linac</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>比_linac/管理棟2F</t>
+          <t>counts_kanri2f_0819</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>cps_kanri2f_0819</t>
         </is>
       </c>
     </row>
@@ -1419,8 +1547,11 @@
       <c r="E2" s="15" t="n">
         <v>34.94322960670809</v>
       </c>
-      <c r="F2" s="16" t="n">
-        <v>1.084658315829646</v>
+      <c r="F2" s="14" t="n">
+        <v>1719691</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>32.91465388654485</v>
       </c>
     </row>
     <row r="3">
@@ -1439,8 +1570,11 @@
       <c r="E3" s="15" t="n">
         <v>0.003563890095331684</v>
       </c>
-      <c r="F3" s="16" t="n">
-        <v>1.58636588701423</v>
+      <c r="F3" s="14" t="n">
+        <v>151</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>0.002890119641766034</v>
       </c>
     </row>
     <row r="4">
@@ -1459,8 +1593,11 @@
       <c r="E4" s="15" t="n">
         <v>0.002613519403243235</v>
       </c>
-      <c r="F4" s="16" t="n">
-        <v>1.745002475715653</v>
+      <c r="F4" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>0.001512049349003422</v>
       </c>
     </row>
     <row r="5">
@@ -1479,8 +1616,11 @@
       <c r="E5" s="15" t="n">
         <v>0.001425556038132674</v>
       </c>
-      <c r="F5" s="16" t="n">
-        <v>0.9518195322085379</v>
+      <c r="F5" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0.001378070292762612</v>
       </c>
     </row>
     <row r="6">
@@ -1499,8 +1639,11 @@
       <c r="E6" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F6" s="16" t="n">
-        <v>0.3172731774028459</v>
+      <c r="F6" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>0.000689035146381306</v>
       </c>
     </row>
     <row r="7">
@@ -1519,8 +1662,11 @@
       <c r="E7" s="15" t="n">
         <v>3.488335625310652</v>
       </c>
-      <c r="F7" s="16" t="n">
-        <v>1.014196557942213</v>
+      <c r="F7" s="14" t="n">
+        <v>180156</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>3.448161550874183</v>
       </c>
     </row>
     <row r="8">
@@ -1539,8 +1685,11 @@
       <c r="E8" s="15" t="n">
         <v>4.655390835195268</v>
       </c>
-      <c r="F8" s="16" t="n">
-        <v>0.9677227020596768</v>
+      <c r="F8" s="14" t="n">
+        <v>251265</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>4.809178223763857</v>
       </c>
     </row>
     <row r="9">
@@ -1559,8 +1708,11 @@
       <c r="E9" s="15" t="n">
         <v>3.659164757213551</v>
       </c>
-      <c r="F9" s="16" t="n">
-        <v>1.000885744609019</v>
+      <c r="F9" s="14" t="n">
+        <v>195488</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>3.74161396377191</v>
       </c>
     </row>
     <row r="10">
@@ -1579,8 +1731,11 @@
       <c r="E10" s="15" t="n">
         <v>2.592611248017289</v>
       </c>
-      <c r="F10" s="16" t="n">
-        <v>1.05038983975117</v>
+      <c r="F10" s="14" t="n">
+        <v>132975</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>2.545123571945949</v>
       </c>
     </row>
     <row r="11">
@@ -1599,8 +1754,11 @@
       <c r="E11" s="15" t="n">
         <v>1.964178627873802</v>
       </c>
-      <c r="F11" s="16" t="n">
-        <v>1.092873898995553</v>
+      <c r="F11" s="14" t="n">
+        <v>95796</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>1.833522524520655</v>
       </c>
     </row>
     <row r="12">
@@ -1619,8 +1777,11 @@
       <c r="E12" s="15" t="n">
         <v>1.679067420247268</v>
       </c>
-      <c r="F12" s="16" t="n">
-        <v>1.175141270810227</v>
+      <c r="F12" s="14" t="n">
+        <v>76821</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>1.470343582782175</v>
       </c>
     </row>
     <row r="13">
@@ -1639,8 +1800,11 @@
       <c r="E13" s="15" t="n">
         <v>1.470461053333853</v>
       </c>
-      <c r="F13" s="16" t="n">
-        <v>1.157785197491871</v>
+      <c r="F13" s="14" t="n">
+        <v>65141</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>1.246789957511796</v>
       </c>
     </row>
     <row r="14">
@@ -1659,8 +1823,11 @@
       <c r="E14" s="15" t="n">
         <v>1.271120800668301</v>
       </c>
-      <c r="F14" s="16" t="n">
-        <v>1.182865156170889</v>
+      <c r="F14" s="14" t="n">
+        <v>57061</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>1.092139846879547</v>
       </c>
     </row>
     <row r="15">
@@ -1679,8 +1846,11 @@
       <c r="E15" s="15" t="n">
         <v>1.161352985732085</v>
       </c>
-      <c r="F15" s="16" t="n">
-        <v>1.235722144338734</v>
+      <c r="F15" s="14" t="n">
+        <v>50590</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>0.9682857793175076</v>
       </c>
     </row>
     <row r="16">
@@ -1699,8 +1869,11 @@
       <c r="E16" s="15" t="n">
         <v>1.044457390605205</v>
       </c>
-      <c r="F16" s="16" t="n">
-        <v>1.225600077208182</v>
+      <c r="F16" s="14" t="n">
+        <v>45286</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>0.8667679344173285</v>
       </c>
     </row>
     <row r="17">
@@ -1719,8 +1892,11 @@
       <c r="E17" s="15" t="n">
         <v>0.9558353235679576</v>
       </c>
-      <c r="F17" s="16" t="n">
-        <v>1.318584703193852</v>
+      <c r="F17" s="14" t="n">
+        <v>41462</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>0.7935770899794919</v>
       </c>
     </row>
     <row r="18">
@@ -1739,8 +1915,11 @@
       <c r="E18" s="15" t="n">
         <v>0.8900221531408326</v>
       </c>
-      <c r="F18" s="16" t="n">
-        <v>1.256348121089917</v>
+      <c r="F18" s="14" t="n">
+        <v>37508</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>0.7178980630686119</v>
       </c>
     </row>
     <row r="19">
@@ -1759,8 +1938,11 @@
       <c r="E19" s="15" t="n">
         <v>0.8436915819015207</v>
       </c>
-      <c r="F19" s="16" t="n">
-        <v>1.327016552364554</v>
+      <c r="F19" s="14" t="n">
+        <v>34985</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>0.6696081832263887</v>
       </c>
     </row>
     <row r="20">
@@ -1779,8 +1961,11 @@
       <c r="E20" s="15" t="n">
         <v>0.7690874825725774</v>
       </c>
-      <c r="F20" s="16" t="n">
-        <v>1.301664480675554</v>
+      <c r="F20" s="14" t="n">
+        <v>31807</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>0.6087816916930612</v>
       </c>
     </row>
     <row r="21">
@@ -1799,8 +1984,11 @@
       <c r="E21" s="15" t="n">
         <v>0.6999480147231427</v>
       </c>
-      <c r="F21" s="16" t="n">
-        <v>1.196782049460671</v>
+      <c r="F21" s="14" t="n">
+        <v>30115</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>0.5763970398131397</v>
       </c>
     </row>
     <row r="22">
@@ -1819,8 +2007,11 @@
       <c r="E22" s="15" t="n">
         <v>0.6716744866335114</v>
       </c>
-      <c r="F22" s="16" t="n">
-        <v>1.259734933311581</v>
+      <c r="F22" s="14" t="n">
+        <v>28290</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>0.541466785864643</v>
       </c>
     </row>
     <row r="23">
@@ -1839,8 +2030,11 @@
       <c r="E23" s="15" t="n">
         <v>0.6127515037240275</v>
       </c>
-      <c r="F23" s="16" t="n">
-        <v>1.254980865831196</v>
+      <c r="F23" s="14" t="n">
+        <v>26038</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>0.4983638094854569</v>
       </c>
     </row>
     <row r="24">
@@ -1859,8 +2053,11 @@
       <c r="E24" s="15" t="n">
         <v>0.5844779756343962</v>
       </c>
-      <c r="F24" s="16" t="n">
-        <v>1.300820027351668</v>
+      <c r="F24" s="14" t="n">
+        <v>24331</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>0.4656920596278766</v>
       </c>
     </row>
     <row r="25">
@@ -1879,8 +2076,11 @@
       <c r="E25" s="15" t="n">
         <v>0.5495518527001457</v>
       </c>
-      <c r="F25" s="16" t="n">
-        <v>1.28746115672418</v>
+      <c r="F25" s="14" t="n">
+        <v>22772</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>0.4358530098165306</v>
       </c>
     </row>
     <row r="26">
@@ -1899,8 +2099,11 @@
       <c r="E26" s="15" t="n">
         <v>0.528881290147222</v>
       </c>
-      <c r="F26" s="16" t="n">
-        <v>1.332547345091953</v>
+      <c r="F26" s="14" t="n">
+        <v>21527</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0.4120238776708438</v>
       </c>
     </row>
     <row r="27">
@@ -1919,8 +2122,11 @@
       <c r="E27" s="15" t="n">
         <v>0.4732846046600476</v>
       </c>
-      <c r="F27" s="16" t="n">
-        <v>1.316683686221811</v>
+      <c r="F27" s="14" t="n">
+        <v>20212</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>0.3868549549627489</v>
       </c>
     </row>
     <row r="28">
@@ -1939,8 +2145,11 @@
       <c r="E28" s="15" t="n">
         <v>0.4566531175484998</v>
       </c>
-      <c r="F28" s="16" t="n">
-        <v>1.325650102104935</v>
+      <c r="F28" s="14" t="n">
+        <v>19264</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>0.3687103627747078</v>
       </c>
     </row>
     <row r="29">
@@ -1959,8 +2168,11 @@
       <c r="E29" s="15" t="n">
         <v>0.4440607058783279</v>
       </c>
-      <c r="F29" s="16" t="n">
-        <v>1.350759837279998</v>
+      <c r="F29" s="14" t="n">
+        <v>17900</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0.3426035866729272</v>
       </c>
     </row>
     <row r="30">
@@ -1979,8 +2191,11 @@
       <c r="E30" s="15" t="n">
         <v>0.4179255118458955</v>
       </c>
-      <c r="F30" s="16" t="n">
-        <v>1.351291813684276</v>
+      <c r="F30" s="14" t="n">
+        <v>17170</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>0.3286314850935285</v>
       </c>
     </row>
     <row r="31">
@@ -1999,8 +2214,11 @@
       <c r="E31" s="15" t="n">
         <v>0.3891767984102199</v>
       </c>
-      <c r="F31" s="16" t="n">
-        <v>1.329139295616015</v>
+      <c r="F31" s="14" t="n">
+        <v>16355</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0.3130324949740628</v>
       </c>
     </row>
     <row r="32">
@@ -2019,8 +2237,11 @@
       <c r="E32" s="15" t="n">
         <v>0.3789603134702691</v>
       </c>
-      <c r="F32" s="16" t="n">
-        <v>1.378884790075039</v>
+      <c r="F32" s="14" t="n">
+        <v>15165</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>0.2902560554131252</v>
       </c>
     </row>
     <row r="33">
@@ -2039,8 +2260,11 @@
       <c r="E33" s="15" t="n">
         <v>0.336431224999311</v>
       </c>
-      <c r="F33" s="16" t="n">
-        <v>1.241046461885165</v>
+      <c r="F33" s="14" t="n">
+        <v>14264</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>0.2730110368884153</v>
       </c>
     </row>
     <row r="34">
@@ -2059,8 +2283,11 @@
       <c r="E34" s="15" t="n">
         <v>0.3278778887705149</v>
       </c>
-      <c r="F34" s="16" t="n">
-        <v>1.223008337474658</v>
+      <c r="F34" s="14" t="n">
+        <v>13164</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>0.2519571851934309</v>
       </c>
     </row>
     <row r="35">
@@ -2079,8 +2306,11 @@
       <c r="E35" s="15" t="n">
         <v>0.2884375050488443</v>
       </c>
-      <c r="F35" s="16" t="n">
-        <v>1.332766911304689</v>
+      <c r="F35" s="14" t="n">
+        <v>12049</v>
+      </c>
+      <c r="G35" s="15" t="n">
+        <v>0.2306162355207877</v>
       </c>
     </row>
     <row r="36">
@@ -2099,8 +2329,11 @@
       <c r="E36" s="15" t="n">
         <v>0.2699052765531195</v>
       </c>
-      <c r="F36" s="16" t="n">
-        <v>1.269092709611384</v>
+      <c r="F36" s="14" t="n">
+        <v>11068</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>0.2118400277818971</v>
       </c>
     </row>
     <row r="37">
@@ -2119,8 +2352,11 @@
       <c r="E37" s="15" t="n">
         <v>0.2594511989401466</v>
       </c>
-      <c r="F37" s="16" t="n">
-        <v>1.408383372861414</v>
+      <c r="F37" s="14" t="n">
+        <v>10133</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>0.1939442538411604</v>
       </c>
     </row>
     <row r="38">
@@ -2139,8 +2375,11 @@
       <c r="E38" s="15" t="n">
         <v>0.23284081956167</v>
       </c>
-      <c r="F38" s="16" t="n">
-        <v>1.340205663167194</v>
+      <c r="F38" s="14" t="n">
+        <v>9351</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>0.1789768792725442</v>
       </c>
     </row>
     <row r="39">
@@ -2159,8 +2398,11 @@
       <c r="E39" s="15" t="n">
         <v>0.2126454423547905</v>
       </c>
-      <c r="F39" s="16" t="n">
-        <v>1.213502110151911</v>
+      <c r="F39" s="14" t="n">
+        <v>8659</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>0.1657320925698814</v>
       </c>
     </row>
     <row r="40">
@@ -2179,8 +2421,11 @@
       <c r="E40" s="15" t="n">
         <v>0.1926876578209331</v>
       </c>
-      <c r="F40" s="16" t="n">
-        <v>1.243036458327092</v>
+      <c r="F40" s="14" t="n">
+        <v>7844</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>0.1501331024504157</v>
       </c>
     </row>
     <row r="41">
@@ -2199,8 +2444,11 @@
       <c r="E41" s="15" t="n">
         <v>0.171304317248943</v>
       </c>
-      <c r="F41" s="16" t="n">
-        <v>1.229860004878774</v>
+      <c r="F41" s="14" t="n">
+        <v>7287</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>0.1394721975466827</v>
       </c>
     </row>
     <row r="42">
@@ -2219,8 +2467,11 @@
       <c r="E42" s="15" t="n">
         <v>0.1594246835978373</v>
       </c>
-      <c r="F42" s="16" t="n">
-        <v>1.314137666896973</v>
+      <c r="F42" s="14" t="n">
+        <v>6671</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>0.1276820405974915</v>
       </c>
     </row>
     <row r="43">
@@ -2239,8 +2490,11 @@
       <c r="E43" s="15" t="n">
         <v>0.1427931964862895</v>
       </c>
-      <c r="F43" s="16" t="n">
-        <v>1.214529806491149</v>
+      <c r="F43" s="14" t="n">
+        <v>5983</v>
+      </c>
+      <c r="G43" s="15" t="n">
+        <v>0.1145138133555376</v>
       </c>
     </row>
     <row r="44">
@@ -2259,8 +2513,11 @@
       <c r="E44" s="15" t="n">
         <v>0.1306759701621618</v>
       </c>
-      <c r="F44" s="16" t="n">
-        <v>1.363283184152854</v>
+      <c r="F44" s="14" t="n">
+        <v>5518</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>0.1056137760481124</v>
       </c>
     </row>
     <row r="45">
@@ -2279,8 +2536,11 @@
       <c r="E45" s="15" t="n">
         <v>0.1145196683966581</v>
       </c>
-      <c r="F45" s="16" t="n">
-        <v>1.402987812001576</v>
+      <c r="F45" s="14" t="n">
+        <v>5017</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>0.0960247035943059</v>
       </c>
     </row>
     <row r="46">
@@ -2299,8 +2559,11 @@
       <c r="E46" s="15" t="n">
         <v>0.1249737460096311</v>
       </c>
-      <c r="F46" s="16" t="n">
-        <v>1.335085530511176</v>
+      <c r="F46" s="14" t="n">
+        <v>4572</v>
+      </c>
+      <c r="G46" s="15" t="n">
+        <v>0.08750746359042587</v>
       </c>
     </row>
     <row r="47">
@@ -2319,8 +2582,11 @@
       <c r="E47" s="15" t="n">
         <v>0.09693781059302181</v>
       </c>
-      <c r="F47" s="16" t="n">
-        <v>1.578627516833673</v>
+      <c r="F47" s="14" t="n">
+        <v>4186</v>
+      </c>
+      <c r="G47" s="15" t="n">
+        <v>0.08011947563200408</v>
       </c>
     </row>
     <row r="48">
@@ -2339,8 +2605,11 @@
       <c r="E48" s="15" t="n">
         <v>0.09147317911351323</v>
       </c>
-      <c r="F48" s="16" t="n">
-        <v>1.372473857304446</v>
+      <c r="F48" s="14" t="n">
+        <v>3976</v>
+      </c>
+      <c r="G48" s="15" t="n">
+        <v>0.0761001039447798</v>
       </c>
     </row>
     <row r="49">
@@ -2359,8 +2628,11 @@
       <c r="E49" s="15" t="n">
         <v>0.08030632348147394</v>
       </c>
-      <c r="F49" s="16" t="n">
-        <v>1.357447265343822</v>
+      <c r="F49" s="14" t="n">
+        <v>3545</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>0.06785082205338139</v>
       </c>
     </row>
     <row r="50">
@@ -2379,8 +2651,11 @@
       <c r="E50" s="15" t="n">
         <v>0.07626724804009805</v>
       </c>
-      <c r="F50" s="16" t="n">
-        <v>1.072049367855932</v>
+      <c r="F50" s="14" t="n">
+        <v>3271</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>0.06260649899481256</v>
       </c>
     </row>
     <row r="51">
@@ -2399,8 +2674,11 @@
       <c r="E51" s="15" t="n">
         <v>0.06628835577316933</v>
       </c>
-      <c r="F51" s="16" t="n">
-        <v>1.341200249930213</v>
+      <c r="F51" s="14" t="n">
+        <v>2983</v>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>0.05709421782376211</v>
       </c>
     </row>
     <row r="52">
@@ -2419,8 +2697,11 @@
       <c r="E52" s="15" t="n">
         <v>0.06866428250339045</v>
       </c>
-      <c r="F52" s="16" t="n">
-        <v>1.328868815498877</v>
+      <c r="F52" s="14" t="n">
+        <v>2757</v>
+      </c>
+      <c r="G52" s="15" t="n">
+        <v>0.05276860829370169</v>
       </c>
     </row>
     <row r="53">
@@ -2439,8 +2720,11 @@
       <c r="E53" s="15" t="n">
         <v>0.05725983419832906</v>
       </c>
-      <c r="F53" s="16" t="n">
-        <v>1.341453258843612</v>
+      <c r="F53" s="14" t="n">
+        <v>2577</v>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>0.04932343256179516</v>
       </c>
     </row>
     <row r="54">
@@ -2459,8 +2743,11 @@
       <c r="E54" s="15" t="n">
         <v>0.04894409064255513</v>
       </c>
-      <c r="F54" s="16" t="n">
-        <v>1.390601586063538</v>
+      <c r="F54" s="14" t="n">
+        <v>2201</v>
+      </c>
+      <c r="G54" s="15" t="n">
+        <v>0.04212684325514596</v>
       </c>
     </row>
     <row r="55">
@@ -2479,8 +2766,11 @@
       <c r="E55" s="15" t="n">
         <v>0.04846890529651091</v>
       </c>
-      <c r="F55" s="16" t="n">
-        <v>1.320892412044502</v>
+      <c r="F55" s="14" t="n">
+        <v>2048</v>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>0.03919844388302541</v>
       </c>
     </row>
     <row r="56">
@@ -2499,8 +2789,11 @@
       <c r="E56" s="15" t="n">
         <v>0.0406283470867812</v>
       </c>
-      <c r="F56" s="16" t="n">
-        <v>1.427729298312807</v>
+      <c r="F56" s="14" t="n">
+        <v>1920</v>
+      </c>
+      <c r="G56" s="15" t="n">
+        <v>0.03674854114033632</v>
       </c>
     </row>
     <row r="57">
@@ -2519,8 +2812,11 @@
       <c r="E57" s="15" t="n">
         <v>0.04110353243282543</v>
       </c>
-      <c r="F57" s="16" t="n">
-        <v>1.076240386092007</v>
+      <c r="F57" s="14" t="n">
+        <v>1729</v>
+      </c>
+      <c r="G57" s="15" t="n">
+        <v>0.03309282689147995</v>
       </c>
     </row>
     <row r="58">
@@ -2539,8 +2835,11 @@
       <c r="E58" s="15" t="n">
         <v>0.03611408629936107</v>
       </c>
-      <c r="F58" s="16" t="n">
-        <v>1.555662031136535</v>
+      <c r="F58" s="14" t="n">
+        <v>1574</v>
+      </c>
+      <c r="G58" s="15" t="n">
+        <v>0.03012614778900488</v>
       </c>
     </row>
     <row r="59">
@@ -2559,8 +2858,11 @@
       <c r="E59" s="15" t="n">
         <v>0.02803593541660925</v>
       </c>
-      <c r="F59" s="16" t="n">
-        <v>1.247941164451194</v>
+      <c r="F59" s="14" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G59" s="15" t="n">
+        <v>0.02660441259638932</v>
       </c>
     </row>
     <row r="60">
@@ -2579,8 +2881,11 @@
       <c r="E60" s="15" t="n">
         <v>0.03563890095331684</v>
       </c>
-      <c r="F60" s="16" t="n">
-        <v>2.163226209564859</v>
+      <c r="F60" s="14" t="n">
+        <v>1309</v>
+      </c>
+      <c r="G60" s="15" t="n">
+        <v>0.02505408351703138</v>
       </c>
     </row>
     <row r="61">
@@ -2599,8 +2904,11 @@
       <c r="E61" s="15" t="n">
         <v>0.02756075007056502</v>
       </c>
-      <c r="F61" s="16" t="n">
-        <v>1.314417449240362</v>
+      <c r="F61" s="14" t="n">
+        <v>1203</v>
+      </c>
+      <c r="G61" s="15" t="n">
+        <v>0.02302525780824198</v>
       </c>
     </row>
     <row r="62">
@@ -2619,8 +2927,11 @@
       <c r="E62" s="15" t="n">
         <v>0.02732315739754291</v>
       </c>
-      <c r="F62" s="16" t="n">
-        <v>1.303086264333118</v>
+      <c r="F62" s="14" t="n">
+        <v>1082</v>
+      </c>
+      <c r="G62" s="15" t="n">
+        <v>0.0207093341217937</v>
       </c>
     </row>
     <row r="63">
@@ -2639,8 +2950,11 @@
       <c r="E63" s="15" t="n">
         <v>0.02043296987990166</v>
       </c>
-      <c r="F63" s="16" t="n">
-        <v>1.09141973026579</v>
+      <c r="F63" s="14" t="n">
+        <v>987</v>
+      </c>
+      <c r="G63" s="15" t="n">
+        <v>0.01889104692995414</v>
       </c>
     </row>
     <row r="64">
@@ -2659,8 +2973,11 @@
       <c r="E64" s="15" t="n">
         <v>0.01972019186083532</v>
       </c>
-      <c r="F64" s="16" t="n">
-        <v>1.196985169292555</v>
+      <c r="F64" s="14" t="n">
+        <v>842</v>
+      </c>
+      <c r="G64" s="15" t="n">
+        <v>0.01611576647925166</v>
       </c>
     </row>
     <row r="65">
@@ -2679,8 +2996,11 @@
       <c r="E65" s="15" t="n">
         <v>0.01995778453385743</v>
       </c>
-      <c r="F65" s="16" t="n">
-        <v>1.480608161213281</v>
+      <c r="F65" s="14" t="n">
+        <v>826</v>
+      </c>
+      <c r="G65" s="15" t="n">
+        <v>0.01580952863641552</v>
       </c>
     </row>
     <row r="66">
@@ -2699,8 +3019,11 @@
       <c r="E66" s="15" t="n">
         <v>0.01710667245759208</v>
       </c>
-      <c r="F66" s="16" t="n">
-        <v>1.52291125153366</v>
+      <c r="F66" s="14" t="n">
+        <v>714</v>
+      </c>
+      <c r="G66" s="15" t="n">
+        <v>0.01366586373656257</v>
       </c>
     </row>
     <row r="67">
@@ -2719,8 +3042,11 @@
       <c r="E67" s="15" t="n">
         <v>0.01449315305434885</v>
       </c>
-      <c r="F67" s="16" t="n">
-        <v>2.150407091285956</v>
+      <c r="F67" s="14" t="n">
+        <v>640</v>
+      </c>
+      <c r="G67" s="15" t="n">
+        <v>0.01224951371344544</v>
       </c>
     </row>
     <row r="68">
@@ -2739,8 +3065,11 @@
       <c r="E68" s="15" t="n">
         <v>0.02043296987990166</v>
       </c>
-      <c r="F68" s="16" t="n">
-        <v>1.515860736480264</v>
+      <c r="F68" s="14" t="n">
+        <v>593</v>
+      </c>
+      <c r="G68" s="15" t="n">
+        <v>0.01134994005011429</v>
       </c>
     </row>
     <row r="69">
@@ -2759,8 +3088,11 @@
       <c r="E69" s="15" t="n">
         <v>0.01211722632412773</v>
       </c>
-      <c r="F69" s="16" t="n">
-        <v>1.797881338616127</v>
+      <c r="F69" s="14" t="n">
+        <v>578</v>
+      </c>
+      <c r="G69" s="15" t="n">
+        <v>0.01106284207245541</v>
       </c>
     </row>
     <row r="70">
@@ -2779,8 +3111,11 @@
       <c r="E70" s="15" t="n">
         <v>0.0116420409780835</v>
       </c>
-      <c r="F70" s="16" t="n">
-        <v>1.943298211592431</v>
+      <c r="F70" s="14" t="n">
+        <v>513</v>
+      </c>
+      <c r="G70" s="15" t="n">
+        <v>0.009818750835933612</v>
       </c>
     </row>
     <row r="71">
@@ -2799,8 +3134,11 @@
       <c r="E71" s="15" t="n">
         <v>0.01140444830506139</v>
       </c>
-      <c r="F71" s="16" t="n">
-        <v>1.52291125153366</v>
+      <c r="F71" s="14" t="n">
+        <v>463</v>
+      </c>
+      <c r="G71" s="15" t="n">
+        <v>0.008861757577070686</v>
       </c>
     </row>
     <row r="72">
@@ -2819,8 +3157,11 @@
       <c r="E72" s="15" t="n">
         <v>0.009741299593906603</v>
       </c>
-      <c r="F72" s="16" t="n">
-        <v>2.601640054703337</v>
+      <c r="F72" s="14" t="n">
+        <v>425</v>
+      </c>
+      <c r="G72" s="15" t="n">
+        <v>0.008134442700334863</v>
       </c>
     </row>
     <row r="73">
@@ -2839,8 +3180,11 @@
       <c r="E73" s="15" t="n">
         <v>0.009741299593906603</v>
       </c>
-      <c r="F73" s="16" t="n">
-        <v>1.626025034189585</v>
+      <c r="F73" s="14" t="n">
+        <v>388</v>
+      </c>
+      <c r="G73" s="15" t="n">
+        <v>0.007426267688776298</v>
       </c>
     </row>
     <row r="74">
@@ -2859,8 +3203,11 @@
       <c r="E74" s="15" t="n">
         <v>0.006652594844619143</v>
       </c>
-      <c r="F74" s="16" t="n">
-        <v>1.776729793455937</v>
+      <c r="F74" s="14" t="n">
+        <v>347</v>
+      </c>
+      <c r="G74" s="15" t="n">
+        <v>0.0066415332165087</v>
       </c>
     </row>
     <row r="75">
@@ -2879,8 +3226,11 @@
       <c r="E75" s="15" t="n">
         <v>0.006890187517641256</v>
       </c>
-      <c r="F75" s="16" t="n">
-        <v>1.840184428936507</v>
+      <c r="F75" s="14" t="n">
+        <v>286</v>
+      </c>
+      <c r="G75" s="15" t="n">
+        <v>0.005474001440695931</v>
       </c>
     </row>
     <row r="76">
@@ -2899,8 +3249,11 @@
       <c r="E76" s="15" t="n">
         <v>0.00736537286368548</v>
       </c>
-      <c r="F76" s="16" t="n">
-        <v>4.917734249744112</v>
+      <c r="F76" s="14" t="n">
+        <v>299</v>
+      </c>
+      <c r="G76" s="15" t="n">
+        <v>0.005722819688000292</v>
       </c>
     </row>
     <row r="77">
@@ -2919,8 +3272,11 @@
       <c r="E77" s="15" t="n">
         <v>0.005939816825552807</v>
       </c>
-      <c r="F77" s="16" t="n">
-        <v>1.58636588701423</v>
+      <c r="F77" s="14" t="n">
+        <v>265</v>
+      </c>
+      <c r="G77" s="15" t="n">
+        <v>0.005072064271973503</v>
       </c>
     </row>
     <row r="78">
@@ -2939,8 +3295,11 @@
       <c r="E78" s="15" t="n">
         <v>0.003563890095331684</v>
       </c>
-      <c r="F78" s="16" t="n">
-        <v>0.67987109443467</v>
+      <c r="F78" s="14" t="n">
+        <v>246</v>
+      </c>
+      <c r="G78" s="15" t="n">
+        <v>0.004708406833605592</v>
       </c>
     </row>
     <row r="79">
@@ -2959,8 +3318,11 @@
       <c r="E79" s="15" t="n">
         <v>0.00308870474928746</v>
       </c>
-      <c r="F79" s="16" t="n">
-        <v>4.124551306236998</v>
+      <c r="F79" s="14" t="n">
+        <v>194</v>
+      </c>
+      <c r="G79" s="15" t="n">
+        <v>0.003713133844388149</v>
       </c>
     </row>
     <row r="80">
@@ -2979,8 +3341,11 @@
       <c r="E80" s="15" t="n">
         <v>0.004276668114398021</v>
       </c>
-      <c r="F80" s="16" t="n">
-        <v>1.903639064417076</v>
+      <c r="F80" s="14" t="n">
+        <v>213</v>
+      </c>
+      <c r="G80" s="15" t="n">
+        <v>0.004076791282756061</v>
       </c>
     </row>
     <row r="81">
@@ -2999,8 +3364,11 @@
       <c r="E81" s="15" t="n">
         <v>0.005464631479508582</v>
       </c>
-      <c r="F81" s="16" t="n">
-        <v>1.042469011466494</v>
+      <c r="F81" s="14" t="n">
+        <v>190</v>
+      </c>
+      <c r="G81" s="15" t="n">
+        <v>0.003636574383679115</v>
       </c>
     </row>
     <row r="82">
@@ -3019,8 +3387,11 @@
       <c r="E82" s="15" t="n">
         <v>0.00308870474928746</v>
       </c>
-      <c r="F82" s="16" t="n">
-        <v>2.062275653118499</v>
+      <c r="F82" s="14" t="n">
+        <v>168</v>
+      </c>
+      <c r="G82" s="15" t="n">
+        <v>0.003215497349779428</v>
       </c>
     </row>
     <row r="83">
@@ -3039,8 +3410,11 @@
       <c r="E83" s="15" t="n">
         <v>0.001663148711154786</v>
       </c>
-      <c r="F83" s="16" t="n">
-        <v>1.110456120909961</v>
+      <c r="F83" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="G83" s="15" t="n">
+        <v>0.002909259506943292</v>
       </c>
     </row>
     <row r="84">
@@ -3059,8 +3433,11 @@
       <c r="E84" s="15" t="n">
         <v>0.002851112076265347</v>
       </c>
-      <c r="F84" s="16" t="n">
-        <v>0.9518195322085379</v>
+      <c r="F84" s="14" t="n">
+        <v>159</v>
+      </c>
+      <c r="G84" s="15" t="n">
+        <v>0.003043238563184102</v>
       </c>
     </row>
     <row r="85">
@@ -3079,8 +3456,11 @@
       <c r="E85" s="15" t="n">
         <v>0.003563890095331684</v>
       </c>
-      <c r="F85" s="16" t="n">
-        <v>1.189774415260672</v>
+      <c r="F85" s="14" t="n">
+        <v>145</v>
+      </c>
+      <c r="G85" s="15" t="n">
+        <v>0.002775280450702483</v>
       </c>
     </row>
     <row r="86">
@@ -3099,8 +3479,11 @@
       <c r="E86" s="15" t="n">
         <v>0.002613519403243235</v>
       </c>
-      <c r="F86" s="16" t="n">
-        <v>3.490004951431306</v>
+      <c r="F86" s="14" t="n">
+        <v>136</v>
+      </c>
+      <c r="G86" s="15" t="n">
+        <v>0.002603021664107156</v>
       </c>
     </row>
     <row r="87">
@@ -3119,8 +3502,11 @@
       <c r="E87" s="15" t="n">
         <v>0.00213833405719901</v>
       </c>
-      <c r="F87" s="16" t="n">
-        <v>1.427729298312807</v>
+      <c r="F87" s="14" t="n">
+        <v>149</v>
+      </c>
+      <c r="G87" s="15" t="n">
+        <v>0.002851839911411517</v>
       </c>
     </row>
     <row r="88">
@@ -3139,8 +3525,11 @@
       <c r="E88" s="15" t="n">
         <v>0.001663148711154786</v>
       </c>
-      <c r="F88" s="16" t="n">
-        <v>0.4441824483639843</v>
+      <c r="F88" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="G88" s="15" t="n">
+        <v>0.002277643956093762</v>
       </c>
     </row>
     <row r="89">
@@ -3159,8 +3548,11 @@
       <c r="E89" s="15" t="n">
         <v>0.00213833405719901</v>
       </c>
-      <c r="F89" s="16" t="n">
-        <v>1.427729298312807</v>
+      <c r="F89" s="14" t="n">
+        <v>129</v>
+      </c>
+      <c r="G89" s="15" t="n">
+        <v>0.002469042607866347</v>
       </c>
     </row>
     <row r="90">
@@ -3179,7 +3571,12 @@
       <c r="E90" s="15" t="n">
         <v>0.001663148711154786</v>
       </c>
-      <c r="F90" s="14" t="n"/>
+      <c r="F90" s="14" t="n">
+        <v>127</v>
+      </c>
+      <c r="G90" s="15" t="n">
+        <v>0.00243076287751183</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="n">
@@ -3197,8 +3594,11 @@
       <c r="E91" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F91" s="16" t="n">
-        <v>0.4759097661042689</v>
+      <c r="F91" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="G91" s="15" t="n">
+        <v>0.002373343281980054</v>
       </c>
     </row>
     <row r="92">
@@ -3217,8 +3617,11 @@
       <c r="E92" s="15" t="n">
         <v>0.001663148711154786</v>
       </c>
-      <c r="F92" s="16" t="n">
-        <v>2.220912241819922</v>
+      <c r="F92" s="14" t="n">
+        <v>111</v>
+      </c>
+      <c r="G92" s="15" t="n">
+        <v>0.002124525034675694</v>
       </c>
     </row>
     <row r="93">
@@ -3237,8 +3640,11 @@
       <c r="E93" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F93" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F93" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="G93" s="15" t="n">
+        <v>0.002143664899852952</v>
       </c>
     </row>
     <row r="94">
@@ -3257,8 +3663,11 @@
       <c r="E94" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F94" s="16" t="n">
-        <v>0.3172731774028459</v>
+      <c r="F94" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="G94" s="15" t="n">
+        <v>0.001971406113257626</v>
       </c>
     </row>
     <row r="95">
@@ -3277,8 +3686,11 @@
       <c r="E95" s="15" t="n">
         <v>0.001425556038132674</v>
       </c>
-      <c r="F95" s="16" t="n">
-        <v>0.3172731774028459</v>
+      <c r="F95" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="G95" s="15" t="n">
+        <v>0.00191398651772585</v>
       </c>
     </row>
     <row r="96">
@@ -3297,8 +3709,11 @@
       <c r="E96" s="15" t="n">
         <v>0.001187963365110561</v>
       </c>
-      <c r="F96" s="16" t="n">
-        <v>0.7931829435071149</v>
+      <c r="F96" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="G96" s="15" t="n">
+        <v>0.001722587865953265</v>
       </c>
     </row>
     <row r="97">
@@ -3317,8 +3732,11 @@
       <c r="E97" s="15" t="n">
         <v>0.001663148711154786</v>
       </c>
-      <c r="F97" s="16" t="n">
-        <v>0.7403040806066405</v>
+      <c r="F97" s="14" t="n">
+        <v>86</v>
+      </c>
+      <c r="G97" s="15" t="n">
+        <v>0.001646028405244231</v>
       </c>
     </row>
     <row r="98">
@@ -3337,8 +3755,11 @@
       <c r="E98" s="15" t="n">
         <v>0.0009503706920884491</v>
       </c>
-      <c r="F98" s="16" t="n">
-        <v>0.634546354805692</v>
+      <c r="F98" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="G98" s="15" t="n">
+        <v>0.001512049349003422</v>
       </c>
     </row>
     <row r="99">
@@ -3357,8 +3778,11 @@
       <c r="E99" s="15" t="n">
         <v>0.001425556038132674</v>
       </c>
-      <c r="F99" s="16" t="n">
-        <v>0.4759097661042689</v>
+      <c r="F99" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="G99" s="15" t="n">
+        <v>0.001971406113257626</v>
       </c>
     </row>
     <row r="100">
@@ -3377,8 +3801,11 @@
       <c r="E100" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F100" s="16" t="n">
-        <v>0.2379548830521345</v>
+      <c r="F100" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="G100" s="15" t="n">
+        <v>0.001722587865953265</v>
       </c>
     </row>
     <row r="101">
@@ -3397,8 +3824,11 @@
       <c r="E101" s="15" t="n">
         <v>0.0009503706920884491</v>
       </c>
-      <c r="F101" s="16" t="n">
-        <v>0.634546354805692</v>
+      <c r="F101" s="14" t="n">
+        <v>81</v>
+      </c>
+      <c r="G101" s="15" t="n">
+        <v>0.001550329079357939</v>
       </c>
     </row>
     <row r="102">
@@ -3417,7 +3847,12 @@
       <c r="E102" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F102" s="14" t="n"/>
+      <c r="F102" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="G102" s="15" t="n">
+        <v>0.001435489888294388</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="14" t="n">
@@ -3435,8 +3870,11 @@
       <c r="E103" s="15" t="n">
         <v>0.001187963365110561</v>
       </c>
-      <c r="F103" s="16" t="n">
-        <v>0.7931829435071149</v>
+      <c r="F103" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="G103" s="15" t="n">
+        <v>0.001473769618648905</v>
       </c>
     </row>
     <row r="104">
@@ -3455,8 +3893,11 @@
       <c r="E104" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F104" s="16" t="n">
-        <v>0.0793182943507115</v>
+      <c r="F104" s="14" t="n">
+        <v>69</v>
+      </c>
+      <c r="G104" s="15" t="n">
+        <v>0.001320650697230837</v>
       </c>
     </row>
     <row r="105">
@@ -3475,8 +3916,11 @@
       <c r="E105" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F105" s="16" t="n">
-        <v>0.1057577258009487</v>
+      <c r="F105" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="G105" s="15" t="n">
+        <v>0.001224951371344544</v>
       </c>
     </row>
     <row r="106">
@@ -3495,8 +3939,11 @@
       <c r="E106" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F106" s="16" t="n">
-        <v>0.634546354805692</v>
+      <c r="F106" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="G106" s="15" t="n">
+        <v>0.001626888540066973</v>
       </c>
     </row>
     <row r="107">
@@ -3515,8 +3962,11 @@
       <c r="E107" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F107" s="16" t="n">
-        <v>0</v>
+      <c r="F107" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="G107" s="15" t="n">
+        <v>0.001186671640990027</v>
       </c>
     </row>
     <row r="108">
@@ -3535,8 +3985,11 @@
       <c r="E108" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F108" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F108" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="G108" s="15" t="n">
+        <v>0.0009378533936856665</v>
       </c>
     </row>
     <row r="109">
@@ -3555,8 +4008,11 @@
       <c r="E109" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F109" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F109" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G109" s="15" t="n">
+        <v>0.001052692584749218</v>
       </c>
     </row>
     <row r="110">
@@ -3575,8 +4031,11 @@
       <c r="E110" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F110" s="16" t="n">
-        <v>0.634546354805692</v>
+      <c r="F110" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="G110" s="15" t="n">
+        <v>0.001186671640990027</v>
       </c>
     </row>
     <row r="111">
@@ -3595,7 +4054,12 @@
       <c r="E111" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F111" s="14" t="n"/>
+      <c r="F111" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="G111" s="15" t="n">
+        <v>0.001263231101699061</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="n">
@@ -3613,8 +4077,11 @@
       <c r="E112" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F112" s="16" t="n">
-        <v>0.634546354805692</v>
+      <c r="F112" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="G112" s="15" t="n">
+        <v>0.00128237096687632</v>
       </c>
     </row>
     <row r="113">
@@ -3633,8 +4100,11 @@
       <c r="E113" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="16" t="n">
-        <v>0</v>
+      <c r="F113" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="G113" s="15" t="n">
+        <v>0.001014412854394701</v>
       </c>
     </row>
     <row r="114">
@@ -3653,8 +4123,11 @@
       <c r="E114" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="16" t="n">
-        <v>0</v>
+      <c r="F114" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="G114" s="15" t="n">
+        <v>0.0009187135285084081</v>
       </c>
     </row>
     <row r="115">
@@ -3673,8 +4146,11 @@
       <c r="E115" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F115" s="16" t="n">
-        <v>0.2115154516018973</v>
+      <c r="F115" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="G115" s="15" t="n">
+        <v>0.0008230142026221155</v>
       </c>
     </row>
     <row r="116">
@@ -3693,8 +4169,11 @@
       <c r="E116" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F116" s="16" t="n">
-        <v>0.634546354805692</v>
+      <c r="F116" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="G116" s="15" t="n">
+        <v>0.001071832449926476</v>
       </c>
     </row>
     <row r="117">
@@ -3713,8 +4192,11 @@
       <c r="E117" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="16" t="n">
-        <v>0</v>
+      <c r="F117" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="G117" s="15" t="n">
+        <v>0.001110112180280993</v>
       </c>
     </row>
     <row r="118">
@@ -3733,8 +4215,11 @@
       <c r="E118" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F118" s="16" t="n">
-        <v>0.9518195322085379</v>
+      <c r="F118" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="G118" s="15" t="n">
+        <v>0.001071832449926476</v>
       </c>
     </row>
     <row r="119">
@@ -3753,8 +4238,11 @@
       <c r="E119" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F119" s="16" t="n">
-        <v>0</v>
+      <c r="F119" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="G119" s="15" t="n">
+        <v>0.00114839191063551</v>
       </c>
     </row>
     <row r="120">
@@ -3773,8 +4261,11 @@
       <c r="E120" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F120" s="16" t="n">
-        <v>0</v>
+      <c r="F120" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="G120" s="15" t="n">
+        <v>0.001033552719571959</v>
       </c>
     </row>
     <row r="121">
@@ -3793,8 +4284,11 @@
       <c r="E121" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F121" s="16" t="n">
-        <v>0</v>
+      <c r="F121" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="G121" s="15" t="n">
+        <v>0.0008612939329766325</v>
       </c>
     </row>
     <row r="122">
@@ -3813,8 +4307,11 @@
       <c r="E122" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F122" s="16" t="n">
-        <v>0</v>
+      <c r="F122" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G122" s="15" t="n">
+        <v>0.001052692584749218</v>
       </c>
     </row>
     <row r="123">
@@ -3833,8 +4330,11 @@
       <c r="E123" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F123" s="16" t="n">
-        <v>0.1057577258009487</v>
+      <c r="F123" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="G123" s="15" t="n">
+        <v>0.001167531775812768</v>
       </c>
     </row>
     <row r="124">
@@ -3853,8 +4353,11 @@
       <c r="E124" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F124" s="16" t="n">
-        <v>0</v>
+      <c r="F124" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="G124" s="15" t="n">
+        <v>0.001033552719571959</v>
       </c>
     </row>
     <row r="125">
@@ -3873,8 +4376,11 @@
       <c r="E125" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F125" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F125" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="G125" s="15" t="n">
+        <v>0.001129252045458252</v>
       </c>
     </row>
     <row r="126">
@@ -3893,8 +4399,11 @@
       <c r="E126" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F126" s="16" t="n">
-        <v>0</v>
+      <c r="F126" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G126" s="15" t="n">
+        <v>0.001052692584749218</v>
       </c>
     </row>
     <row r="127">
@@ -3913,8 +4422,11 @@
       <c r="E127" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F127" s="16" t="n">
-        <v>0</v>
+      <c r="F127" s="14" t="n">
+        <v>51</v>
+      </c>
+      <c r="G127" s="15" t="n">
+        <v>0.0009761331240401836</v>
       </c>
     </row>
     <row r="128">
@@ -3933,7 +4445,12 @@
       <c r="E128" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F128" s="14" t="n"/>
+      <c r="F128" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="G128" s="15" t="n">
+        <v>0.0009952729892174421</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="14" t="n">
@@ -3951,8 +4468,11 @@
       <c r="E129" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F129" s="16" t="n">
-        <v>0</v>
+      <c r="F129" s="14" t="n">
+        <v>51</v>
+      </c>
+      <c r="G129" s="15" t="n">
+        <v>0.0009761331240401836</v>
       </c>
     </row>
     <row r="130">
@@ -3971,7 +4491,12 @@
       <c r="E130" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F130" s="14" t="n"/>
+      <c r="F130" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="G130" s="15" t="n">
+        <v>0.0009187135285084081</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="14" t="n">
@@ -3989,8 +4514,11 @@
       <c r="E131" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F131" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F131" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="G131" s="15" t="n">
+        <v>0.001014412854394701</v>
       </c>
     </row>
     <row r="132">
@@ -4009,8 +4537,11 @@
       <c r="E132" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F132" s="16" t="n">
-        <v>0</v>
+      <c r="F132" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="G132" s="15" t="n">
+        <v>0.0008995736633311495</v>
       </c>
     </row>
     <row r="133">
@@ -4029,8 +4560,11 @@
       <c r="E133" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F133" s="16" t="n">
-        <v>0.2115154516018973</v>
+      <c r="F133" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="G133" s="15" t="n">
+        <v>0.0007273148767358231</v>
       </c>
     </row>
     <row r="134">
@@ -4049,8 +4583,11 @@
       <c r="E134" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F134" s="16" t="n">
-        <v>0</v>
+      <c r="F134" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="G134" s="15" t="n">
+        <v>0.0008421540677993741</v>
       </c>
     </row>
     <row r="135">
@@ -4069,8 +4606,11 @@
       <c r="E135" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F135" s="16" t="n">
-        <v>0</v>
+      <c r="F135" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="G135" s="15" t="n">
+        <v>0.0007847344722675985</v>
       </c>
     </row>
     <row r="136">
@@ -4089,7 +4629,12 @@
       <c r="E136" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F136" s="14" t="n"/>
+      <c r="F136" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G136" s="15" t="n">
+        <v>0.0009569932588629251</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="14" t="n">
@@ -4107,8 +4652,11 @@
       <c r="E137" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F137" s="16" t="n">
-        <v>0.1057577258009487</v>
+      <c r="F137" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="G137" s="15" t="n">
+        <v>0.0008995736633311495</v>
       </c>
     </row>
     <row r="138">
@@ -4127,8 +4675,11 @@
       <c r="E138" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F138" s="16" t="n">
-        <v>0</v>
+      <c r="F138" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="G138" s="15" t="n">
+        <v>0.0009187135285084081</v>
       </c>
     </row>
     <row r="139">
@@ -4147,8 +4698,11 @@
       <c r="E139" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F139" s="16" t="n">
-        <v>0</v>
+      <c r="F139" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="G139" s="15" t="n">
+        <v>0.0006698952812040476</v>
       </c>
     </row>
     <row r="140">
@@ -4167,7 +4721,12 @@
       <c r="E140" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F140" s="14" t="n"/>
+      <c r="F140" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="G140" s="15" t="n">
+        <v>0.001301510832053578</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="14" t="n">
@@ -4185,8 +4744,11 @@
       <c r="E141" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F141" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F141" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G141" s="15" t="n">
+        <v>0.0007655946070903401</v>
       </c>
     </row>
     <row r="142">
@@ -4205,8 +4767,11 @@
       <c r="E142" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F142" s="16" t="n">
-        <v>0</v>
+      <c r="F142" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="G142" s="15" t="n">
+        <v>0.0008612939329766325</v>
       </c>
     </row>
     <row r="143">
@@ -4225,7 +4790,12 @@
       <c r="E143" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F143" s="14" t="n"/>
+      <c r="F143" s="14" t="n">
+        <v>51</v>
+      </c>
+      <c r="G143" s="15" t="n">
+        <v>0.0009761331240401836</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="14" t="n">
@@ -4243,7 +4813,12 @@
       <c r="E144" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F144" s="14" t="n"/>
+      <c r="F144" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="G144" s="15" t="n">
+        <v>0.0008804337981538911</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="14" t="n">
@@ -4261,8 +4836,11 @@
       <c r="E145" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F145" s="16" t="n">
-        <v>0.2115154516018973</v>
+      <c r="F145" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="G145" s="15" t="n">
+        <v>0.0007464547419130816</v>
       </c>
     </row>
     <row r="146">
@@ -4281,8 +4859,11 @@
       <c r="E146" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F146" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F146" s="14" t="n">
+        <v>51</v>
+      </c>
+      <c r="G146" s="15" t="n">
+        <v>0.0009761331240401836</v>
       </c>
     </row>
     <row r="147">
@@ -4301,8 +4882,11 @@
       <c r="E147" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F147" s="16" t="n">
-        <v>0</v>
+      <c r="F147" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="G147" s="15" t="n">
+        <v>0.0008804337981538911</v>
       </c>
     </row>
     <row r="148">
@@ -4321,7 +4905,12 @@
       <c r="E148" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F148" s="14" t="n"/>
+      <c r="F148" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="G148" s="15" t="n">
+        <v>0.0009952729892174421</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="14" t="n">
@@ -4339,8 +4928,11 @@
       <c r="E149" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F149" s="16" t="n">
-        <v>0.2115154516018973</v>
+      <c r="F149" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="G149" s="15" t="n">
+        <v>0.0009187135285084081</v>
       </c>
     </row>
     <row r="150">
@@ -4359,8 +4951,11 @@
       <c r="E150" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F150" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F150" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="G150" s="15" t="n">
+        <v>0.0009187135285084081</v>
       </c>
     </row>
     <row r="151">
@@ -4379,8 +4974,11 @@
       <c r="E151" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F151" s="16" t="n">
-        <v>0</v>
+      <c r="F151" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="G151" s="15" t="n">
+        <v>0.001090972315103735</v>
       </c>
     </row>
     <row r="152">
@@ -4399,7 +4997,12 @@
       <c r="E152" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F152" s="14" t="n"/>
+      <c r="F152" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G152" s="15" t="n">
+        <v>0.000650755416026789</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="14" t="n">
@@ -4417,8 +5020,11 @@
       <c r="E153" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F153" s="16" t="n">
-        <v>0</v>
+      <c r="F153" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="G153" s="15" t="n">
+        <v>0.0007847344722675985</v>
       </c>
     </row>
     <row r="154">
@@ -4437,7 +5043,12 @@
       <c r="E154" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F154" s="14" t="n"/>
+      <c r="F154" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="G154" s="15" t="n">
+        <v>0.0008421540677993741</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="14" t="n">
@@ -4455,7 +5066,12 @@
       <c r="E155" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F155" s="14" t="n"/>
+      <c r="F155" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="G155" s="15" t="n">
+        <v>0.0007464547419130816</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="14" t="n">
@@ -4473,8 +5089,11 @@
       <c r="E156" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F156" s="16" t="n">
-        <v>0</v>
+      <c r="F156" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="G156" s="15" t="n">
+        <v>0.0008421540677993741</v>
       </c>
     </row>
     <row r="157">
@@ -4493,8 +5112,11 @@
       <c r="E157" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F157" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F157" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="G157" s="15" t="n">
+        <v>0.0008230142026221155</v>
       </c>
     </row>
     <row r="158">
@@ -4513,8 +5135,11 @@
       <c r="E158" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F158" s="16" t="n">
-        <v>0</v>
+      <c r="F158" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="G158" s="15" t="n">
+        <v>0.0008612939329766325</v>
       </c>
     </row>
     <row r="159">
@@ -4533,8 +5158,11 @@
       <c r="E159" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F159" s="16" t="n">
-        <v>0</v>
+      <c r="F159" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="G159" s="15" t="n">
+        <v>0.0008804337981538911</v>
       </c>
     </row>
     <row r="160">
@@ -4553,8 +5181,11 @@
       <c r="E160" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F160" s="16" t="n">
-        <v>0</v>
+      <c r="F160" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="G160" s="15" t="n">
+        <v>0.0006698952812040476</v>
       </c>
     </row>
     <row r="161">
@@ -4573,8 +5204,11 @@
       <c r="E161" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F161" s="16" t="n">
-        <v>0</v>
+      <c r="F161" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="G161" s="15" t="n">
+        <v>0.0008804337981538911</v>
       </c>
     </row>
     <row r="162">
@@ -4593,8 +5227,11 @@
       <c r="E162" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F162" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F162" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="G162" s="15" t="n">
+        <v>0.0008995736633311495</v>
       </c>
     </row>
     <row r="163">
@@ -4613,7 +5250,12 @@
       <c r="E163" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F163" s="14" t="n"/>
+      <c r="F163" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="G163" s="15" t="n">
+        <v>0.0007273148767358231</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="14" t="n">
@@ -4631,8 +5273,11 @@
       <c r="E164" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F164" s="16" t="n">
-        <v>0</v>
+      <c r="F164" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="G164" s="15" t="n">
+        <v>0.0008038743374448571</v>
       </c>
     </row>
     <row r="165">
@@ -4651,7 +5296,12 @@
       <c r="E165" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F165" s="14" t="n"/>
+      <c r="F165" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="G165" s="15" t="n">
+        <v>0.0007464547419130816</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="14" t="n">
@@ -4669,8 +5319,11 @@
       <c r="E166" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F166" s="16" t="n">
-        <v>0</v>
+      <c r="F166" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="G166" s="15" t="n">
+        <v>0.0009378533936856665</v>
       </c>
     </row>
     <row r="167">
@@ -4689,8 +5342,11 @@
       <c r="E167" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F167" s="16" t="n">
-        <v>0</v>
+      <c r="F167" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="G167" s="15" t="n">
+        <v>0.0007081750115585646</v>
       </c>
     </row>
     <row r="168">
@@ -4709,8 +5365,11 @@
       <c r="E168" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F168" s="16" t="n">
-        <v>0</v>
+      <c r="F168" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="G168" s="15" t="n">
+        <v>0.0005550560901404966</v>
       </c>
     </row>
     <row r="169">
@@ -4729,8 +5388,11 @@
       <c r="E169" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F169" s="16" t="n">
-        <v>0</v>
+      <c r="F169" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="G169" s="15" t="n">
+        <v>0.0006698952812040476</v>
       </c>
     </row>
     <row r="170">
@@ -4749,8 +5411,11 @@
       <c r="E170" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F170" s="16" t="n">
-        <v>0</v>
+      <c r="F170" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="G170" s="15" t="n">
+        <v>0.0008230142026221155</v>
       </c>
     </row>
     <row r="171">
@@ -4769,8 +5434,11 @@
       <c r="E171" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F171" s="16" t="n">
-        <v>0</v>
+      <c r="F171" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="G171" s="15" t="n">
+        <v>0.0008230142026221155</v>
       </c>
     </row>
     <row r="172">
@@ -4789,8 +5457,11 @@
       <c r="E172" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F172" s="16" t="n">
-        <v>0</v>
+      <c r="F172" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G172" s="15" t="n">
+        <v>0.000689035146381306</v>
       </c>
     </row>
     <row r="173">
@@ -4809,7 +5480,12 @@
       <c r="E173" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F173" s="14" t="n"/>
+      <c r="F173" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="G173" s="15" t="n">
+        <v>0.0009187135285084081</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="14" t="n">
@@ -4827,8 +5503,11 @@
       <c r="E174" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F174" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F174" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G174" s="15" t="n">
+        <v>0.000650755416026789</v>
       </c>
     </row>
     <row r="175">
@@ -4847,8 +5526,11 @@
       <c r="E175" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F175" s="16" t="n">
-        <v>0</v>
+      <c r="F175" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="G175" s="15" t="n">
+        <v>0.0006698952812040476</v>
       </c>
     </row>
     <row r="176">
@@ -4867,7 +5549,12 @@
       <c r="E176" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F176" s="14" t="n"/>
+      <c r="F176" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="G176" s="15" t="n">
+        <v>0.0008995736633311495</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="14" t="n">
@@ -4885,8 +5572,11 @@
       <c r="E177" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F177" s="16" t="n">
-        <v>0</v>
+      <c r="F177" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="G177" s="15" t="n">
+        <v>0.0008038743374448571</v>
       </c>
     </row>
     <row r="178">
@@ -4905,7 +5595,12 @@
       <c r="E178" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F178" s="14" t="n"/>
+      <c r="F178" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="G178" s="15" t="n">
+        <v>0.000612475685672272</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="14" t="n">
@@ -4923,7 +5618,12 @@
       <c r="E179" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F179" s="14" t="n"/>
+      <c r="F179" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G179" s="15" t="n">
+        <v>0.0005933358204950136</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="14" t="n">
@@ -4941,8 +5641,11 @@
       <c r="E180" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F180" s="16" t="n">
-        <v>0</v>
+      <c r="F180" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="G180" s="15" t="n">
+        <v>0.0006698952812040476</v>
       </c>
     </row>
     <row r="181">
@@ -4961,8 +5664,11 @@
       <c r="E181" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F181" s="16" t="n">
-        <v>0</v>
+      <c r="F181" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G181" s="15" t="n">
+        <v>0.0007655946070903401</v>
       </c>
     </row>
     <row r="182">
@@ -4981,8 +5687,11 @@
       <c r="E182" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F182" s="16" t="n">
-        <v>0</v>
+      <c r="F182" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="G182" s="15" t="n">
+        <v>0.000612475685672272</v>
       </c>
     </row>
     <row r="183">
@@ -5001,8 +5710,11 @@
       <c r="E183" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F183" s="16" t="n">
-        <v>0</v>
+      <c r="F183" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="G183" s="15" t="n">
+        <v>0.0008995736633311495</v>
       </c>
     </row>
     <row r="184">
@@ -5021,7 +5733,12 @@
       <c r="E184" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F184" s="14" t="n"/>
+      <c r="F184" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="G184" s="15" t="n">
+        <v>0.0007081750115585646</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="14" t="n">
@@ -5039,8 +5756,11 @@
       <c r="E185" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F185" s="16" t="n">
-        <v>0</v>
+      <c r="F185" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G185" s="15" t="n">
+        <v>0.0005933358204950136</v>
       </c>
     </row>
     <row r="186">
@@ -5059,8 +5779,11 @@
       <c r="E186" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F186" s="16" t="n">
-        <v>0</v>
+      <c r="F186" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="G186" s="15" t="n">
+        <v>0.0008230142026221155</v>
       </c>
     </row>
     <row r="187">
@@ -5079,7 +5802,12 @@
       <c r="E187" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F187" s="14" t="n"/>
+      <c r="F187" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G187" s="15" t="n">
+        <v>0.0005933358204950136</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="14" t="n">
@@ -5097,7 +5825,12 @@
       <c r="E188" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F188" s="14" t="n"/>
+      <c r="F188" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="G188" s="15" t="n">
+        <v>0.0007081750115585646</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="14" t="n">
@@ -5115,8 +5848,11 @@
       <c r="E189" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F189" s="16" t="n">
-        <v>0</v>
+      <c r="F189" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G189" s="15" t="n">
+        <v>0.0004784966294314625</v>
       </c>
     </row>
     <row r="190">
@@ -5135,7 +5871,12 @@
       <c r="E190" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F190" s="14" t="n"/>
+      <c r="F190" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G190" s="15" t="n">
+        <v>0.000535916224963238</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="14" t="n">
@@ -5153,7 +5894,12 @@
       <c r="E191" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F191" s="14" t="n"/>
+      <c r="F191" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="G191" s="15" t="n">
+        <v>0.0007464547419130816</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="14" t="n">
@@ -5171,7 +5917,12 @@
       <c r="E192" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F192" s="14" t="n"/>
+      <c r="F192" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="G192" s="15" t="n">
+        <v>0.0009187135285084081</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="14" t="n">
@@ -5189,7 +5940,12 @@
       <c r="E193" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F193" s="14" t="n"/>
+      <c r="F193" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="G193" s="15" t="n">
+        <v>0.0008804337981538911</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="14" t="n">
@@ -5207,8 +5963,11 @@
       <c r="E194" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F194" s="16" t="n">
-        <v>0.634546354805692</v>
+      <c r="F194" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G194" s="15" t="n">
+        <v>0.000689035146381306</v>
       </c>
     </row>
     <row r="195">
@@ -5227,7 +5986,12 @@
       <c r="E195" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F195" s="14" t="n"/>
+      <c r="F195" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G195" s="15" t="n">
+        <v>0.000689035146381306</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="14" t="n">
@@ -5245,7 +6009,12 @@
       <c r="E196" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F196" s="14" t="n"/>
+      <c r="F196" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G196" s="15" t="n">
+        <v>0.000689035146381306</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="14" t="n">
@@ -5263,7 +6032,12 @@
       <c r="E197" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F197" s="14" t="n"/>
+      <c r="F197" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G197" s="15" t="n">
+        <v>0.0005933358204950136</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="14" t="n">
@@ -5281,7 +6055,12 @@
       <c r="E198" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F198" s="14" t="n"/>
+      <c r="F198" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="G198" s="15" t="n">
+        <v>0.0007847344722675985</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="14" t="n">
@@ -5299,7 +6078,12 @@
       <c r="E199" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F199" s="14" t="n"/>
+      <c r="F199" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="G199" s="15" t="n">
+        <v>0.0008230142026221155</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="14" t="n">
@@ -5317,7 +6101,12 @@
       <c r="E200" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F200" s="14" t="n"/>
+      <c r="F200" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G200" s="15" t="n">
+        <v>0.000574195955317755</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="14" t="n">
@@ -5335,7 +6124,12 @@
       <c r="E201" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F201" s="14" t="n"/>
+      <c r="F201" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="G201" s="15" t="n">
+        <v>0.0005167763597859796</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="14" t="n">
@@ -5353,8 +6147,11 @@
       <c r="E202" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F202" s="16" t="n">
-        <v>0</v>
+      <c r="F202" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G202" s="15" t="n">
+        <v>0.0006316155508495306</v>
       </c>
     </row>
     <row r="203">
@@ -5373,8 +6170,11 @@
       <c r="E203" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F203" s="16" t="n">
-        <v>0</v>
+      <c r="F203" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G203" s="15" t="n">
+        <v>0.000421077033899687</v>
       </c>
     </row>
     <row r="204">
@@ -5393,8 +6193,11 @@
       <c r="E204" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F204" s="16" t="n">
-        <v>0</v>
+      <c r="F204" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G204" s="15" t="n">
+        <v>0.000574195955317755</v>
       </c>
     </row>
     <row r="205">
@@ -5413,7 +6216,12 @@
       <c r="E205" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F205" s="14" t="n"/>
+      <c r="F205" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G205" s="15" t="n">
+        <v>0.000689035146381306</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="14" t="n">
@@ -5431,8 +6239,11 @@
       <c r="E206" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F206" s="16" t="n">
-        <v>0</v>
+      <c r="F206" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="G206" s="15" t="n">
+        <v>0.000612475685672272</v>
       </c>
     </row>
     <row r="207">
@@ -5451,8 +6262,11 @@
       <c r="E207" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F207" s="16" t="n">
-        <v>0</v>
+      <c r="F207" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="G207" s="15" t="n">
+        <v>0.0008421540677993741</v>
       </c>
     </row>
     <row r="208">
@@ -5471,8 +6285,11 @@
       <c r="E208" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F208" s="16" t="n">
-        <v>0</v>
+      <c r="F208" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="G208" s="15" t="n">
+        <v>0.0007464547419130816</v>
       </c>
     </row>
     <row r="209">
@@ -5491,8 +6308,11 @@
       <c r="E209" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F209" s="16" t="n">
-        <v>0.1057577258009487</v>
+      <c r="F209" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G209" s="15" t="n">
+        <v>0.000497636494608721</v>
       </c>
     </row>
     <row r="210">
@@ -5511,8 +6331,11 @@
       <c r="E210" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F210" s="16" t="n">
-        <v>0</v>
+      <c r="F210" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G210" s="15" t="n">
+        <v>0.0004402168990769455</v>
       </c>
     </row>
     <row r="211">
@@ -5531,8 +6354,11 @@
       <c r="E211" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F211" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F211" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G211" s="15" t="n">
+        <v>0.000535916224963238</v>
       </c>
     </row>
     <row r="212">
@@ -5551,7 +6377,12 @@
       <c r="E212" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F212" s="14" t="n"/>
+      <c r="F212" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G212" s="15" t="n">
+        <v>0.000497636494608721</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="14" t="n">
@@ -5569,8 +6400,11 @@
       <c r="E213" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F213" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F213" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G213" s="15" t="n">
+        <v>0.0003827973035451701</v>
       </c>
     </row>
     <row r="214">
@@ -5589,8 +6423,11 @@
       <c r="E214" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F214" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F214" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="G214" s="15" t="n">
+        <v>0.0005167763597859796</v>
       </c>
     </row>
     <row r="215">
@@ -5609,7 +6446,12 @@
       <c r="E215" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F215" s="14" t="n"/>
+      <c r="F215" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="G215" s="15" t="n">
+        <v>0.0005550560901404966</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="14" t="n">
@@ -5627,7 +6469,12 @@
       <c r="E216" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F216" s="14" t="n"/>
+      <c r="F216" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G216" s="15" t="n">
+        <v>0.000535916224963238</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="14" t="n">
@@ -5645,8 +6492,11 @@
       <c r="E217" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F217" s="16" t="n">
-        <v>0</v>
+      <c r="F217" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G217" s="15" t="n">
+        <v>0.000535916224963238</v>
       </c>
     </row>
     <row r="218">
@@ -5665,8 +6515,11 @@
       <c r="E218" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F218" s="16" t="n">
-        <v>0</v>
+      <c r="F218" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="G218" s="15" t="n">
+        <v>0.0005167763597859796</v>
       </c>
     </row>
     <row r="219">
@@ -5685,7 +6538,12 @@
       <c r="E219" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F219" s="14" t="n"/>
+      <c r="F219" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G219" s="15" t="n">
+        <v>0.0004402168990769455</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="14" t="n">
@@ -5703,7 +6561,12 @@
       <c r="E220" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F220" s="14" t="n"/>
+      <c r="F220" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="G220" s="15" t="n">
+        <v>0.0007273148767358231</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="14" t="n">
@@ -5721,7 +6584,12 @@
       <c r="E221" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F221" s="14" t="n"/>
+      <c r="F221" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="G221" s="15" t="n">
+        <v>0.0005550560901404966</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="14" t="n">
@@ -5739,8 +6607,11 @@
       <c r="E222" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F222" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F222" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G222" s="15" t="n">
+        <v>0.000497636494608721</v>
       </c>
     </row>
     <row r="223">
@@ -5759,7 +6630,12 @@
       <c r="E223" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F223" s="14" t="n"/>
+      <c r="F223" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="G223" s="15" t="n">
+        <v>0.0005167763597859796</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="14" t="n">
@@ -5777,8 +6653,11 @@
       <c r="E224" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F224" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F224" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G224" s="15" t="n">
+        <v>0.000497636494608721</v>
       </c>
     </row>
     <row r="225">
@@ -5797,8 +6676,11 @@
       <c r="E225" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F225" s="16" t="n">
-        <v>0</v>
+      <c r="F225" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="G225" s="15" t="n">
+        <v>0.000612475685672272</v>
       </c>
     </row>
     <row r="226">
@@ -5817,8 +6699,11 @@
       <c r="E226" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F226" s="16" t="n">
-        <v>0</v>
+      <c r="F226" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="G226" s="15" t="n">
+        <v>0.0005550560901404966</v>
       </c>
     </row>
     <row r="227">
@@ -5837,7 +6722,12 @@
       <c r="E227" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F227" s="14" t="n"/>
+      <c r="F227" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G227" s="15" t="n">
+        <v>0.000689035146381306</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="14" t="n">
@@ -5855,8 +6745,11 @@
       <c r="E228" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F228" s="16" t="n">
-        <v>0</v>
+      <c r="F228" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G228" s="15" t="n">
+        <v>0.0004019371687224285</v>
       </c>
     </row>
     <row r="229">
@@ -5875,8 +6768,11 @@
       <c r="E229" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F229" s="16" t="n">
-        <v>0</v>
+      <c r="F229" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G229" s="15" t="n">
+        <v>0.000689035146381306</v>
       </c>
     </row>
     <row r="230">
@@ -5895,8 +6791,11 @@
       <c r="E230" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F230" s="16" t="n">
-        <v>0</v>
+      <c r="F230" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G230" s="15" t="n">
+        <v>0.000344517573190653</v>
       </c>
     </row>
     <row r="231">
@@ -5915,7 +6814,12 @@
       <c r="E231" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F231" s="14" t="n"/>
+      <c r="F231" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G231" s="15" t="n">
+        <v>0.0004784966294314625</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="14" t="n">
@@ -5933,8 +6837,11 @@
       <c r="E232" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F232" s="16" t="n">
-        <v>0</v>
+      <c r="F232" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G232" s="15" t="n">
+        <v>0.0005933358204950136</v>
       </c>
     </row>
     <row r="233">
@@ -5953,7 +6860,12 @@
       <c r="E233" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F233" s="14" t="n"/>
+      <c r="F233" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G233" s="15" t="n">
+        <v>0.000650755416026789</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="14" t="n">
@@ -5971,7 +6883,12 @@
       <c r="E234" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F234" s="14" t="n"/>
+      <c r="F234" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G234" s="15" t="n">
+        <v>0.000459356764254204</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="14" t="n">
@@ -5989,7 +6906,12 @@
       <c r="E235" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F235" s="14" t="n"/>
+      <c r="F235" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G235" s="15" t="n">
+        <v>0.000497636494608721</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="14" t="n">
@@ -6007,7 +6929,12 @@
       <c r="E236" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F236" s="14" t="n"/>
+      <c r="F236" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G236" s="15" t="n">
+        <v>0.0004784966294314625</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="14" t="n">
@@ -6025,8 +6952,11 @@
       <c r="E237" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F237" s="16" t="n">
-        <v>0</v>
+      <c r="F237" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G237" s="15" t="n">
+        <v>0.0003827973035451701</v>
       </c>
     </row>
     <row r="238">
@@ -6045,7 +6975,12 @@
       <c r="E238" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F238" s="14" t="n"/>
+      <c r="F238" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G238" s="15" t="n">
+        <v>0.000650755416026789</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="14" t="n">
@@ -6063,7 +6998,12 @@
       <c r="E239" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F239" s="14" t="n"/>
+      <c r="F239" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G239" s="15" t="n">
+        <v>0.000497636494608721</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="14" t="n">
@@ -6081,8 +7021,11 @@
       <c r="E240" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F240" s="16" t="n">
-        <v>0</v>
+      <c r="F240" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="G240" s="15" t="n">
+        <v>0.0005167763597859796</v>
       </c>
     </row>
     <row r="241">
@@ -6101,8 +7044,11 @@
       <c r="E241" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F241" s="16" t="n">
-        <v>0</v>
+      <c r="F241" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G241" s="15" t="n">
+        <v>0.0003253777080133945</v>
       </c>
     </row>
     <row r="242">
@@ -6121,7 +7067,12 @@
       <c r="E242" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F242" s="14" t="n"/>
+      <c r="F242" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G242" s="15" t="n">
+        <v>0.000535916224963238</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="14" t="n">
@@ -6139,7 +7090,12 @@
       <c r="E243" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F243" s="14" t="n"/>
+      <c r="F243" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G243" s="15" t="n">
+        <v>0.000574195955317755</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="14" t="n">
@@ -6157,7 +7113,12 @@
       <c r="E244" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F244" s="14" t="n"/>
+      <c r="F244" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G244" s="15" t="n">
+        <v>0.0004402168990769455</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="14" t="n">
@@ -6175,8 +7136,11 @@
       <c r="E245" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F245" s="16" t="n">
-        <v>0</v>
+      <c r="F245" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G245" s="15" t="n">
+        <v>0.000689035146381306</v>
       </c>
     </row>
     <row r="246">
@@ -6195,8 +7159,11 @@
       <c r="E246" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F246" s="16" t="n">
-        <v>0</v>
+      <c r="F246" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G246" s="15" t="n">
+        <v>0.0005933358204950136</v>
       </c>
     </row>
     <row r="247">
@@ -6215,8 +7182,11 @@
       <c r="E247" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F247" s="16" t="n">
-        <v>0</v>
+      <c r="F247" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G247" s="15" t="n">
+        <v>0.0004019371687224285</v>
       </c>
     </row>
     <row r="248">
@@ -6235,8 +7205,11 @@
       <c r="E248" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F248" s="16" t="n">
-        <v>0.634546354805692</v>
+      <c r="F248" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G248" s="15" t="n">
+        <v>0.000574195955317755</v>
       </c>
     </row>
     <row r="249">
@@ -6255,8 +7228,11 @@
       <c r="E249" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F249" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F249" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="G249" s="15" t="n">
+        <v>0.0006698952812040476</v>
       </c>
     </row>
     <row r="250">
@@ -6275,8 +7251,11 @@
       <c r="E250" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F250" s="16" t="n">
-        <v>0</v>
+      <c r="F250" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G250" s="15" t="n">
+        <v>0.0004784966294314625</v>
       </c>
     </row>
     <row r="251">
@@ -6295,8 +7274,11 @@
       <c r="E251" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F251" s="16" t="n">
-        <v>0</v>
+      <c r="F251" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G251" s="15" t="n">
+        <v>0.0002870979776588775</v>
       </c>
     </row>
     <row r="252">
@@ -6315,8 +7297,11 @@
       <c r="E252" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F252" s="16" t="n">
-        <v>0</v>
+      <c r="F252" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G252" s="15" t="n">
+        <v>0.000497636494608721</v>
       </c>
     </row>
     <row r="253">
@@ -6335,7 +7320,12 @@
       <c r="E253" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F253" s="14" t="n"/>
+      <c r="F253" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G253" s="15" t="n">
+        <v>0.000574195955317755</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="14" t="n">
@@ -6353,8 +7343,11 @@
       <c r="E254" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F254" s="16" t="n">
-        <v>0</v>
+      <c r="F254" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G254" s="15" t="n">
+        <v>0.0005933358204950136</v>
       </c>
     </row>
     <row r="255">
@@ -6373,8 +7366,11 @@
       <c r="E255" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F255" s="16" t="n">
-        <v>0</v>
+      <c r="F255" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G255" s="15" t="n">
+        <v>0.0005933358204950136</v>
       </c>
     </row>
     <row r="256">
@@ -6393,8 +7389,11 @@
       <c r="E256" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F256" s="16" t="n">
-        <v>0</v>
+      <c r="F256" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="G256" s="15" t="n">
+        <v>0.0006698952812040476</v>
       </c>
     </row>
     <row r="257">
@@ -6413,8 +7412,11 @@
       <c r="E257" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F257" s="16" t="n">
-        <v>0</v>
+      <c r="F257" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G257" s="15" t="n">
+        <v>0.000650755416026789</v>
       </c>
     </row>
     <row r="258">
@@ -6433,7 +7435,12 @@
       <c r="E258" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F258" s="14" t="n"/>
+      <c r="F258" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="G258" s="15" t="n">
+        <v>0.0007081750115585646</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="14" t="n">
@@ -6451,8 +7458,11 @@
       <c r="E259" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F259" s="16" t="n">
-        <v>0</v>
+      <c r="F259" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="G259" s="15" t="n">
+        <v>0.0007081750115585646</v>
       </c>
     </row>
     <row r="260">
@@ -6471,8 +7481,11 @@
       <c r="E260" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F260" s="16" t="n">
-        <v>0</v>
+      <c r="F260" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G260" s="15" t="n">
+        <v>0.000459356764254204</v>
       </c>
     </row>
     <row r="261">
@@ -6491,8 +7504,11 @@
       <c r="E261" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F261" s="16" t="n">
-        <v>0</v>
+      <c r="F261" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G261" s="15" t="n">
+        <v>0.000689035146381306</v>
       </c>
     </row>
     <row r="262">
@@ -6511,7 +7527,12 @@
       <c r="E262" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F262" s="14" t="n"/>
+      <c r="F262" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="G262" s="15" t="n">
+        <v>0.0007464547419130816</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="14" t="n">
@@ -6529,8 +7550,11 @@
       <c r="E263" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F263" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F263" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G263" s="15" t="n">
+        <v>0.0006316155508495306</v>
       </c>
     </row>
     <row r="264">
@@ -6549,7 +7573,12 @@
       <c r="E264" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F264" s="14" t="n"/>
+      <c r="F264" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="G264" s="15" t="n">
+        <v>0.0008612939329766325</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="14" t="n">
@@ -6567,7 +7596,12 @@
       <c r="E265" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F265" s="14" t="n"/>
+      <c r="F265" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="G265" s="15" t="n">
+        <v>0.0007464547419130816</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="14" t="n">
@@ -6585,7 +7619,12 @@
       <c r="E266" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F266" s="14" t="n"/>
+      <c r="F266" s="14" t="n">
+        <v>51</v>
+      </c>
+      <c r="G266" s="15" t="n">
+        <v>0.0009761331240401836</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="14" t="n">
@@ -6603,8 +7642,11 @@
       <c r="E267" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F267" s="16" t="n">
-        <v>0</v>
+      <c r="F267" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="G267" s="15" t="n">
+        <v>0.0007464547419130816</v>
       </c>
     </row>
     <row r="268">
@@ -6623,8 +7665,11 @@
       <c r="E268" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F268" s="16" t="n">
-        <v>0</v>
+      <c r="F268" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="G268" s="15" t="n">
+        <v>0.0008612939329766325</v>
       </c>
     </row>
     <row r="269">
@@ -6643,8 +7688,11 @@
       <c r="E269" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F269" s="16" t="n">
-        <v>0</v>
+      <c r="F269" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="G269" s="15" t="n">
+        <v>0.0009378533936856665</v>
       </c>
     </row>
     <row r="270">
@@ -6663,8 +7711,11 @@
       <c r="E270" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F270" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F270" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G270" s="15" t="n">
+        <v>0.0009569932588629251</v>
       </c>
     </row>
     <row r="271">
@@ -6683,8 +7734,11 @@
       <c r="E271" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F271" s="16" t="n">
-        <v>0</v>
+      <c r="F271" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="G271" s="15" t="n">
+        <v>0.0009378533936856665</v>
       </c>
     </row>
     <row r="272">
@@ -6703,8 +7757,11 @@
       <c r="E272" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F272" s="16" t="n">
-        <v>0</v>
+      <c r="F272" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G272" s="15" t="n">
+        <v>0.001052692584749218</v>
       </c>
     </row>
     <row r="273">
@@ -6723,8 +7780,11 @@
       <c r="E273" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F273" s="16" t="n">
-        <v>0.634546354805692</v>
+      <c r="F273" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="G273" s="15" t="n">
+        <v>0.0008421540677993741</v>
       </c>
     </row>
     <row r="274">
@@ -6743,8 +7803,11 @@
       <c r="E274" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F274" s="16" t="n">
-        <v>0</v>
+      <c r="F274" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="G274" s="15" t="n">
+        <v>0.0008995736633311495</v>
       </c>
     </row>
     <row r="275">
@@ -6763,8 +7826,11 @@
       <c r="E275" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F275" s="16" t="n">
-        <v>0</v>
+      <c r="F275" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G275" s="15" t="n">
+        <v>0.0007655946070903401</v>
       </c>
     </row>
     <row r="276">
@@ -6783,7 +7849,12 @@
       <c r="E276" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F276" s="14" t="n"/>
+      <c r="F276" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G276" s="15" t="n">
+        <v>0.0006316155508495306</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="14" t="n">
@@ -6801,8 +7872,11 @@
       <c r="E277" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F277" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F277" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="G277" s="15" t="n">
+        <v>0.0008612939329766325</v>
       </c>
     </row>
     <row r="278">
@@ -6821,8 +7895,11 @@
       <c r="E278" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F278" s="16" t="n">
-        <v>0</v>
+      <c r="F278" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="G278" s="15" t="n">
+        <v>0.000689035146381306</v>
       </c>
     </row>
     <row r="279">
@@ -6841,8 +7918,11 @@
       <c r="E279" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F279" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F279" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="G279" s="15" t="n">
+        <v>0.001014412854394701</v>
       </c>
     </row>
     <row r="280">
@@ -6861,8 +7941,11 @@
       <c r="E280" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F280" s="16" t="n">
-        <v>0</v>
+      <c r="F280" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="G280" s="15" t="n">
+        <v>0.000612475685672272</v>
       </c>
     </row>
     <row r="281">
@@ -6881,7 +7964,12 @@
       <c r="E281" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F281" s="14" t="n"/>
+      <c r="F281" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="G281" s="15" t="n">
+        <v>0.0008230142026221155</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="14" t="n">
@@ -6899,7 +7987,12 @@
       <c r="E282" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F282" s="14" t="n"/>
+      <c r="F282" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="G282" s="15" t="n">
+        <v>0.001110112180280993</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="14" t="n">
@@ -6917,8 +8010,11 @@
       <c r="E283" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F283" s="16" t="n">
-        <v>0.9518195322085379</v>
+      <c r="F283" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="G283" s="15" t="n">
+        <v>0.0008421540677993741</v>
       </c>
     </row>
     <row r="284">
@@ -6937,8 +8033,11 @@
       <c r="E284" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F284" s="16" t="n">
-        <v>0</v>
+      <c r="F284" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="G284" s="15" t="n">
+        <v>0.0008421540677993741</v>
       </c>
     </row>
     <row r="285">
@@ -6957,8 +8056,11 @@
       <c r="E285" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F285" s="16" t="n">
-        <v>0</v>
+      <c r="F285" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="G285" s="15" t="n">
+        <v>0.0008612939329766325</v>
       </c>
     </row>
     <row r="286">
@@ -6977,8 +8079,11 @@
       <c r="E286" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F286" s="16" t="n">
-        <v>0.634546354805692</v>
+      <c r="F286" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="G286" s="15" t="n">
+        <v>0.0008230142026221155</v>
       </c>
     </row>
     <row r="287">
@@ -6997,7 +8102,12 @@
       <c r="E287" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F287" s="14" t="n"/>
+      <c r="F287" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="G287" s="15" t="n">
+        <v>0.0008995736633311495</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="14" t="n">
@@ -7015,8 +8125,11 @@
       <c r="E288" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F288" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F288" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="G288" s="15" t="n">
+        <v>0.001014412854394701</v>
       </c>
     </row>
     <row r="289">
@@ -7035,7 +8148,12 @@
       <c r="E289" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F289" s="14" t="n"/>
+      <c r="F289" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="G289" s="15" t="n">
+        <v>0.0009952729892174421</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="14" t="n">
@@ -7053,8 +8171,11 @@
       <c r="E290" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F290" s="16" t="n">
-        <v>0</v>
+      <c r="F290" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G290" s="15" t="n">
+        <v>0.0007655946070903401</v>
       </c>
     </row>
     <row r="291">
@@ -7073,8 +8194,11 @@
       <c r="E291" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F291" s="16" t="n">
-        <v>0</v>
+      <c r="F291" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="G291" s="15" t="n">
+        <v>0.00114839191063551</v>
       </c>
     </row>
     <row r="292">
@@ -7093,8 +8217,11 @@
       <c r="E292" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F292" s="16" t="n">
-        <v>0</v>
+      <c r="F292" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="G292" s="15" t="n">
+        <v>0.001014412854394701</v>
       </c>
     </row>
     <row r="293">
@@ -7113,8 +8240,11 @@
       <c r="E293" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F293" s="16" t="n">
-        <v>0</v>
+      <c r="F293" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="G293" s="15" t="n">
+        <v>0.0007847344722675985</v>
       </c>
     </row>
     <row r="294">
@@ -7133,7 +8263,12 @@
       <c r="E294" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F294" s="14" t="n"/>
+      <c r="F294" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="G294" s="15" t="n">
+        <v>0.0008230142026221155</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="14" t="n">
@@ -7151,8 +8286,11 @@
       <c r="E295" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F295" s="16" t="n">
-        <v>0</v>
+      <c r="F295" s="14" t="n">
+        <v>51</v>
+      </c>
+      <c r="G295" s="15" t="n">
+        <v>0.0009761331240401836</v>
       </c>
     </row>
     <row r="296">
@@ -7171,7 +8309,12 @@
       <c r="E296" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F296" s="14" t="n"/>
+      <c r="F296" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="G296" s="15" t="n">
+        <v>0.001090972315103735</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="14" t="n">
@@ -7189,8 +8332,11 @@
       <c r="E297" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F297" s="16" t="n">
-        <v>0</v>
+      <c r="F297" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G297" s="15" t="n">
+        <v>0.0009569932588629251</v>
       </c>
     </row>
     <row r="298">
@@ -7209,8 +8355,11 @@
       <c r="E298" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F298" s="16" t="n">
-        <v>0.1057577258009487</v>
+      <c r="F298" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="G298" s="15" t="n">
+        <v>0.0007081750115585646</v>
       </c>
     </row>
     <row r="299">
@@ -7229,8 +8378,11 @@
       <c r="E299" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F299" s="16" t="n">
-        <v>0</v>
+      <c r="F299" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="G299" s="15" t="n">
+        <v>0.0008230142026221155</v>
       </c>
     </row>
     <row r="300">
@@ -7249,7 +8401,12 @@
       <c r="E300" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F300" s="14" t="n"/>
+      <c r="F300" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G300" s="15" t="n">
+        <v>0.001052692584749218</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="14" t="n">
@@ -7267,8 +8424,11 @@
       <c r="E301" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F301" s="16" t="n">
-        <v>0</v>
+      <c r="F301" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="G301" s="15" t="n">
+        <v>0.001090972315103735</v>
       </c>
     </row>
     <row r="302">
@@ -7287,8 +8447,11 @@
       <c r="E302" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F302" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F302" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="G302" s="15" t="n">
+        <v>0.0008804337981538911</v>
       </c>
     </row>
     <row r="303">
@@ -7307,7 +8470,12 @@
       <c r="E303" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F303" s="14" t="n"/>
+      <c r="F303" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="G303" s="15" t="n">
+        <v>0.0007847344722675985</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="14" t="n">
@@ -7325,8 +8493,11 @@
       <c r="E304" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F304" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F304" s="14" t="n">
+        <v>51</v>
+      </c>
+      <c r="G304" s="15" t="n">
+        <v>0.0009761331240401836</v>
       </c>
     </row>
     <row r="305">
@@ -7345,8 +8516,11 @@
       <c r="E305" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F305" s="16" t="n">
-        <v>0</v>
+      <c r="F305" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="G305" s="15" t="n">
+        <v>0.0008038743374448571</v>
       </c>
     </row>
     <row r="306">
@@ -7365,8 +8539,11 @@
       <c r="E306" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F306" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F306" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="G306" s="15" t="n">
+        <v>0.0008804337981538911</v>
       </c>
     </row>
     <row r="307">
@@ -7385,8 +8562,11 @@
       <c r="E307" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F307" s="16" t="n">
-        <v>0</v>
+      <c r="F307" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="G307" s="15" t="n">
+        <v>0.0008804337981538911</v>
       </c>
     </row>
     <row r="308">
@@ -7405,7 +8585,12 @@
       <c r="E308" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F308" s="14" t="n"/>
+      <c r="F308" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="G308" s="15" t="n">
+        <v>0.001014412854394701</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="14" t="n">
@@ -7423,8 +8608,11 @@
       <c r="E309" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F309" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F309" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="G309" s="15" t="n">
+        <v>0.0008804337981538911</v>
       </c>
     </row>
     <row r="310">
@@ -7443,8 +8631,11 @@
       <c r="E310" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F310" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F310" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G310" s="15" t="n">
+        <v>0.001052692584749218</v>
       </c>
     </row>
     <row r="311">
@@ -7463,8 +8654,11 @@
       <c r="E311" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F311" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F311" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="G311" s="15" t="n">
+        <v>0.0009378533936856665</v>
       </c>
     </row>
     <row r="312">
@@ -7483,8 +8677,11 @@
       <c r="E312" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F312" s="16" t="n">
-        <v>0</v>
+      <c r="F312" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="G312" s="15" t="n">
+        <v>0.001090972315103735</v>
       </c>
     </row>
     <row r="313">
@@ -7503,8 +8700,11 @@
       <c r="E313" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F313" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F313" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="G313" s="15" t="n">
+        <v>0.001052692584749218</v>
       </c>
     </row>
     <row r="314">
@@ -7523,8 +8723,11 @@
       <c r="E314" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F314" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F314" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="G314" s="15" t="n">
+        <v>0.001033552719571959</v>
       </c>
     </row>
     <row r="315">
@@ -7543,8 +8746,11 @@
       <c r="E315" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F315" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F315" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="G315" s="15" t="n">
+        <v>0.001033552719571959</v>
       </c>
     </row>
     <row r="316">
@@ -7563,8 +8769,11 @@
       <c r="E316" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F316" s="16" t="n">
-        <v>0</v>
+      <c r="F316" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="G316" s="15" t="n">
+        <v>0.001071832449926476</v>
       </c>
     </row>
     <row r="317">
@@ -7583,8 +8792,11 @@
       <c r="E317" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F317" s="16" t="n">
-        <v>0.9518195322085379</v>
+      <c r="F317" s="14" t="n">
+        <v>87</v>
+      </c>
+      <c r="G317" s="15" t="n">
+        <v>0.00166516827042149</v>
       </c>
     </row>
     <row r="318">
@@ -7603,7 +8815,12 @@
       <c r="E318" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F318" s="14" t="n"/>
+      <c r="F318" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="G318" s="15" t="n">
+        <v>0.002105385169498435</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="14" t="n">
@@ -7621,8 +8838,11 @@
       <c r="E319" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F319" s="16" t="n">
-        <v>0</v>
+      <c r="F319" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="G319" s="15" t="n">
+        <v>0.00153118921418068</v>
       </c>
     </row>
     <row r="320">
@@ -7641,8 +8861,11 @@
       <c r="E320" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F320" s="16" t="n">
-        <v>0</v>
+      <c r="F320" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="G320" s="15" t="n">
+        <v>0.002067105439143918</v>
       </c>
     </row>
     <row r="321">
@@ -7661,8 +8884,11 @@
       <c r="E321" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F321" s="16" t="n">
-        <v>0</v>
+      <c r="F321" s="14" t="n">
+        <v>130</v>
+      </c>
+      <c r="G321" s="15" t="n">
+        <v>0.002488182473043605</v>
       </c>
     </row>
     <row r="322">
@@ -7681,8 +8907,11 @@
       <c r="E322" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F322" s="16" t="n">
-        <v>0.3172731774028459</v>
+      <c r="F322" s="14" t="n">
+        <v>145</v>
+      </c>
+      <c r="G322" s="15" t="n">
+        <v>0.002775280450702483</v>
       </c>
     </row>
     <row r="323">
@@ -7701,8 +8930,11 @@
       <c r="E323" s="15" t="n">
         <v>0.0009503706920884491</v>
       </c>
-      <c r="F323" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F323" s="14" t="n">
+        <v>157</v>
+      </c>
+      <c r="G323" s="15" t="n">
+        <v>0.003004958832829585</v>
       </c>
     </row>
     <row r="324">
@@ -7721,8 +8953,11 @@
       <c r="E324" s="15" t="n">
         <v>0.001425556038132674</v>
       </c>
-      <c r="F324" s="16" t="n">
-        <v>0.3172731774028459</v>
+      <c r="F324" s="14" t="n">
+        <v>182</v>
+      </c>
+      <c r="G324" s="15" t="n">
+        <v>0.003483455462261047</v>
       </c>
     </row>
     <row r="325">
@@ -7741,8 +8976,11 @@
       <c r="E325" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F325" s="16" t="n">
-        <v>0.2379548830521345</v>
+      <c r="F325" s="14" t="n">
+        <v>252</v>
+      </c>
+      <c r="G325" s="15" t="n">
+        <v>0.004823246024669142</v>
       </c>
     </row>
     <row r="326">
@@ -7761,8 +8999,11 @@
       <c r="E326" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F326" s="16" t="n">
-        <v>0.07050515053396578</v>
+      <c r="F326" s="14" t="n">
+        <v>288</v>
+      </c>
+      <c r="G326" s="15" t="n">
+        <v>0.005512281171050448</v>
       </c>
     </row>
     <row r="327">
@@ -7781,8 +9022,11 @@
       <c r="E327" s="15" t="n">
         <v>0.0009503706920884491</v>
       </c>
-      <c r="F327" s="16" t="n">
-        <v>0.2115154516018973</v>
+      <c r="F327" s="14" t="n">
+        <v>328</v>
+      </c>
+      <c r="G327" s="15" t="n">
+        <v>0.006277875778140788</v>
       </c>
     </row>
     <row r="328">
@@ -7801,8 +9045,11 @@
       <c r="E328" s="15" t="n">
         <v>0.001663148711154786</v>
       </c>
-      <c r="F328" s="16" t="n">
-        <v>0.2467680268688802</v>
+      <c r="F328" s="14" t="n">
+        <v>339</v>
+      </c>
+      <c r="G328" s="15" t="n">
+        <v>0.006488414295090632</v>
       </c>
     </row>
     <row r="329">
@@ -7821,8 +9068,11 @@
       <c r="E329" s="15" t="n">
         <v>0.002375926730221123</v>
       </c>
-      <c r="F329" s="16" t="n">
-        <v>0.2884301612753145</v>
+      <c r="F329" s="14" t="n">
+        <v>403</v>
+      </c>
+      <c r="G329" s="15" t="n">
+        <v>0.007713365666435176</v>
       </c>
     </row>
     <row r="330">
@@ -7841,8 +9091,11 @@
       <c r="E330" s="15" t="n">
         <v>0.001900741384176898</v>
       </c>
-      <c r="F330" s="16" t="n">
-        <v>0.2538185419222768</v>
+      <c r="F330" s="14" t="n">
+        <v>489</v>
+      </c>
+      <c r="G330" s="15" t="n">
+        <v>0.009359394071679407</v>
       </c>
     </row>
     <row r="331">
@@ -7861,8 +9114,11 @@
       <c r="E331" s="15" t="n">
         <v>0.001900741384176898</v>
       </c>
-      <c r="F331" s="16" t="n">
-        <v>0.2820206021358631</v>
+      <c r="F331" s="14" t="n">
+        <v>584</v>
+      </c>
+      <c r="G331" s="15" t="n">
+        <v>0.01117768126351897</v>
       </c>
     </row>
     <row r="332">
@@ -7881,8 +9137,11 @@
       <c r="E332" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F332" s="16" t="n">
-        <v>0.06798710944346699</v>
+      <c r="F332" s="14" t="n">
+        <v>634</v>
+      </c>
+      <c r="G332" s="15" t="n">
+        <v>0.01213467452238189</v>
       </c>
     </row>
     <row r="333">
@@ -7901,8 +9160,11 @@
       <c r="E333" s="15" t="n">
         <v>0.00213833405719901</v>
       </c>
-      <c r="F333" s="16" t="n">
-        <v>0.1784661622891008</v>
+      <c r="F333" s="14" t="n">
+        <v>728</v>
+      </c>
+      <c r="G333" s="15" t="n">
+        <v>0.01393382184904419</v>
       </c>
     </row>
     <row r="334">
@@ -7921,8 +9183,11 @@
       <c r="E334" s="15" t="n">
         <v>0.001900741384176898</v>
       </c>
-      <c r="F334" s="16" t="n">
-        <v>0.1493050246601628</v>
+      <c r="F334" s="14" t="n">
+        <v>793</v>
+      </c>
+      <c r="G334" s="15" t="n">
+        <v>0.01517791308556599</v>
       </c>
     </row>
     <row r="335">
@@ -7941,8 +9206,11 @@
       <c r="E335" s="15" t="n">
         <v>0.002375926730221123</v>
       </c>
-      <c r="F335" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F335" s="14" t="n">
+        <v>826</v>
+      </c>
+      <c r="G335" s="15" t="n">
+        <v>0.01580952863641552</v>
       </c>
     </row>
     <row r="336">
@@ -7961,8 +9229,11 @@
       <c r="E336" s="15" t="n">
         <v>0.001663148711154786</v>
       </c>
-      <c r="F336" s="16" t="n">
-        <v>0.09253801007583007</v>
+      <c r="F336" s="14" t="n">
+        <v>892</v>
+      </c>
+      <c r="G336" s="15" t="n">
+        <v>0.01707275973811458</v>
       </c>
     </row>
     <row r="337">
@@ -7981,8 +9252,11 @@
       <c r="E337" s="15" t="n">
         <v>0.003563890095331684</v>
       </c>
-      <c r="F337" s="16" t="n">
-        <v>0.22662369814489</v>
+      <c r="F337" s="14" t="n">
+        <v>964</v>
+      </c>
+      <c r="G337" s="15" t="n">
+        <v>0.01845083003087719</v>
       </c>
     </row>
     <row r="338">
@@ -8001,8 +9275,11 @@
       <c r="E338" s="15" t="n">
         <v>0.002375926730221123</v>
       </c>
-      <c r="F338" s="16" t="n">
-        <v>0.0961433870917715</v>
+      <c r="F338" s="14" t="n">
+        <v>1072</v>
+      </c>
+      <c r="G338" s="15" t="n">
+        <v>0.02051793547002111</v>
       </c>
     </row>
     <row r="339">
@@ -8021,8 +9298,11 @@
       <c r="E339" s="15" t="n">
         <v>0.003326297422309572</v>
       </c>
-      <c r="F339" s="16" t="n">
-        <v>0.1480608161213281</v>
+      <c r="F339" s="14" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G339" s="15" t="n">
+        <v>0.02143664899852952</v>
       </c>
     </row>
     <row r="340">
@@ -8041,8 +9321,11 @@
       <c r="E340" s="15" t="n">
         <v>0.003801482768353797</v>
       </c>
-      <c r="F340" s="16" t="n">
-        <v>0.2307441290202516</v>
+      <c r="F340" s="14" t="n">
+        <v>1161</v>
+      </c>
+      <c r="G340" s="15" t="n">
+        <v>0.02222138347079712</v>
       </c>
     </row>
     <row r="341">
@@ -8061,8 +9344,11 @@
       <c r="E341" s="15" t="n">
         <v>0.00308870474928746</v>
       </c>
-      <c r="F341" s="16" t="n">
-        <v>0.1422259071116206</v>
+      <c r="F341" s="14" t="n">
+        <v>1257</v>
+      </c>
+      <c r="G341" s="15" t="n">
+        <v>0.02405881052781393</v>
       </c>
     </row>
     <row r="342">
@@ -8081,8 +9367,11 @@
       <c r="E342" s="15" t="n">
         <v>0.003801482768353797</v>
       </c>
-      <c r="F342" s="16" t="n">
-        <v>0.1637538980143721</v>
+      <c r="F342" s="14" t="n">
+        <v>1355</v>
+      </c>
+      <c r="G342" s="15" t="n">
+        <v>0.02593451731518527</v>
       </c>
     </row>
     <row r="343">
@@ -8101,8 +9390,11 @@
       <c r="E343" s="15" t="n">
         <v>0.003326297422309572</v>
       </c>
-      <c r="F343" s="16" t="n">
-        <v>0.1269092709611384</v>
+      <c r="F343" s="14" t="n">
+        <v>1359</v>
+      </c>
+      <c r="G343" s="15" t="n">
+        <v>0.0260110767758943</v>
       </c>
     </row>
     <row r="344">
@@ -8121,8 +9413,11 @@
       <c r="E344" s="15" t="n">
         <v>0.004989446133464357</v>
       </c>
-      <c r="F344" s="16" t="n">
-        <v>0.1903639064417076</v>
+      <c r="F344" s="14" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G344" s="15" t="n">
+        <v>0.02526462203398122</v>
       </c>
     </row>
     <row r="345">
@@ -8141,8 +9436,11 @@
       <c r="E345" s="15" t="n">
         <v>0.003801482768353797</v>
       </c>
-      <c r="F345" s="16" t="n">
-        <v>0.181298958515912</v>
+      <c r="F345" s="14" t="n">
+        <v>1360</v>
+      </c>
+      <c r="G345" s="15" t="n">
+        <v>0.02603021664107156</v>
       </c>
     </row>
     <row r="346">
@@ -8161,8 +9459,11 @@
       <c r="E346" s="15" t="n">
         <v>0.00213833405719901</v>
       </c>
-      <c r="F346" s="16" t="n">
-        <v>0.09211156763308431</v>
+      <c r="F346" s="14" t="n">
+        <v>1334</v>
+      </c>
+      <c r="G346" s="15" t="n">
+        <v>0.02553258014646284</v>
       </c>
     </row>
     <row r="347">
@@ -8181,8 +9482,11 @@
       <c r="E347" s="15" t="n">
         <v>0.00213833405719901</v>
       </c>
-      <c r="F347" s="16" t="n">
-        <v>0.07717455666555711</v>
+      <c r="F347" s="14" t="n">
+        <v>1265</v>
+      </c>
+      <c r="G347" s="15" t="n">
+        <v>0.02421192944923201</v>
       </c>
     </row>
     <row r="348">
@@ -8201,8 +9505,11 @@
       <c r="E348" s="15" t="n">
         <v>0.002375926730221123</v>
       </c>
-      <c r="F348" s="16" t="n">
-        <v>0.09914786793838937</v>
+      <c r="F348" s="14" t="n">
+        <v>1159</v>
+      </c>
+      <c r="G348" s="15" t="n">
+        <v>0.0221831037404426</v>
       </c>
     </row>
     <row r="349">
@@ -8221,8 +9528,11 @@
       <c r="E349" s="15" t="n">
         <v>0.002613519403243235</v>
       </c>
-      <c r="F349" s="16" t="n">
-        <v>0.1292594426456039</v>
+      <c r="F349" s="14" t="n">
+        <v>1078</v>
+      </c>
+      <c r="G349" s="15" t="n">
+        <v>0.02063277466108467</v>
       </c>
     </row>
     <row r="350">
@@ -8241,8 +9551,11 @@
       <c r="E350" s="15" t="n">
         <v>0.002375926730221123</v>
       </c>
-      <c r="F350" s="16" t="n">
-        <v>0.09914786793838937</v>
+      <c r="F350" s="14" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G350" s="15" t="n">
+        <v>0.02168546724583388</v>
       </c>
     </row>
     <row r="351">
@@ -8261,8 +9574,11 @@
       <c r="E351" s="15" t="n">
         <v>0.001900741384176898</v>
       </c>
-      <c r="F351" s="16" t="n">
-        <v>0.0793182943507115</v>
+      <c r="F351" s="14" t="n">
+        <v>1072</v>
+      </c>
+      <c r="G351" s="15" t="n">
+        <v>0.02051793547002111</v>
       </c>
     </row>
     <row r="352">
@@ -8281,8 +9597,11 @@
       <c r="E352" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F352" s="16" t="n">
-        <v>0.02643943145023716</v>
+      <c r="F352" s="14" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G352" s="15" t="n">
+        <v>0.01915900504243576</v>
       </c>
     </row>
     <row r="353">
@@ -8301,8 +9620,11 @@
       <c r="E353" s="15" t="n">
         <v>0.00213833405719901</v>
       </c>
-      <c r="F353" s="16" t="n">
-        <v>0.1784661622891008</v>
+      <c r="F353" s="14" t="n">
+        <v>776</v>
+      </c>
+      <c r="G353" s="15" t="n">
+        <v>0.0148525353775526</v>
       </c>
     </row>
     <row r="354">
@@ -8321,8 +9643,11 @@
       <c r="E354" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F354" s="16" t="n">
-        <v>0</v>
+      <c r="F354" s="14" t="n">
+        <v>616</v>
+      </c>
+      <c r="G354" s="15" t="n">
+        <v>0.01179015694919124</v>
       </c>
     </row>
     <row r="355">
@@ -8341,8 +9666,11 @@
       <c r="E355" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F355" s="16" t="n">
-        <v>0.1057577258009487</v>
+      <c r="F355" s="14" t="n">
+        <v>579</v>
+      </c>
+      <c r="G355" s="15" t="n">
+        <v>0.01108198193763267</v>
       </c>
     </row>
     <row r="356">
@@ -8361,8 +9689,11 @@
       <c r="E356" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F356" s="16" t="n">
-        <v>0.0793182943507115</v>
+      <c r="F356" s="14" t="n">
+        <v>456</v>
+      </c>
+      <c r="G356" s="15" t="n">
+        <v>0.008727778520829876</v>
       </c>
     </row>
     <row r="357">
@@ -8381,8 +9712,11 @@
       <c r="E357" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F357" s="16" t="n">
-        <v>0.07931829435071149</v>
+      <c r="F357" s="14" t="n">
+        <v>364</v>
+      </c>
+      <c r="G357" s="15" t="n">
+        <v>0.006966910924522095</v>
       </c>
     </row>
     <row r="358">
@@ -8401,8 +9735,11 @@
       <c r="E358" s="15" t="n">
         <v>0.0009503706920884491</v>
       </c>
-      <c r="F358" s="16" t="n">
-        <v>0.181298958515912</v>
+      <c r="F358" s="14" t="n">
+        <v>273</v>
+      </c>
+      <c r="G358" s="15" t="n">
+        <v>0.005225183193391571</v>
       </c>
     </row>
     <row r="359">
@@ -8421,8 +9758,11 @@
       <c r="E359" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F359" s="16" t="n">
-        <v>0.1189774415260672</v>
+      <c r="F359" s="14" t="n">
+        <v>239</v>
+      </c>
+      <c r="G359" s="15" t="n">
+        <v>0.004574427777364782</v>
       </c>
     </row>
     <row r="360">
@@ -8441,8 +9781,11 @@
       <c r="E360" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F360" s="16" t="n">
-        <v>0.2115154516018973</v>
+      <c r="F360" s="14" t="n">
+        <v>192</v>
+      </c>
+      <c r="G360" s="15" t="n">
+        <v>0.003674854114033632</v>
       </c>
     </row>
     <row r="361">
@@ -8461,8 +9804,11 @@
       <c r="E361" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F361" s="16" t="n">
-        <v>0.1903639064417076</v>
+      <c r="F361" s="14" t="n">
+        <v>196</v>
+      </c>
+      <c r="G361" s="15" t="n">
+        <v>0.003751413574742666</v>
       </c>
     </row>
     <row r="362">
@@ -8481,8 +9827,11 @@
       <c r="E362" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F362" s="16" t="n">
-        <v>0.0793182943507115</v>
+      <c r="F362" s="14" t="n">
+        <v>151</v>
+      </c>
+      <c r="G362" s="15" t="n">
+        <v>0.002890119641766034</v>
       </c>
     </row>
     <row r="363">
@@ -8501,8 +9850,11 @@
       <c r="E363" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F363" s="16" t="n">
-        <v>0.0793182943507115</v>
+      <c r="F363" s="14" t="n">
+        <v>167</v>
+      </c>
+      <c r="G363" s="15" t="n">
+        <v>0.00319635748460217</v>
       </c>
     </row>
     <row r="364">
@@ -8521,8 +9873,11 @@
       <c r="E364" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F364" s="16" t="n">
-        <v>0.1269092709611384</v>
+      <c r="F364" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="G364" s="15" t="n">
+        <v>0.00306237842836136</v>
       </c>
     </row>
     <row r="365">
@@ -8541,8 +9896,11 @@
       <c r="E365" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F365" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F365" s="14" t="n">
+        <v>143</v>
+      </c>
+      <c r="G365" s="15" t="n">
+        <v>0.002737000720347966</v>
       </c>
     </row>
     <row r="366">
@@ -8561,8 +9919,11 @@
       <c r="E366" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F366" s="16" t="n">
-        <v>0.06345463548056919</v>
+      <c r="F366" s="14" t="n">
+        <v>136</v>
+      </c>
+      <c r="G366" s="15" t="n">
+        <v>0.002603021664107156</v>
       </c>
     </row>
     <row r="367">
@@ -8581,8 +9942,11 @@
       <c r="E367" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F367" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F367" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="G367" s="15" t="n">
+        <v>0.002909259506943292</v>
       </c>
     </row>
     <row r="368">
@@ -8601,8 +9965,11 @@
       <c r="E368" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F368" s="16" t="n">
-        <v>0</v>
+      <c r="F368" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="G368" s="15" t="n">
+        <v>0.002315923686448279</v>
       </c>
     </row>
     <row r="369">
@@ -8621,8 +9988,11 @@
       <c r="E369" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F369" s="16" t="n">
-        <v>0.1057577258009487</v>
+      <c r="F369" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="G369" s="15" t="n">
+        <v>0.002315923686448279</v>
       </c>
     </row>
     <row r="370">
@@ -8641,8 +10011,11 @@
       <c r="E370" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F370" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F370" s="14" t="n">
+        <v>114</v>
+      </c>
+      <c r="G370" s="15" t="n">
+        <v>0.002181944630207469</v>
       </c>
     </row>
     <row r="371">
@@ -8661,8 +10034,11 @@
       <c r="E371" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F371" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F371" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="G371" s="15" t="n">
+        <v>0.001741727731130524</v>
       </c>
     </row>
     <row r="372">
@@ -8681,8 +10057,11 @@
       <c r="E372" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F372" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F372" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="G372" s="15" t="n">
+        <v>0.002067105439143918</v>
       </c>
     </row>
     <row r="373">
@@ -8701,8 +10080,11 @@
       <c r="E373" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F373" s="16" t="n">
-        <v>0</v>
+      <c r="F373" s="14" t="n">
+        <v>93</v>
+      </c>
+      <c r="G373" s="15" t="n">
+        <v>0.001780007461485041</v>
       </c>
     </row>
     <row r="374">
@@ -8721,7 +10103,12 @@
       <c r="E374" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F374" s="14" t="n"/>
+      <c r="F374" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="G374" s="15" t="n">
+        <v>0.001703448000776007</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="14" t="n">
@@ -8739,8 +10126,11 @@
       <c r="E375" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F375" s="16" t="n">
-        <v>0.0793182943507115</v>
+      <c r="F375" s="14" t="n">
+        <v>87</v>
+      </c>
+      <c r="G375" s="15" t="n">
+        <v>0.00166516827042149</v>
       </c>
     </row>
     <row r="376">
@@ -8759,7 +10149,12 @@
       <c r="E376" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F376" s="14" t="n"/>
+      <c r="F376" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="G376" s="15" t="n">
+        <v>0.001626888540066973</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="14" t="n">
@@ -8777,8 +10172,11 @@
       <c r="E377" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F377" s="16" t="n">
-        <v>0</v>
+      <c r="F377" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="G377" s="15" t="n">
+        <v>0.001263231101699061</v>
       </c>
     </row>
     <row r="378">
@@ -8797,7 +10195,12 @@
       <c r="E378" s="15" t="n">
         <v>0.0007127780190663368</v>
       </c>
-      <c r="F378" s="14" t="n"/>
+      <c r="F378" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="G378" s="15" t="n">
+        <v>0.001569468944535197</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="14" t="n">
@@ -8815,8 +10218,11 @@
       <c r="E379" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F379" s="16" t="n">
-        <v>0</v>
+      <c r="F379" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="G379" s="15" t="n">
+        <v>0.001186671640990027</v>
       </c>
     </row>
     <row r="380">
@@ -8835,8 +10241,11 @@
       <c r="E380" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F380" s="16" t="n">
-        <v>0</v>
+      <c r="F380" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="G380" s="15" t="n">
+        <v>0.001244091236521803</v>
       </c>
     </row>
     <row r="381">
@@ -8855,8 +10264,11 @@
       <c r="E381" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F381" s="16" t="n">
-        <v>0</v>
+      <c r="F381" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G381" s="15" t="n">
+        <v>0.0009569932588629251</v>
       </c>
     </row>
     <row r="382">
@@ -8875,8 +10287,11 @@
       <c r="E382" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F382" s="16" t="n">
-        <v>0</v>
+      <c r="F382" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="G382" s="15" t="n">
+        <v>0.0009187135285084081</v>
       </c>
     </row>
     <row r="383">
@@ -8895,8 +10310,11 @@
       <c r="E383" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F383" s="16" t="n">
-        <v>0</v>
+      <c r="F383" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="G383" s="15" t="n">
+        <v>0.0009187135285084081</v>
       </c>
     </row>
     <row r="384">
@@ -8915,7 +10333,12 @@
       <c r="E384" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F384" s="14" t="n"/>
+      <c r="F384" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G384" s="15" t="n">
+        <v>0.0009569932588629251</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="14" t="n">
@@ -8933,8 +10356,11 @@
       <c r="E385" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F385" s="16" t="n">
-        <v>0</v>
+      <c r="F385" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="G385" s="15" t="n">
+        <v>0.0008995736633311495</v>
       </c>
     </row>
     <row r="386">
@@ -8953,8 +10379,11 @@
       <c r="E386" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F386" s="16" t="n">
-        <v>0.634546354805692</v>
+      <c r="F386" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="G386" s="15" t="n">
+        <v>0.0008038743374448571</v>
       </c>
     </row>
     <row r="387">
@@ -8973,7 +10402,12 @@
       <c r="E387" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F387" s="14" t="n"/>
+      <c r="F387" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G387" s="15" t="n">
+        <v>0.000650755416026789</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="14" t="n">
@@ -8991,7 +10425,12 @@
       <c r="E388" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F388" s="14" t="n"/>
+      <c r="F388" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G388" s="15" t="n">
+        <v>0.000650755416026789</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="14" t="n">
@@ -9009,7 +10448,12 @@
       <c r="E389" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F389" s="14" t="n"/>
+      <c r="F389" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="G389" s="15" t="n">
+        <v>0.0008804337981538911</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="14" t="n">
@@ -9027,8 +10471,11 @@
       <c r="E390" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F390" s="16" t="n">
-        <v>0</v>
+      <c r="F390" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G390" s="15" t="n">
+        <v>0.000459356764254204</v>
       </c>
     </row>
     <row r="391">
@@ -9047,7 +10494,12 @@
       <c r="E391" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F391" s="14" t="n"/>
+      <c r="F391" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G391" s="15" t="n">
+        <v>0.000459356764254204</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="14" t="n">
@@ -9065,8 +10517,11 @@
       <c r="E392" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F392" s="16" t="n">
-        <v>0</v>
+      <c r="F392" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G392" s="15" t="n">
+        <v>0.000497636494608721</v>
       </c>
     </row>
     <row r="393">
@@ -9085,8 +10540,11 @@
       <c r="E393" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F393" s="16" t="n">
-        <v>0</v>
+      <c r="F393" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G393" s="15" t="n">
+        <v>0.000497636494608721</v>
       </c>
     </row>
     <row r="394">
@@ -9105,8 +10563,11 @@
       <c r="E394" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F394" s="16" t="n">
-        <v>0</v>
+      <c r="F394" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="G394" s="15" t="n">
+        <v>0.0007464547419130816</v>
       </c>
     </row>
     <row r="395">
@@ -9125,8 +10586,11 @@
       <c r="E395" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F395" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F395" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G395" s="15" t="n">
+        <v>0.0004019371687224285</v>
       </c>
     </row>
     <row r="396">
@@ -9145,8 +10609,11 @@
       <c r="E396" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F396" s="16" t="n">
-        <v>0</v>
+      <c r="F396" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G396" s="15" t="n">
+        <v>0.0006316155508495306</v>
       </c>
     </row>
     <row r="397">
@@ -9165,7 +10632,12 @@
       <c r="E397" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F397" s="14" t="n"/>
+      <c r="F397" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G397" s="15" t="n">
+        <v>0.0003636574383679116</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="14" t="n">
@@ -9183,8 +10655,11 @@
       <c r="E398" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F398" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F398" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G398" s="15" t="n">
+        <v>0.0004402168990769455</v>
       </c>
     </row>
     <row r="399">
@@ -9203,7 +10678,12 @@
       <c r="E399" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F399" s="14" t="n"/>
+      <c r="F399" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G399" s="15" t="n">
+        <v>0.000421077033899687</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="14" t="n">
@@ -9221,8 +10701,11 @@
       <c r="E400" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F400" s="16" t="n">
-        <v>0</v>
+      <c r="F400" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G400" s="15" t="n">
+        <v>0.000421077033899687</v>
       </c>
     </row>
     <row r="401">
@@ -9241,8 +10724,11 @@
       <c r="E401" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F401" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F401" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="G401" s="15" t="n">
+        <v>0.0005167763597859796</v>
       </c>
     </row>
     <row r="402">
@@ -9261,8 +10747,11 @@
       <c r="E402" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F402" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F402" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G402" s="15" t="n">
+        <v>0.0003636574383679116</v>
       </c>
     </row>
     <row r="403">
@@ -9281,8 +10770,11 @@
       <c r="E403" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F403" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F403" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G403" s="15" t="n">
+        <v>0.000421077033899687</v>
       </c>
     </row>
     <row r="404">
@@ -9301,7 +10793,12 @@
       <c r="E404" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F404" s="14" t="n"/>
+      <c r="F404" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G404" s="15" t="n">
+        <v>0.0003253777080133945</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="14" t="n">
@@ -9319,7 +10816,12 @@
       <c r="E405" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F405" s="14" t="n"/>
+      <c r="F405" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G405" s="15" t="n">
+        <v>0.0003827973035451701</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="14" t="n">
@@ -9337,7 +10839,12 @@
       <c r="E406" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F406" s="14" t="n"/>
+      <c r="F406" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G406" s="15" t="n">
+        <v>0.000459356764254204</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="14" t="n">
@@ -9355,8 +10862,11 @@
       <c r="E407" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F407" s="16" t="n">
-        <v>0</v>
+      <c r="F407" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G407" s="15" t="n">
+        <v>0.0003827973035451701</v>
       </c>
     </row>
     <row r="408">
@@ -9375,8 +10885,11 @@
       <c r="E408" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F408" s="16" t="n">
-        <v>0</v>
+      <c r="F408" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G408" s="15" t="n">
+        <v>0.0004402168990769455</v>
       </c>
     </row>
     <row r="409">
@@ -9395,7 +10908,12 @@
       <c r="E409" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F409" s="14" t="n"/>
+      <c r="F409" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G409" s="15" t="n">
+        <v>0.000497636494608721</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="14" t="n">
@@ -9413,8 +10931,11 @@
       <c r="E410" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F410" s="16" t="n">
-        <v>0</v>
+      <c r="F410" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G410" s="15" t="n">
+        <v>0.000344517573190653</v>
       </c>
     </row>
     <row r="411">
@@ -9433,8 +10954,11 @@
       <c r="E411" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F411" s="16" t="n">
-        <v>0</v>
+      <c r="F411" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G411" s="15" t="n">
+        <v>0.000574195955317755</v>
       </c>
     </row>
     <row r="412">
@@ -9453,8 +10977,11 @@
       <c r="E412" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F412" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F412" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G412" s="15" t="n">
+        <v>0.0003827973035451701</v>
       </c>
     </row>
     <row r="413">
@@ -9473,8 +11000,11 @@
       <c r="E413" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F413" s="16" t="n">
-        <v>0</v>
+      <c r="F413" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G413" s="15" t="n">
+        <v>0.000421077033899687</v>
       </c>
     </row>
     <row r="414">
@@ -9493,8 +11023,11 @@
       <c r="E414" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F414" s="16" t="n">
-        <v>0</v>
+      <c r="F414" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G414" s="15" t="n">
+        <v>0.000421077033899687</v>
       </c>
     </row>
     <row r="415">
@@ -9513,7 +11046,12 @@
       <c r="E415" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F415" s="14" t="n"/>
+      <c r="F415" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G415" s="15" t="n">
+        <v>0.0004402168990769455</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="14" t="n">
@@ -9531,8 +11069,11 @@
       <c r="E416" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F416" s="16" t="n">
-        <v>0</v>
+      <c r="F416" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="G416" s="15" t="n">
+        <v>0.0005550560901404966</v>
       </c>
     </row>
     <row r="417">
@@ -9551,7 +11092,12 @@
       <c r="E417" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F417" s="14" t="n"/>
+      <c r="F417" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G417" s="15" t="n">
+        <v>0.0003253777080133945</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="14" t="n">
@@ -9569,7 +11115,12 @@
       <c r="E418" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F418" s="14" t="n"/>
+      <c r="F418" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G418" s="15" t="n">
+        <v>0.000267958112481619</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="14" t="n">
@@ -9587,8 +11138,11 @@
       <c r="E419" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F419" s="16" t="n">
-        <v>0</v>
+      <c r="F419" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G419" s="15" t="n">
+        <v>0.0004402168990769455</v>
       </c>
     </row>
     <row r="420">
@@ -9607,7 +11161,12 @@
       <c r="E420" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F420" s="14" t="n"/>
+      <c r="F420" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G420" s="15" t="n">
+        <v>0.000306237842836136</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="14" t="n">
@@ -9625,7 +11184,12 @@
       <c r="E421" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F421" s="14" t="n"/>
+      <c r="F421" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G421" s="15" t="n">
+        <v>0.000306237842836136</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="14" t="n">
@@ -9643,8 +11207,11 @@
       <c r="E422" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F422" s="16" t="n">
-        <v>0.1057577258009487</v>
+      <c r="F422" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G422" s="15" t="n">
+        <v>0.0004019371687224285</v>
       </c>
     </row>
     <row r="423">
@@ -9663,7 +11230,12 @@
       <c r="E423" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F423" s="14" t="n"/>
+      <c r="F423" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G423" s="15" t="n">
+        <v>0.000306237842836136</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="14" t="n">
@@ -9681,7 +11253,12 @@
       <c r="E424" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F424" s="14" t="n"/>
+      <c r="F424" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G424" s="15" t="n">
+        <v>0.0004019371687224285</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="14" t="n">
@@ -9699,8 +11276,11 @@
       <c r="E425" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F425" s="16" t="n">
-        <v>0</v>
+      <c r="F425" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="G425" s="15" t="n">
+        <v>0.0005167763597859796</v>
       </c>
     </row>
     <row r="426">
@@ -9719,7 +11299,12 @@
       <c r="E426" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F426" s="14" t="n"/>
+      <c r="F426" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G426" s="15" t="n">
+        <v>0.0004019371687224285</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="14" t="n">
@@ -9737,7 +11322,12 @@
       <c r="E427" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F427" s="14" t="n"/>
+      <c r="F427" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G427" s="15" t="n">
+        <v>0.000535916224963238</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="14" t="n">
@@ -9755,8 +11345,11 @@
       <c r="E428" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F428" s="16" t="n">
-        <v>0</v>
+      <c r="F428" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G428" s="15" t="n">
+        <v>0.0003827973035451701</v>
       </c>
     </row>
     <row r="429">
@@ -9775,8 +11368,11 @@
       <c r="E429" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F429" s="16" t="n">
-        <v>0</v>
+      <c r="F429" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G429" s="15" t="n">
+        <v>0.0003636574383679116</v>
       </c>
     </row>
     <row r="430">
@@ -9795,7 +11391,12 @@
       <c r="E430" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F430" s="14" t="n"/>
+      <c r="F430" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G430" s="15" t="n">
+        <v>0.0004784966294314625</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="14" t="n">
@@ -9813,8 +11414,11 @@
       <c r="E431" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F431" s="16" t="n">
-        <v>0</v>
+      <c r="F431" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G431" s="15" t="n">
+        <v>0.000421077033899687</v>
       </c>
     </row>
     <row r="432">
@@ -9833,8 +11437,11 @@
       <c r="E432" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F432" s="16" t="n">
-        <v>0</v>
+      <c r="F432" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G432" s="15" t="n">
+        <v>0.0004402168990769455</v>
       </c>
     </row>
     <row r="433">
@@ -9853,8 +11460,11 @@
       <c r="E433" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F433" s="16" t="n">
-        <v>0</v>
+      <c r="F433" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G433" s="15" t="n">
+        <v>0.0005933358204950136</v>
       </c>
     </row>
     <row r="434">
@@ -9873,7 +11483,12 @@
       <c r="E434" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F434" s="14" t="n"/>
+      <c r="F434" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G434" s="15" t="n">
+        <v>0.000497636494608721</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="14" t="n">
@@ -9891,8 +11506,11 @@
       <c r="E435" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F435" s="16" t="n">
-        <v>0</v>
+      <c r="F435" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G435" s="15" t="n">
+        <v>0.0004402168990769455</v>
       </c>
     </row>
     <row r="436">
@@ -9911,8 +11529,11 @@
       <c r="E436" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F436" s="16" t="n">
-        <v>0</v>
+      <c r="F436" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G436" s="15" t="n">
+        <v>0.0002105385169498435</v>
       </c>
     </row>
     <row r="437">
@@ -9931,7 +11552,12 @@
       <c r="E437" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F437" s="14" t="n"/>
+      <c r="F437" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G437" s="15" t="n">
+        <v>0.0003827973035451701</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="14" t="n">
@@ -9949,8 +11575,11 @@
       <c r="E438" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F438" s="16" t="n">
-        <v>0</v>
+      <c r="F438" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G438" s="15" t="n">
+        <v>0.000229678382127102</v>
       </c>
     </row>
     <row r="439">
@@ -9969,7 +11598,12 @@
       <c r="E439" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F439" s="14" t="n"/>
+      <c r="F439" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G439" s="15" t="n">
+        <v>0.0003827973035451701</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="14" t="n">
@@ -9987,8 +11621,11 @@
       <c r="E440" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F440" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F440" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G440" s="15" t="n">
+        <v>0.000421077033899687</v>
       </c>
     </row>
     <row r="441">
@@ -10007,7 +11644,12 @@
       <c r="E441" s="15" t="n">
         <v>0.0004751853460442246</v>
       </c>
-      <c r="F441" s="14" t="n"/>
+      <c r="F441" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G441" s="15" t="n">
+        <v>0.0003636574383679116</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="14" t="n">
@@ -10025,7 +11667,12 @@
       <c r="E442" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F442" s="14" t="n"/>
+      <c r="F442" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G442" s="15" t="n">
+        <v>0.000574195955317755</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="14" t="n">
@@ -10043,8 +11690,11 @@
       <c r="E443" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F443" s="16" t="n">
-        <v>0</v>
+      <c r="F443" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G443" s="15" t="n">
+        <v>0.000344517573190653</v>
       </c>
     </row>
     <row r="444">
@@ -10063,7 +11713,12 @@
       <c r="E444" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F444" s="14" t="n"/>
+      <c r="F444" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G444" s="15" t="n">
+        <v>0.000459356764254204</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="14" t="n">
@@ -10081,7 +11736,12 @@
       <c r="E445" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F445" s="14" t="n"/>
+      <c r="F445" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G445" s="15" t="n">
+        <v>0.0003253777080133945</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="14" t="n">
@@ -10099,7 +11759,12 @@
       <c r="E446" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F446" s="14" t="n"/>
+      <c r="F446" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G446" s="15" t="n">
+        <v>0.0003636574383679116</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="14" t="n">
@@ -10117,8 +11782,11 @@
       <c r="E447" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F447" s="16" t="n">
-        <v>0</v>
+      <c r="F447" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G447" s="15" t="n">
+        <v>0.000421077033899687</v>
       </c>
     </row>
     <row r="448">
@@ -10137,8 +11805,11 @@
       <c r="E448" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F448" s="16" t="n">
-        <v>0</v>
+      <c r="F448" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G448" s="15" t="n">
+        <v>0.000421077033899687</v>
       </c>
     </row>
     <row r="449">
@@ -10157,7 +11828,12 @@
       <c r="E449" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F449" s="14" t="n"/>
+      <c r="F449" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G449" s="15" t="n">
+        <v>0.0004019371687224285</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="14" t="n">
@@ -10175,7 +11851,12 @@
       <c r="E450" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F450" s="14" t="n"/>
+      <c r="F450" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G450" s="15" t="n">
+        <v>0.0006316155508495306</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="14" t="n">
@@ -10193,7 +11874,12 @@
       <c r="E451" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F451" s="14" t="n"/>
+      <c r="F451" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="G451" s="15" t="n">
+        <v>0.0005167763597859796</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="14" t="n">
@@ -10211,8 +11897,11 @@
       <c r="E452" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F452" s="16" t="n">
-        <v>0</v>
+      <c r="F452" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="G452" s="15" t="n">
+        <v>0.0005550560901404966</v>
       </c>
     </row>
     <row r="453">
@@ -10231,8 +11920,11 @@
       <c r="E453" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F453" s="16" t="n">
-        <v>0</v>
+      <c r="F453" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G453" s="15" t="n">
+        <v>0.0003827973035451701</v>
       </c>
     </row>
     <row r="454">
@@ -10251,7 +11943,12 @@
       <c r="E454" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F454" s="14" t="n"/>
+      <c r="F454" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G454" s="15" t="n">
+        <v>0.000497636494608721</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="14" t="n">
@@ -10269,8 +11966,11 @@
       <c r="E455" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F455" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F455" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G455" s="15" t="n">
+        <v>0.0004019371687224285</v>
       </c>
     </row>
     <row r="456">
@@ -10289,8 +11989,11 @@
       <c r="E456" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F456" s="16" t="n">
-        <v>0</v>
+      <c r="F456" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G456" s="15" t="n">
+        <v>0.0004019371687224285</v>
       </c>
     </row>
     <row r="457">
@@ -10309,7 +12012,12 @@
       <c r="E457" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F457" s="14" t="n"/>
+      <c r="F457" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G457" s="15" t="n">
+        <v>0.0003253777080133945</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="14" t="n">
@@ -10327,8 +12035,11 @@
       <c r="E458" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F458" s="16" t="n">
-        <v>0</v>
+      <c r="F458" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G458" s="15" t="n">
+        <v>0.000344517573190653</v>
       </c>
     </row>
     <row r="459">
@@ -10347,7 +12058,12 @@
       <c r="E459" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F459" s="14" t="n"/>
+      <c r="F459" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G459" s="15" t="n">
+        <v>0.000344517573190653</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="14" t="n">
@@ -10365,7 +12081,12 @@
       <c r="E460" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F460" s="14" t="n"/>
+      <c r="F460" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G460" s="15" t="n">
+        <v>0.000459356764254204</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="14" t="n">
@@ -10383,8 +12104,11 @@
       <c r="E461" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F461" s="16" t="n">
-        <v>0</v>
+      <c r="F461" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="G461" s="15" t="n">
+        <v>0.0004402168990769455</v>
       </c>
     </row>
     <row r="462">
@@ -10403,8 +12127,11 @@
       <c r="E462" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F462" s="16" t="n">
-        <v>0</v>
+      <c r="F462" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G462" s="15" t="n">
+        <v>0.0004784966294314625</v>
       </c>
     </row>
     <row r="463">
@@ -10423,7 +12150,12 @@
       <c r="E463" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F463" s="14" t="n"/>
+      <c r="F463" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G463" s="15" t="n">
+        <v>0.000421077033899687</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="14" t="n">
@@ -10441,8 +12173,11 @@
       <c r="E464" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F464" s="16" t="n">
-        <v>0</v>
+      <c r="F464" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G464" s="15" t="n">
+        <v>0.0004019371687224285</v>
       </c>
     </row>
     <row r="465">
@@ -10461,7 +12196,12 @@
       <c r="E465" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F465" s="14" t="n"/>
+      <c r="F465" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G465" s="15" t="n">
+        <v>0.0004784966294314625</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="14" t="n">
@@ -10479,7 +12219,12 @@
       <c r="E466" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F466" s="14" t="n"/>
+      <c r="F466" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G466" s="15" t="n">
+        <v>0.000344517573190653</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="14" t="n">
@@ -10497,7 +12242,12 @@
       <c r="E467" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F467" s="14" t="n"/>
+      <c r="F467" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G467" s="15" t="n">
+        <v>0.0003636574383679116</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="14" t="n">
@@ -10515,7 +12265,12 @@
       <c r="E468" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F468" s="14" t="n"/>
+      <c r="F468" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G468" s="15" t="n">
+        <v>0.000421077033899687</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="14" t="n">
@@ -10533,8 +12288,11 @@
       <c r="E469" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F469" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F469" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G469" s="15" t="n">
+        <v>0.0004019371687224285</v>
       </c>
     </row>
     <row r="470">
@@ -10553,8 +12311,11 @@
       <c r="E470" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F470" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F470" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G470" s="15" t="n">
+        <v>0.000267958112481619</v>
       </c>
     </row>
     <row r="471">
@@ -10573,8 +12334,11 @@
       <c r="E471" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F471" s="16" t="n">
-        <v>0</v>
+      <c r="F471" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G471" s="15" t="n">
+        <v>0.0004019371687224285</v>
       </c>
     </row>
     <row r="472">
@@ -10593,7 +12357,12 @@
       <c r="E472" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F472" s="14" t="n"/>
+      <c r="F472" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G472" s="15" t="n">
+        <v>0.0003636574383679116</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="14" t="n">
@@ -10611,8 +12380,11 @@
       <c r="E473" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F473" s="16" t="n">
-        <v>0</v>
+      <c r="F473" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="G473" s="15" t="n">
+        <v>0.000497636494608721</v>
       </c>
     </row>
     <row r="474">
@@ -10631,7 +12403,12 @@
       <c r="E474" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F474" s="14" t="n"/>
+      <c r="F474" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G474" s="15" t="n">
+        <v>0.0003253777080133945</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="14" t="n">
@@ -10649,8 +12426,11 @@
       <c r="E475" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F475" s="16" t="n">
-        <v>0</v>
+      <c r="F475" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G475" s="15" t="n">
+        <v>0.000344517573190653</v>
       </c>
     </row>
     <row r="476">
@@ -10669,8 +12449,11 @@
       <c r="E476" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F476" s="16" t="n">
-        <v>0</v>
+      <c r="F476" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G476" s="15" t="n">
+        <v>0.0003636574383679116</v>
       </c>
     </row>
     <row r="477">
@@ -10689,7 +12472,12 @@
       <c r="E477" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F477" s="14" t="n"/>
+      <c r="F477" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G477" s="15" t="n">
+        <v>0.000574195955317755</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="14" t="n">
@@ -10707,8 +12495,11 @@
       <c r="E478" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F478" s="16" t="n">
-        <v>0.158636588701423</v>
+      <c r="F478" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G478" s="15" t="n">
+        <v>0.0003253777080133945</v>
       </c>
     </row>
     <row r="479">
@@ -10727,7 +12518,12 @@
       <c r="E479" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F479" s="14" t="n"/>
+      <c r="F479" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="G479" s="15" t="n">
+        <v>0.0005550560901404966</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="14" t="n">
@@ -10745,8 +12541,11 @@
       <c r="E480" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F480" s="16" t="n">
-        <v>0</v>
+      <c r="F480" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="G480" s="15" t="n">
+        <v>0.0004784966294314625</v>
       </c>
     </row>
     <row r="481">
@@ -10765,7 +12564,12 @@
       <c r="E481" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F481" s="14" t="n"/>
+      <c r="F481" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G481" s="15" t="n">
+        <v>0.0003827973035451701</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="14" t="n">
@@ -10783,7 +12587,12 @@
       <c r="E482" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F482" s="14" t="n"/>
+      <c r="F482" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G482" s="15" t="n">
+        <v>0.0004019371687224285</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="14" t="n">
@@ -10801,7 +12610,12 @@
       <c r="E483" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F483" s="14" t="n"/>
+      <c r="F483" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="G483" s="15" t="n">
+        <v>0.0005550560901404966</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="14" t="n">
@@ -10819,8 +12633,11 @@
       <c r="E484" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F484" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F484" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G484" s="15" t="n">
+        <v>0.000459356764254204</v>
       </c>
     </row>
     <row r="485">
@@ -10839,7 +12656,12 @@
       <c r="E485" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F485" s="14" t="n"/>
+      <c r="F485" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G485" s="15" t="n">
+        <v>0.0004019371687224285</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="14" t="n">
@@ -10857,7 +12679,12 @@
       <c r="E486" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F486" s="14" t="n"/>
+      <c r="F486" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G486" s="15" t="n">
+        <v>0.000267958112481619</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="14" t="n">
@@ -10875,8 +12702,11 @@
       <c r="E487" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F487" s="16" t="n">
-        <v>0</v>
+      <c r="F487" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G487" s="15" t="n">
+        <v>0.000421077033899687</v>
       </c>
     </row>
     <row r="488">
@@ -10895,7 +12725,12 @@
       <c r="E488" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F488" s="14" t="n"/>
+      <c r="F488" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="G488" s="15" t="n">
+        <v>0.0002105385169498435</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="14" t="n">
@@ -10913,7 +12748,12 @@
       <c r="E489" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F489" s="14" t="n"/>
+      <c r="F489" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G489" s="15" t="n">
+        <v>0.0003253777080133945</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="14" t="n">
@@ -10931,7 +12771,12 @@
       <c r="E490" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F490" s="14" t="n"/>
+      <c r="F490" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="G490" s="15" t="n">
+        <v>0.0005167763597859796</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="14" t="n">
@@ -10949,8 +12794,11 @@
       <c r="E491" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F491" s="16" t="n">
-        <v>0</v>
+      <c r="F491" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G491" s="15" t="n">
+        <v>0.0003253777080133945</v>
       </c>
     </row>
     <row r="492">
@@ -10969,7 +12817,12 @@
       <c r="E492" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F492" s="14" t="n"/>
+      <c r="F492" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G492" s="15" t="n">
+        <v>0.000306237842836136</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="14" t="n">
@@ -10987,8 +12840,11 @@
       <c r="E493" s="15" t="n">
         <v>0.0002375926730221123</v>
       </c>
-      <c r="F493" s="16" t="n">
-        <v>0.317273177402846</v>
+      <c r="F493" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G493" s="15" t="n">
+        <v>0.000344517573190653</v>
       </c>
     </row>
     <row r="494">
@@ -11007,8 +12863,11 @@
       <c r="E494" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F494" s="16" t="n">
-        <v>0</v>
+      <c r="F494" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G494" s="15" t="n">
+        <v>0.000344517573190653</v>
       </c>
     </row>
     <row r="495">
@@ -11027,8 +12886,11 @@
       <c r="E495" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F495" s="16" t="n">
-        <v>0</v>
+      <c r="F495" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="G495" s="15" t="n">
+        <v>0.0005550560901404966</v>
       </c>
     </row>
     <row r="496">
@@ -11047,7 +12909,12 @@
       <c r="E496" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F496" s="14" t="n"/>
+      <c r="F496" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G496" s="15" t="n">
+        <v>0.000421077033899687</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="14" t="n">
@@ -11065,7 +12932,12 @@
       <c r="E497" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F497" s="14" t="n"/>
+      <c r="F497" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G497" s="15" t="n">
+        <v>0.000306237842836136</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="14" t="n">
@@ -11083,7 +12955,12 @@
       <c r="E498" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F498" s="14" t="n"/>
+      <c r="F498" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G498" s="15" t="n">
+        <v>0.0003253777080133945</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="14" t="n">
@@ -11101,8 +12978,11 @@
       <c r="E499" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F499" s="16" t="n">
-        <v>0</v>
+      <c r="F499" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G499" s="15" t="n">
+        <v>0.0003253777080133945</v>
       </c>
     </row>
     <row r="500">
@@ -11121,8 +13001,11 @@
       <c r="E500" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F500" s="16" t="n">
-        <v>0</v>
+      <c r="F500" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G500" s="15" t="n">
+        <v>0.000306237842836136</v>
       </c>
     </row>
     <row r="501">
@@ -11141,8 +13024,11 @@
       <c r="E501" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F501" s="16" t="n">
-        <v>0</v>
+      <c r="F501" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="G501" s="15" t="n">
+        <v>0.0004019371687224285</v>
       </c>
     </row>
     <row r="502">
@@ -11161,7 +13047,12 @@
       <c r="E502" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F502" s="14" t="n"/>
+      <c r="F502" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G502" s="15" t="n">
+        <v>0.000344517573190653</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="14" t="n">
@@ -11179,7 +13070,12 @@
       <c r="E503" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F503" s="14" t="n"/>
+      <c r="F503" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G503" s="15" t="n">
+        <v>0.0001722587865953265</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="14" t="n">
@@ -11197,7 +13093,12 @@
       <c r="E504" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F504" s="14" t="n"/>
+      <c r="F504" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G504" s="15" t="n">
+        <v>0.0002870979776588775</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="14" t="n">
@@ -11215,7 +13116,12 @@
       <c r="E505" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F505" s="14" t="n"/>
+      <c r="F505" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G505" s="15" t="n">
+        <v>0.0003253777080133945</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="14" t="n">
@@ -11233,8 +13139,11 @@
       <c r="E506" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F506" s="16" t="n">
-        <v>0</v>
+      <c r="F506" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G506" s="15" t="n">
+        <v>0.000344517573190653</v>
       </c>
     </row>
     <row r="507">
@@ -11253,8 +13162,11 @@
       <c r="E507" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F507" s="16" t="n">
-        <v>0</v>
+      <c r="F507" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G507" s="15" t="n">
+        <v>0.000267958112481619</v>
       </c>
     </row>
     <row r="508">
@@ -11273,7 +13185,12 @@
       <c r="E508" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F508" s="14" t="n"/>
+      <c r="F508" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="G508" s="15" t="n">
+        <v>0.0001722587865953265</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="14" t="n">
@@ -11291,7 +13208,12 @@
       <c r="E509" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F509" s="14" t="n"/>
+      <c r="F509" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="G509" s="15" t="n">
+        <v>0.000267958112481619</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="14" t="n">
@@ -11309,8 +13231,11 @@
       <c r="E510" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F510" s="16" t="n">
-        <v>0</v>
+      <c r="F510" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G510" s="15" t="n">
+        <v>0.000229678382127102</v>
       </c>
     </row>
     <row r="511">
@@ -11329,7 +13254,12 @@
       <c r="E511" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F511" s="14" t="n"/>
+      <c r="F511" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G511" s="15" t="n">
+        <v>0.0003253777080133945</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="14" t="n">
@@ -11347,7 +13277,12 @@
       <c r="E512" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F512" s="14" t="n"/>
+      <c r="F512" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G512" s="15" t="n">
+        <v>0.000153118921418068</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="14" t="n">
@@ -11365,10 +13300,15 @@
       <c r="E513" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F513" s="14" t="n"/>
+      <c r="F513" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G513" s="15" t="n">
+        <v>9.569932588629251e-05</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F513"/>
+  <autoFilter ref="A1:G513"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11379,21 +13319,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>チャンネル帯ごとのカウントと計数率</t>
         </is>
@@ -11437,7 +13379,17 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>計数率比</t>
+          <t>管理棟2階_0819 カウント</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>管理棟2階_0819 [s⁻¹]</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>管理棟2階_0819 [%]</t>
         </is>
       </c>
     </row>
@@ -11453,7 +13405,7 @@
       <c r="C4" s="11" t="n">
         <v>32.21588688045075</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>49.28794839774068</v>
       </c>
       <c r="E4" s="5" t="n">
@@ -11462,11 +13414,17 @@
       <c r="F4" s="11" t="n">
         <v>34.94322960670809</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="9" t="n">
         <v>48.6717785624696</v>
       </c>
-      <c r="H4" s="11" t="n">
-        <v>1.084658315829646</v>
+      <c r="H4" s="5" t="n">
+        <v>1719691</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>32.91465388654485</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>49.26829170465113</v>
       </c>
     </row>
     <row r="5">
@@ -11481,7 +13439,7 @@
       <c r="C5" s="11" t="n">
         <v>25.52259081030968</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>39.04769542751738</v>
       </c>
       <c r="E5" s="5" t="n">
@@ -11490,11 +13448,17 @@
       <c r="F5" s="11" t="n">
         <v>27.82471553029259</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="9" t="n">
         <v>38.75653189750174</v>
       </c>
-      <c r="H5" s="11" t="n">
-        <v>1.090199491779376</v>
+      <c r="H5" s="5" t="n">
+        <v>1355084</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>25.93612506386016</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>38.82248252523591</v>
       </c>
     </row>
     <row r="6">
@@ -11509,7 +13473,7 @@
       <c r="C6" s="11" t="n">
         <v>6.855798335437625</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>10.48886953931464</v>
       </c>
       <c r="E6" s="5" t="n">
@@ -11518,39 +13482,51 @@
       <c r="F6" s="11" t="n">
         <v>8.92326802069147</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="9" t="n">
         <v>12.42905507146616</v>
       </c>
-      <c r="H6" s="11" t="n">
-        <v>1.30156512547446</v>
+      <c r="H6" s="5" t="n">
+        <v>374121</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>7.160625499981128</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>10.71838054675857</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>ch150–450（ROI）</t>
+          <t>自動ROI</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>993</v>
+        <v>759</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.7436163568639609</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>1.137678585749802</v>
+        <v>0.5683834993552329</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.8695851425821752</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>423</v>
+        <v>328</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1005017006883535</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>0.1399869610253797</v>
-      </c>
-      <c r="H7" s="11" t="n">
-        <v>0.1351526223981912</v>
+        <v>0.07793039675125282</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>0.1085478090220438</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>31342</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0.599881654385636</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.8979327091943703</v>
       </c>
     </row>
     <row r="8">
@@ -11565,7 +13541,7 @@
       <c r="C8" s="11" t="n">
         <v>0.02471232605892317</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>0.03780804967748588</v>
       </c>
       <c r="E8" s="5" t="n">
@@ -11574,11 +13550,17 @@
       <c r="F8" s="11" t="n">
         <v>0.001900741384176898</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="9" t="n">
         <v>0.00264750753712302</v>
       </c>
-      <c r="H8" s="11" t="n">
-        <v>0.07691470967341721</v>
+      <c r="H8" s="5" t="n">
+        <v>1165</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>0.02229794293150615</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.03337667048087044</v>
       </c>
     </row>
     <row r="9">
@@ -11593,7 +13575,7 @@
       <c r="C9" s="11" t="n">
         <v>65.36260470912094</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>100</v>
       </c>
       <c r="E9" s="5" t="n">
@@ -11602,44 +13584,56 @@
       <c r="F9" s="11" t="n">
         <v>71.79361559976469</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="H9" s="11" t="n">
-        <v>1.098389758475252</v>
+      <c r="H9" s="5" t="n">
+        <v>3490462</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>66.80697208634406</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>ch0除く</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
+      <c r="B10" s="18" t="n">
         <v>44263</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="19" t="n">
         <v>33.14671782867019</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="20" t="n">
         <v>50.71205160225932</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <v>155099</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <v>36.85038599305659</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="20" t="n">
         <v>51.3282214375304</v>
       </c>
-      <c r="H10" s="20" t="n">
-        <v>1.111735592752502</v>
+      <c r="H10" s="18" t="n">
+        <v>1770771</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>33.89231819979921</v>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>50.73170829534887</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/03_今年度用/測定_20260818/測定_20260818_MCA.xlsx
+++ b/03_今年度用/測定_20260818/測定_20260818_MCA.xlsx
@@ -12,7 +12,7 @@
     <sheet name="チャンネル帯" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'スペクトル'!$A$1:$G$513</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'スペクトル'!$A$1:$I$513</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -350,6 +350,39 @@
             </numRef>
           </yVal>
         </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>管理棟1階_0819</v>
+          </tx>
+          <spPr>
+            <a:ln w="15000">
+              <a:solidFill>
+                <a:srgbClr val="9467BD"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'スペクトル'!$A$3:$A$82</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'スペクトル'!$I$3:$I$82</f>
+            </numRef>
+          </yVal>
+        </ser>
         <axId val="10"/>
         <axId val="20"/>
       </scatterChart>
@@ -576,6 +609,39 @@
           <yVal>
             <numRef>
               <f>'スペクトル'!$G$2:$G$513</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>管理棟1階_0819</v>
+          </tx>
+          <spPr>
+            <a:ln w="12000">
+              <a:solidFill>
+                <a:srgbClr val="9467BD"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'スペクトル'!$A$2:$A$513</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'スペクトル'!$I$2:$I$513</f>
             </numRef>
           </yVal>
         </ser>
@@ -1035,6 +1101,7 @@
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1072,6 +1139,11 @@
           <t>管理棟2階_0819</t>
         </is>
       </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>管理棟1階_0819</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1094,6 +1166,11 @@
           <t>2026-08-18〜08-19</t>
         </is>
       </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1116,6 +1193,11 @@
           <t>管理棟2階_0819</t>
         </is>
       </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>管理棟1階_0819</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1138,6 +1220,11 @@
           <t>08/18/2026 18:00:44</t>
         </is>
       </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>08/19/2026 08:52:40</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1154,6 +1241,9 @@
       <c r="D8" s="8" t="n">
         <v>52246.972</v>
       </c>
+      <c r="E8" s="8" t="n">
+        <v>17482.328</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1170,6 +1260,9 @@
       <c r="D9" s="9" t="n">
         <v>52300.335</v>
       </c>
+      <c r="E9" s="9" t="n">
+        <v>17499.746</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1186,6 +1279,9 @@
       <c r="D10" s="10" t="n">
         <v>0.1020318512300111</v>
       </c>
+      <c r="E10" s="10" t="n">
+        <v>0.09953287321997628</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1202,6 +1298,9 @@
       <c r="D11" s="5" t="n">
         <v>3490462</v>
       </c>
+      <c r="E11" s="5" t="n">
+        <v>1131721</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1218,6 +1317,9 @@
       <c r="D12" s="10" t="n">
         <v>66.80697208634406</v>
       </c>
+      <c r="E12" s="10" t="n">
+        <v>64.73514282537199</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1234,6 +1336,9 @@
       <c r="D13" s="11" t="n">
         <v>33.89231819979921</v>
       </c>
+      <c r="E13" s="11" t="n">
+        <v>32.95333436141914</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1256,6 +1361,11 @@
           <t>314–366</t>
         </is>
       </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>313–366</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1272,6 +1382,9 @@
       <c r="D15" s="5" t="n">
         <v>342</v>
       </c>
+      <c r="E15" s="5" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1288,6 +1401,9 @@
       <c r="D16" s="12" t="n">
         <v>0.599881654385636</v>
       </c>
+      <c r="E16" s="12" t="n">
+        <v>0.4334662980811251</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1304,6 +1420,9 @@
       <c r="D17" s="11" t="n">
         <v>25.93612506386016</v>
       </c>
+      <c r="E17" s="11" t="n">
+        <v>25.23371029304564</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1320,6 +1439,9 @@
       <c r="D18" s="7" t="n">
         <v>6</v>
       </c>
+      <c r="E18" s="7" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1342,6 +1464,11 @@
           <t>MCA8000D</t>
         </is>
       </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>MCA8000D</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1358,6 +1485,9 @@
       <c r="D20" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="E20" s="7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1374,6 +1504,9 @@
       <c r="D21" s="5" t="n">
         <v>42</v>
       </c>
+      <c r="E21" s="5" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1396,6 +1529,11 @@
           <t>管理棟2階_0819.mca</t>
         </is>
       </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>管理棟1階_0819.mca</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1416,6 +1554,11 @@
       <c r="D23" s="5" t="inlineStr">
         <is>
           <t>終夜（18:00開始）。ROIは自動抽出。</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>管理棟1階（08:52開始）。ROIは自動抽出。</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G513"/>
+  <dimension ref="A1:I513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1492,6 +1635,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1530,6 +1675,16 @@
           <t>cps_kanri2f_0819</t>
         </is>
       </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>counts_kanri1f_0819</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>cps_kanri1f_0819</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="14" t="n">
@@ -1553,6 +1708,12 @@
       <c r="G2" s="15" t="n">
         <v>32.91465388654485</v>
       </c>
+      <c r="H2" s="14" t="n">
+        <v>555620</v>
+      </c>
+      <c r="I2" s="15" t="n">
+        <v>31.78180846395285</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
@@ -1575,6 +1736,12 @@
       </c>
       <c r="G3" s="15" t="n">
         <v>0.002890119641766034</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="I3" s="15" t="n">
+        <v>0.002631228518307173</v>
       </c>
     </row>
     <row r="4">
@@ -1599,6 +1766,12 @@
       <c r="G4" s="15" t="n">
         <v>0.001512049349003422</v>
       </c>
+      <c r="H4" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="I4" s="15" t="n">
+        <v>0.001258413639190387</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
@@ -1622,6 +1795,12 @@
       <c r="G5" s="15" t="n">
         <v>0.001378070292762612</v>
       </c>
+      <c r="H5" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>0.0008580092994479911</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n">
@@ -1645,6 +1824,12 @@
       <c r="G6" s="15" t="n">
         <v>0.000689035146381306</v>
       </c>
+      <c r="H6" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -1668,6 +1853,12 @@
       <c r="G7" s="15" t="n">
         <v>3.448161550874183</v>
       </c>
+      <c r="H7" s="14" t="n">
+        <v>59628</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>3.410758567165654</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="n">
@@ -1691,6 +1882,12 @@
       <c r="G8" s="15" t="n">
         <v>4.809178223763857</v>
       </c>
+      <c r="H8" s="14" t="n">
+        <v>81168</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>4.64285992117297</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
@@ -1714,6 +1911,12 @@
       <c r="G9" s="15" t="n">
         <v>3.74161396377191</v>
       </c>
+      <c r="H9" s="14" t="n">
+        <v>62215</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>3.558736571010451</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="n">
@@ -1737,6 +1940,12 @@
       <c r="G10" s="15" t="n">
         <v>2.545123571945949</v>
       </c>
+      <c r="H10" s="14" t="n">
+        <v>42414</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>2.42610709511914</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
@@ -1760,6 +1969,12 @@
       <c r="G11" s="15" t="n">
         <v>1.833522524520655</v>
       </c>
+      <c r="H11" s="14" t="n">
+        <v>30896</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>1.767270354383009</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n">
@@ -1783,6 +1998,12 @@
       <c r="G12" s="15" t="n">
         <v>1.470343582782175</v>
       </c>
+      <c r="H12" s="14" t="n">
+        <v>24850</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>1.421435406085505</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
@@ -1806,6 +2027,12 @@
       <c r="G13" s="15" t="n">
         <v>1.246789957511796</v>
       </c>
+      <c r="H13" s="14" t="n">
+        <v>21423</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>1.225408881471621</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="n">
@@ -1829,6 +2056,12 @@
       <c r="G14" s="15" t="n">
         <v>1.092139846879547</v>
       </c>
+      <c r="H14" s="14" t="n">
+        <v>18771</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>1.073712837329216</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n">
@@ -1852,6 +2085,12 @@
       <c r="G15" s="15" t="n">
         <v>0.9682857793175076</v>
       </c>
+      <c r="H15" s="14" t="n">
+        <v>16688</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>0.9545639459458717</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="n">
@@ -1875,6 +2114,12 @@
       <c r="G16" s="15" t="n">
         <v>0.8667679344173285</v>
       </c>
+      <c r="H16" s="14" t="n">
+        <v>15200</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>0.8694494234406309</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n">
@@ -1898,6 +2143,12 @@
       <c r="G17" s="15" t="n">
         <v>0.7935770899794919</v>
       </c>
+      <c r="H17" s="14" t="n">
+        <v>13736</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>0.785707715814507</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="n">
@@ -1921,6 +2172,12 @@
       <c r="G18" s="15" t="n">
         <v>0.7178980630686119</v>
       </c>
+      <c r="H18" s="14" t="n">
+        <v>12714</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>0.7272486822121172</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n">
@@ -1944,6 +2201,12 @@
       <c r="G19" s="15" t="n">
         <v>0.6696081832263887</v>
       </c>
+      <c r="H19" s="14" t="n">
+        <v>11430</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>0.6538030861793692</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="n">
@@ -1967,6 +2230,12 @@
       <c r="G20" s="15" t="n">
         <v>0.6087816916930612</v>
       </c>
+      <c r="H20" s="14" t="n">
+        <v>10601</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>0.6063837722298769</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n">
@@ -1990,6 +2259,12 @@
       <c r="G21" s="15" t="n">
         <v>0.5763970398131397</v>
       </c>
+      <c r="H21" s="14" t="n">
+        <v>10034</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>0.5739510207107428</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="n">
@@ -2013,6 +2288,12 @@
       <c r="G22" s="15" t="n">
         <v>0.541466785864643</v>
       </c>
+      <c r="H22" s="14" t="n">
+        <v>9280</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>0.5308217532584905</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n">
@@ -2036,6 +2317,12 @@
       <c r="G23" s="15" t="n">
         <v>0.4983638094854569</v>
       </c>
+      <c r="H23" s="14" t="n">
+        <v>8681</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>0.496558581900534</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="n">
@@ -2059,6 +2346,12 @@
       <c r="G24" s="15" t="n">
         <v>0.4656920596278766</v>
       </c>
+      <c r="H24" s="14" t="n">
+        <v>8067</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>0.4614374012431296</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
@@ -2082,6 +2375,12 @@
       <c r="G25" s="15" t="n">
         <v>0.4358530098165306</v>
       </c>
+      <c r="H25" s="14" t="n">
+        <v>7456</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>0.4264878224456148</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="n">
@@ -2105,6 +2404,12 @@
       <c r="G26" s="15" t="n">
         <v>0.4120238776708438</v>
       </c>
+      <c r="H26" s="14" t="n">
+        <v>7112</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>0.4068108091782742</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
@@ -2128,6 +2433,12 @@
       <c r="G27" s="15" t="n">
         <v>0.3868549549627489</v>
       </c>
+      <c r="H27" s="14" t="n">
+        <v>6757</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>0.3865045890913384</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="n">
@@ -2151,6 +2462,12 @@
       <c r="G28" s="15" t="n">
         <v>0.3687103627747078</v>
       </c>
+      <c r="H28" s="14" t="n">
+        <v>6451</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>0.3690011993825993</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
@@ -2174,6 +2491,12 @@
       <c r="G29" s="15" t="n">
         <v>0.3426035866729272</v>
       </c>
+      <c r="H29" s="14" t="n">
+        <v>6152</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>0.3518982140136027</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="n">
@@ -2197,6 +2520,12 @@
       <c r="G30" s="15" t="n">
         <v>0.3286314850935285</v>
       </c>
+      <c r="H30" s="14" t="n">
+        <v>5683</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>0.3250711232508622</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
@@ -2220,6 +2549,12 @@
       <c r="G31" s="15" t="n">
         <v>0.3130324949740628</v>
       </c>
+      <c r="H31" s="14" t="n">
+        <v>5304</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>0.3033920882848096</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="n">
@@ -2243,6 +2578,12 @@
       <c r="G32" s="15" t="n">
         <v>0.2902560554131252</v>
       </c>
+      <c r="H32" s="14" t="n">
+        <v>5170</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>0.2957272052097409</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="n">
@@ -2266,6 +2607,12 @@
       <c r="G33" s="15" t="n">
         <v>0.2730110368884153</v>
       </c>
+      <c r="H33" s="14" t="n">
+        <v>4734</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>0.270787734905786</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="n">
@@ -2289,6 +2636,12 @@
       <c r="G34" s="15" t="n">
         <v>0.2519571851934309</v>
       </c>
+      <c r="H34" s="14" t="n">
+        <v>4587</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>0.2623792437711956</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n">
@@ -2312,6 +2665,12 @@
       <c r="G35" s="15" t="n">
         <v>0.2306162355207877</v>
       </c>
+      <c r="H35" s="14" t="n">
+        <v>4113</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>0.2352661499086391</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="n">
@@ -2335,6 +2694,12 @@
       <c r="G36" s="15" t="n">
         <v>0.2118400277818971</v>
       </c>
+      <c r="H36" s="14" t="n">
+        <v>3704</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>0.2118710963436906</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n">
@@ -2358,6 +2723,12 @@
       <c r="G37" s="15" t="n">
         <v>0.1939442538411604</v>
       </c>
+      <c r="H37" s="14" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>0.194482107874878</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="n">
@@ -2381,6 +2752,12 @@
       <c r="G38" s="15" t="n">
         <v>0.1789768792725442</v>
       </c>
+      <c r="H38" s="14" t="n">
+        <v>3187</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>0.1822983758227165</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="n">
@@ -2404,6 +2781,12 @@
       <c r="G39" s="15" t="n">
         <v>0.1657320925698814</v>
       </c>
+      <c r="H39" s="14" t="n">
+        <v>2843</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>0.1626213625553759</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n">
@@ -2427,6 +2810,12 @@
       <c r="G40" s="15" t="n">
         <v>0.1501331024504157</v>
       </c>
+      <c r="H40" s="14" t="n">
+        <v>2702</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>0.1545560751405648</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="n">
@@ -2450,6 +2839,12 @@
       <c r="G41" s="15" t="n">
         <v>0.1394721975466827</v>
       </c>
+      <c r="H41" s="14" t="n">
+        <v>2339</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>0.1337922500939234</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="n">
@@ -2473,6 +2868,12 @@
       <c r="G42" s="15" t="n">
         <v>0.1276820405974915</v>
       </c>
+      <c r="H42" s="14" t="n">
+        <v>2261</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>0.1293306017367939</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="n">
@@ -2496,6 +2897,12 @@
       <c r="G43" s="15" t="n">
         <v>0.1145138133555376</v>
       </c>
+      <c r="H43" s="14" t="n">
+        <v>2085</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>0.1192632926232708</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="n">
@@ -2519,6 +2926,12 @@
       <c r="G44" s="15" t="n">
         <v>0.1056137760481124</v>
       </c>
+      <c r="H44" s="14" t="n">
+        <v>1839</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>0.1051919401123237</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="n">
@@ -2542,6 +2955,12 @@
       <c r="G45" s="15" t="n">
         <v>0.0960247035943059</v>
       </c>
+      <c r="H45" s="14" t="n">
+        <v>1682</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>0.0962114427781014</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="n">
@@ -2565,6 +2984,12 @@
       <c r="G46" s="15" t="n">
         <v>0.08750746359042587</v>
       </c>
+      <c r="H46" s="14" t="n">
+        <v>1491</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>0.08528612436513031</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="n">
@@ -2588,6 +3013,12 @@
       <c r="G47" s="15" t="n">
         <v>0.08011947563200408</v>
       </c>
+      <c r="H47" s="14" t="n">
+        <v>1483</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>0.08482851940542471</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="n">
@@ -2611,6 +3042,12 @@
       <c r="G48" s="15" t="n">
         <v>0.0761001039447798</v>
       </c>
+      <c r="H48" s="14" t="n">
+        <v>1308</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>0.07481841091186482</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="n">
@@ -2634,6 +3071,12 @@
       <c r="G49" s="15" t="n">
         <v>0.06785082205338139</v>
       </c>
+      <c r="H49" s="14" t="n">
+        <v>1231</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>0.07041396317469847</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="n">
@@ -2657,6 +3100,12 @@
       <c r="G50" s="15" t="n">
         <v>0.06260649899481256</v>
       </c>
+      <c r="H50" s="14" t="n">
+        <v>1052</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>0.06017505220128577</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="n">
@@ -2680,6 +3129,12 @@
       <c r="G51" s="15" t="n">
         <v>0.05709421782376211</v>
       </c>
+      <c r="H51" s="14" t="n">
+        <v>984</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>0.05628541004378822</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="n">
@@ -2703,6 +3158,12 @@
       <c r="G52" s="15" t="n">
         <v>0.05276860829370169</v>
       </c>
+      <c r="H52" s="14" t="n">
+        <v>901</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>0.05153775858684266</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="n">
@@ -2726,6 +3187,12 @@
       <c r="G53" s="15" t="n">
         <v>0.04932343256179516</v>
       </c>
+      <c r="H53" s="14" t="n">
+        <v>818</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>0.04679010712989711</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="n">
@@ -2749,6 +3216,12 @@
       <c r="G54" s="15" t="n">
         <v>0.04212684325514596</v>
       </c>
+      <c r="H54" s="14" t="n">
+        <v>759</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>0.04341527055206835</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="n">
@@ -2772,6 +3245,12 @@
       <c r="G55" s="15" t="n">
         <v>0.03919844388302541</v>
       </c>
+      <c r="H55" s="14" t="n">
+        <v>723</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>0.04135604823339317</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="n">
@@ -2795,6 +3274,12 @@
       <c r="G56" s="15" t="n">
         <v>0.03674854114033632</v>
       </c>
+      <c r="H56" s="14" t="n">
+        <v>627</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>0.03586478871692603</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="n">
@@ -2818,6 +3303,12 @@
       <c r="G57" s="15" t="n">
         <v>0.03309282689147995</v>
       </c>
+      <c r="H57" s="14" t="n">
+        <v>587</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>0.03357676391839805</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="n">
@@ -2841,6 +3332,12 @@
       <c r="G58" s="15" t="n">
         <v>0.03012614778900488</v>
       </c>
+      <c r="H58" s="14" t="n">
+        <v>492</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>0.02814270502189411</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="n">
@@ -2864,6 +3361,12 @@
       <c r="G59" s="15" t="n">
         <v>0.02660441259638932</v>
       </c>
+      <c r="H59" s="14" t="n">
+        <v>461</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>0.02636948580303492</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="n">
@@ -2887,6 +3390,12 @@
       <c r="G60" s="15" t="n">
         <v>0.02505408351703138</v>
       </c>
+      <c r="H60" s="14" t="n">
+        <v>413</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>0.02362385604480136</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="14" t="n">
@@ -2910,6 +3419,12 @@
       <c r="G61" s="15" t="n">
         <v>0.02302525780824198</v>
       </c>
+      <c r="H61" s="14" t="n">
+        <v>403</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>0.02305184984516936</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="n">
@@ -2933,6 +3448,12 @@
       <c r="G62" s="15" t="n">
         <v>0.0207093341217937</v>
       </c>
+      <c r="H62" s="14" t="n">
+        <v>385</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>0.02202223868583177</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="n">
@@ -2956,6 +3477,12 @@
       <c r="G63" s="15" t="n">
         <v>0.01889104692995414</v>
       </c>
+      <c r="H63" s="14" t="n">
+        <v>338</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>0.0193338095475614</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="n">
@@ -2979,6 +3506,12 @@
       <c r="G64" s="15" t="n">
         <v>0.01611576647925166</v>
       </c>
+      <c r="H64" s="14" t="n">
+        <v>285</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>0.01630217668951183</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="n">
@@ -3002,6 +3535,12 @@
       <c r="G65" s="15" t="n">
         <v>0.01580952863641552</v>
       </c>
+      <c r="H65" s="14" t="n">
+        <v>281</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>0.01607337420965903</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="n">
@@ -3025,6 +3564,12 @@
       <c r="G66" s="15" t="n">
         <v>0.01366586373656257</v>
       </c>
+      <c r="H66" s="14" t="n">
+        <v>273</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>0.01561576924995344</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="14" t="n">
@@ -3048,6 +3593,12 @@
       <c r="G67" s="15" t="n">
         <v>0.01224951371344544</v>
       </c>
+      <c r="H67" s="14" t="n">
+        <v>238</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>0.01361374755124146</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="n">
@@ -3071,6 +3622,12 @@
       <c r="G68" s="15" t="n">
         <v>0.01134994005011429</v>
       </c>
+      <c r="H68" s="14" t="n">
+        <v>194</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <v>0.01109692027286069</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="14" t="n">
@@ -3094,6 +3651,12 @@
       <c r="G69" s="15" t="n">
         <v>0.01106284207245541</v>
       </c>
+      <c r="H69" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>0.009152099194111904</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="n">
@@ -3117,6 +3680,12 @@
       <c r="G70" s="15" t="n">
         <v>0.009818750835933612</v>
       </c>
+      <c r="H70" s="14" t="n">
+        <v>169</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>0.0096669047737807</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="14" t="n">
@@ -3140,6 +3709,12 @@
       <c r="G71" s="15" t="n">
         <v>0.008861757577070686</v>
       </c>
+      <c r="H71" s="14" t="n">
+        <v>164</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>0.009380901673964702</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="n">
@@ -3163,6 +3738,12 @@
       <c r="G72" s="15" t="n">
         <v>0.008134442700334863</v>
       </c>
+      <c r="H72" s="14" t="n">
+        <v>137</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>0.007836484934958319</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="14" t="n">
@@ -3186,6 +3767,12 @@
       <c r="G73" s="15" t="n">
         <v>0.007426267688776298</v>
       </c>
+      <c r="H73" s="14" t="n">
+        <v>146</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>0.008351290514627113</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="n">
@@ -3209,6 +3796,12 @@
       <c r="G74" s="15" t="n">
         <v>0.0066415332165087</v>
       </c>
+      <c r="H74" s="14" t="n">
+        <v>98</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <v>0.005605660756393542</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="n">
@@ -3232,6 +3825,12 @@
       <c r="G75" s="15" t="n">
         <v>0.005474001440695931</v>
       </c>
+      <c r="H75" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="I75" s="15" t="n">
+        <v>0.006635271915731131</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="n">
@@ -3255,6 +3854,12 @@
       <c r="G76" s="15" t="n">
         <v>0.005722819688000292</v>
       </c>
+      <c r="H76" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="I76" s="15" t="n">
+        <v>0.004862052696871949</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="14" t="n">
@@ -3278,6 +3883,12 @@
       <c r="G77" s="15" t="n">
         <v>0.005072064271973503</v>
       </c>
+      <c r="H77" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <v>0.005662861376356741</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="n">
@@ -3301,6 +3912,12 @@
       <c r="G78" s="15" t="n">
         <v>0.004708406833605592</v>
       </c>
+      <c r="H78" s="14" t="n">
+        <v>93</v>
+      </c>
+      <c r="I78" s="15" t="n">
+        <v>0.005319657656577544</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="14" t="n">
@@ -3324,6 +3941,12 @@
       <c r="G79" s="15" t="n">
         <v>0.003713133844388149</v>
       </c>
+      <c r="H79" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="I79" s="15" t="n">
+        <v>0.00388964215749756</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="n">
@@ -3347,6 +3970,12 @@
       <c r="G80" s="15" t="n">
         <v>0.004076791282756061</v>
       </c>
+      <c r="H80" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="I80" s="15" t="n">
+        <v>0.004404447737166355</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="n">
@@ -3370,6 +3999,12 @@
       <c r="G81" s="15" t="n">
         <v>0.003636574383679115</v>
       </c>
+      <c r="H81" s="14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I81" s="15" t="n">
+        <v>0.003374836577828765</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="n">
@@ -3393,6 +4028,12 @@
       <c r="G82" s="15" t="n">
         <v>0.003215497349779428</v>
       </c>
+      <c r="H82" s="14" t="n">
+        <v>67</v>
+      </c>
+      <c r="I82" s="15" t="n">
+        <v>0.00383244153753436</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="14" t="n">
@@ -3416,6 +4057,12 @@
       <c r="G83" s="15" t="n">
         <v>0.002909259506943292</v>
       </c>
+      <c r="H83" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="I83" s="15" t="n">
+        <v>0.003317635957865565</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="n">
@@ -3439,6 +4086,12 @@
       <c r="G84" s="15" t="n">
         <v>0.003043238563184102</v>
       </c>
+      <c r="H84" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="I84" s="15" t="n">
+        <v>0.002345225418491176</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="14" t="n">
@@ -3462,6 +4115,12 @@
       <c r="G85" s="15" t="n">
         <v>0.002775280450702483</v>
       </c>
+      <c r="H85" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I85" s="15" t="n">
+        <v>0.002288024798527976</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="n">
@@ -3485,6 +4144,12 @@
       <c r="G86" s="15" t="n">
         <v>0.002603021664107156</v>
       </c>
+      <c r="H86" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="I86" s="15" t="n">
+        <v>0.002516827278380774</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="14" t="n">
@@ -3508,6 +4173,12 @@
       <c r="G87" s="15" t="n">
         <v>0.002851839911411517</v>
       </c>
+      <c r="H87" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I87" s="15" t="n">
+        <v>0.00194482107874878</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="n">
@@ -3531,6 +4202,12 @@
       <c r="G88" s="15" t="n">
         <v>0.002277643956093762</v>
       </c>
+      <c r="H88" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="I88" s="15" t="n">
+        <v>0.002059222318675179</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="n">
@@ -3554,6 +4231,12 @@
       <c r="G89" s="15" t="n">
         <v>0.002469042607866347</v>
       </c>
+      <c r="H89" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="I89" s="15" t="n">
+        <v>0.002802830378196771</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="n">
@@ -3577,6 +4260,12 @@
       <c r="G90" s="15" t="n">
         <v>0.00243076287751183</v>
       </c>
+      <c r="H90" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I90" s="15" t="n">
+        <v>0.00194482107874878</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="n">
@@ -3600,6 +4289,12 @@
       <c r="G91" s="15" t="n">
         <v>0.002373343281980054</v>
       </c>
+      <c r="H91" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="I91" s="15" t="n">
+        <v>0.002002021698711979</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="n">
@@ -3623,6 +4318,12 @@
       <c r="G92" s="15" t="n">
         <v>0.002124525034675694</v>
       </c>
+      <c r="H92" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="I92" s="15" t="n">
+        <v>0.001830419838822381</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="n">
@@ -3646,6 +4347,12 @@
       <c r="G93" s="15" t="n">
         <v>0.002143664899852952</v>
       </c>
+      <c r="H93" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="15" t="n">
+        <v>0.001716018598895982</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="n">
@@ -3669,6 +4376,12 @@
       <c r="G94" s="15" t="n">
         <v>0.001971406113257626</v>
       </c>
+      <c r="H94" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="I94" s="15" t="n">
+        <v>0.00188762045878558</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="n">
@@ -3692,6 +4405,12 @@
       <c r="G95" s="15" t="n">
         <v>0.00191398651772585</v>
       </c>
+      <c r="H95" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="I95" s="15" t="n">
+        <v>0.001372814879116786</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="n">
@@ -3715,6 +4434,12 @@
       <c r="G96" s="15" t="n">
         <v>0.001722587865953265</v>
       </c>
+      <c r="H96" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I96" s="15" t="n">
+        <v>0.001144012399263988</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="14" t="n">
@@ -3738,6 +4463,12 @@
       <c r="G97" s="15" t="n">
         <v>0.001646028405244231</v>
       </c>
+      <c r="H97" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="I97" s="15" t="n">
+        <v>0.002059222318675179</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="n">
@@ -3761,6 +4492,12 @@
       <c r="G98" s="15" t="n">
         <v>0.001512049349003422</v>
       </c>
+      <c r="H98" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="I98" s="15" t="n">
+        <v>0.001601617358969583</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="14" t="n">
@@ -3784,6 +4521,12 @@
       <c r="G99" s="15" t="n">
         <v>0.001971406113257626</v>
       </c>
+      <c r="H99" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I99" s="15" t="n">
+        <v>0.001144012399263988</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="n">
@@ -3807,6 +4550,12 @@
       <c r="G100" s="15" t="n">
         <v>0.001722587865953265</v>
       </c>
+      <c r="H100" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="I100" s="15" t="n">
+        <v>0.0009724105393743899</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="14" t="n">
@@ -3830,6 +4579,12 @@
       <c r="G101" s="15" t="n">
         <v>0.001550329079357939</v>
       </c>
+      <c r="H101" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="I101" s="15" t="n">
+        <v>0.001029611159337589</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="n">
@@ -3853,6 +4608,12 @@
       <c r="G102" s="15" t="n">
         <v>0.001435489888294388</v>
       </c>
+      <c r="H102" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="I102" s="15" t="n">
+        <v>0.001487216119043185</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="14" t="n">
@@ -3876,6 +4637,12 @@
       <c r="G103" s="15" t="n">
         <v>0.001473769618648905</v>
       </c>
+      <c r="H103" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="I103" s="15" t="n">
+        <v>0.0009724105393743899</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="n">
@@ -3899,6 +4666,12 @@
       <c r="G104" s="15" t="n">
         <v>0.001320650697230837</v>
       </c>
+      <c r="H104" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I104" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="14" t="n">
@@ -3922,6 +4695,12 @@
       <c r="G105" s="15" t="n">
         <v>0.001224951371344544</v>
       </c>
+      <c r="H105" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I105" s="15" t="n">
+        <v>0.0009152099194111905</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="n">
@@ -3945,6 +4724,12 @@
       <c r="G106" s="15" t="n">
         <v>0.001626888540066973</v>
       </c>
+      <c r="H106" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="I106" s="15" t="n">
+        <v>0.001372814879116786</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="14" t="n">
@@ -3968,6 +4753,12 @@
       <c r="G107" s="15" t="n">
         <v>0.001186671640990027</v>
       </c>
+      <c r="H107" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I107" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="n">
@@ -3991,6 +4782,12 @@
       <c r="G108" s="15" t="n">
         <v>0.0009378533936856665</v>
       </c>
+      <c r="H108" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="I108" s="15" t="n">
+        <v>0.001086811779300789</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="14" t="n">
@@ -4014,6 +4811,12 @@
       <c r="G109" s="15" t="n">
         <v>0.001052692584749218</v>
       </c>
+      <c r="H109" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I109" s="15" t="n">
+        <v>0.0009152099194111905</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="n">
@@ -4037,6 +4840,12 @@
       <c r="G110" s="15" t="n">
         <v>0.001186671640990027</v>
       </c>
+      <c r="H110" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I110" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="14" t="n">
@@ -4060,6 +4869,12 @@
       <c r="G111" s="15" t="n">
         <v>0.001263231101699061</v>
       </c>
+      <c r="H111" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I111" s="15" t="n">
+        <v>0.0008580092994479911</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="n">
@@ -4083,6 +4898,12 @@
       <c r="G112" s="15" t="n">
         <v>0.00128237096687632</v>
       </c>
+      <c r="H112" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="I112" s="15" t="n">
+        <v>0.001086811779300789</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="14" t="n">
@@ -4106,6 +4927,12 @@
       <c r="G113" s="15" t="n">
         <v>0.001014412854394701</v>
       </c>
+      <c r="H113" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="I113" s="15" t="n">
+        <v>0.0009724105393743899</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="n">
@@ -4129,6 +4956,12 @@
       <c r="G114" s="15" t="n">
         <v>0.0009187135285084081</v>
       </c>
+      <c r="H114" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I114" s="15" t="n">
+        <v>0.0008580092994479911</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="n">
@@ -4152,6 +4985,12 @@
       <c r="G115" s="15" t="n">
         <v>0.0008230142026221155</v>
       </c>
+      <c r="H115" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I115" s="15" t="n">
+        <v>0.0009152099194111905</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="n">
@@ -4175,6 +5014,12 @@
       <c r="G116" s="15" t="n">
         <v>0.001071832449926476</v>
       </c>
+      <c r="H116" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I116" s="15" t="n">
+        <v>0.0008580092994479911</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="14" t="n">
@@ -4198,6 +5043,12 @@
       <c r="G117" s="15" t="n">
         <v>0.001110112180280993</v>
       </c>
+      <c r="H117" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I117" s="15" t="n">
+        <v>0.0008008086794847916</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="n">
@@ -4221,6 +5072,12 @@
       <c r="G118" s="15" t="n">
         <v>0.001071832449926476</v>
       </c>
+      <c r="H118" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I118" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="14" t="n">
@@ -4244,6 +5101,12 @@
       <c r="G119" s="15" t="n">
         <v>0.00114839191063551</v>
       </c>
+      <c r="H119" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I119" s="15" t="n">
+        <v>0.0008008086794847916</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="14" t="n">
@@ -4267,6 +5130,12 @@
       <c r="G120" s="15" t="n">
         <v>0.001033552719571959</v>
       </c>
+      <c r="H120" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I120" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="14" t="n">
@@ -4290,6 +5159,12 @@
       <c r="G121" s="15" t="n">
         <v>0.0008612939329766325</v>
       </c>
+      <c r="H121" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I121" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="14" t="n">
@@ -4313,6 +5188,12 @@
       <c r="G122" s="15" t="n">
         <v>0.001052692584749218</v>
       </c>
+      <c r="H122" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I122" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="n">
@@ -4336,6 +5217,12 @@
       <c r="G123" s="15" t="n">
         <v>0.001167531775812768</v>
       </c>
+      <c r="H123" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="I123" s="15" t="n">
+        <v>0.001029611159337589</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="14" t="n">
@@ -4359,6 +5246,12 @@
       <c r="G124" s="15" t="n">
         <v>0.001033552719571959</v>
       </c>
+      <c r="H124" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I124" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="14" t="n">
@@ -4382,6 +5275,12 @@
       <c r="G125" s="15" t="n">
         <v>0.001129252045458252</v>
       </c>
+      <c r="H125" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I125" s="15" t="n">
+        <v>0.0008580092994479911</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="14" t="n">
@@ -4405,6 +5304,12 @@
       <c r="G126" s="15" t="n">
         <v>0.001052692584749218</v>
       </c>
+      <c r="H126" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I126" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="14" t="n">
@@ -4428,6 +5333,12 @@
       <c r="G127" s="15" t="n">
         <v>0.0009761331240401836</v>
       </c>
+      <c r="H127" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="I127" s="15" t="n">
+        <v>0.001086811779300789</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="14" t="n">
@@ -4451,6 +5362,12 @@
       <c r="G128" s="15" t="n">
         <v>0.0009952729892174421</v>
       </c>
+      <c r="H128" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I128" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="14" t="n">
@@ -4474,6 +5391,12 @@
       <c r="G129" s="15" t="n">
         <v>0.0009761331240401836</v>
       </c>
+      <c r="H129" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I129" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="14" t="n">
@@ -4497,6 +5420,12 @@
       <c r="G130" s="15" t="n">
         <v>0.0009187135285084081</v>
       </c>
+      <c r="H130" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I130" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="14" t="n">
@@ -4520,6 +5449,12 @@
       <c r="G131" s="15" t="n">
         <v>0.001014412854394701</v>
       </c>
+      <c r="H131" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I131" s="15" t="n">
+        <v>0.0008580092994479911</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="14" t="n">
@@ -4543,6 +5478,12 @@
       <c r="G132" s="15" t="n">
         <v>0.0008995736633311495</v>
       </c>
+      <c r="H132" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I132" s="15" t="n">
+        <v>0.0008008086794847916</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="14" t="n">
@@ -4566,6 +5507,12 @@
       <c r="G133" s="15" t="n">
         <v>0.0007273148767358231</v>
       </c>
+      <c r="H133" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I133" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="14" t="n">
@@ -4589,6 +5536,12 @@
       <c r="G134" s="15" t="n">
         <v>0.0008421540677993741</v>
       </c>
+      <c r="H134" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I134" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="14" t="n">
@@ -4612,6 +5565,12 @@
       <c r="G135" s="15" t="n">
         <v>0.0007847344722675985</v>
       </c>
+      <c r="H135" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I135" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="14" t="n">
@@ -4635,6 +5594,12 @@
       <c r="G136" s="15" t="n">
         <v>0.0009569932588629251</v>
       </c>
+      <c r="H136" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I136" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="14" t="n">
@@ -4658,6 +5623,12 @@
       <c r="G137" s="15" t="n">
         <v>0.0008995736633311495</v>
       </c>
+      <c r="H137" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I137" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="14" t="n">
@@ -4681,6 +5652,12 @@
       <c r="G138" s="15" t="n">
         <v>0.0009187135285084081</v>
       </c>
+      <c r="H138" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I138" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="14" t="n">
@@ -4704,6 +5681,12 @@
       <c r="G139" s="15" t="n">
         <v>0.0006698952812040476</v>
       </c>
+      <c r="H139" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I139" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="14" t="n">
@@ -4727,6 +5710,12 @@
       <c r="G140" s="15" t="n">
         <v>0.001301510832053578</v>
       </c>
+      <c r="H140" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I140" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="14" t="n">
@@ -4750,6 +5739,12 @@
       <c r="G141" s="15" t="n">
         <v>0.0007655946070903401</v>
       </c>
+      <c r="H141" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I141" s="15" t="n">
+        <v>0.0009152099194111905</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="14" t="n">
@@ -4773,6 +5768,12 @@
       <c r="G142" s="15" t="n">
         <v>0.0008612939329766325</v>
       </c>
+      <c r="H142" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I142" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="14" t="n">
@@ -4796,6 +5797,12 @@
       <c r="G143" s="15" t="n">
         <v>0.0009761331240401836</v>
       </c>
+      <c r="H143" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I143" s="15" t="n">
+        <v>0.0008008086794847916</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="14" t="n">
@@ -4819,6 +5826,12 @@
       <c r="G144" s="15" t="n">
         <v>0.0008804337981538911</v>
       </c>
+      <c r="H144" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I144" s="15" t="n">
+        <v>0.001144012399263988</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="14" t="n">
@@ -4842,6 +5855,12 @@
       <c r="G145" s="15" t="n">
         <v>0.0007464547419130816</v>
       </c>
+      <c r="H145" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I145" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="14" t="n">
@@ -4865,6 +5884,12 @@
       <c r="G146" s="15" t="n">
         <v>0.0009761331240401836</v>
       </c>
+      <c r="H146" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I146" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="14" t="n">
@@ -4888,6 +5913,12 @@
       <c r="G147" s="15" t="n">
         <v>0.0008804337981538911</v>
       </c>
+      <c r="H147" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I147" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="14" t="n">
@@ -4911,6 +5942,12 @@
       <c r="G148" s="15" t="n">
         <v>0.0009952729892174421</v>
       </c>
+      <c r="H148" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I148" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="14" t="n">
@@ -4934,6 +5971,12 @@
       <c r="G149" s="15" t="n">
         <v>0.0009187135285084081</v>
       </c>
+      <c r="H149" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I149" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="14" t="n">
@@ -4957,6 +6000,12 @@
       <c r="G150" s="15" t="n">
         <v>0.0009187135285084081</v>
       </c>
+      <c r="H150" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I150" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="14" t="n">
@@ -4980,6 +6029,12 @@
       <c r="G151" s="15" t="n">
         <v>0.001090972315103735</v>
       </c>
+      <c r="H151" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I151" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="14" t="n">
@@ -5003,6 +6058,12 @@
       <c r="G152" s="15" t="n">
         <v>0.000650755416026789</v>
       </c>
+      <c r="H152" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I152" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="14" t="n">
@@ -5026,6 +6087,12 @@
       <c r="G153" s="15" t="n">
         <v>0.0007847344722675985</v>
       </c>
+      <c r="H153" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I153" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="14" t="n">
@@ -5049,6 +6116,12 @@
       <c r="G154" s="15" t="n">
         <v>0.0008421540677993741</v>
       </c>
+      <c r="H154" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I154" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="14" t="n">
@@ -5072,6 +6145,12 @@
       <c r="G155" s="15" t="n">
         <v>0.0007464547419130816</v>
       </c>
+      <c r="H155" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I155" s="15" t="n">
+        <v>0.0008008086794847916</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="14" t="n">
@@ -5095,6 +6174,12 @@
       <c r="G156" s="15" t="n">
         <v>0.0008421540677993741</v>
       </c>
+      <c r="H156" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I156" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="14" t="n">
@@ -5118,6 +6203,12 @@
       <c r="G157" s="15" t="n">
         <v>0.0008230142026221155</v>
       </c>
+      <c r="H157" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I157" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="14" t="n">
@@ -5141,6 +6232,12 @@
       <c r="G158" s="15" t="n">
         <v>0.0008612939329766325</v>
       </c>
+      <c r="H158" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I158" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="14" t="n">
@@ -5164,6 +6261,12 @@
       <c r="G159" s="15" t="n">
         <v>0.0008804337981538911</v>
       </c>
+      <c r="H159" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I159" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="14" t="n">
@@ -5187,6 +6290,12 @@
       <c r="G160" s="15" t="n">
         <v>0.0006698952812040476</v>
       </c>
+      <c r="H160" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I160" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="14" t="n">
@@ -5210,6 +6319,12 @@
       <c r="G161" s="15" t="n">
         <v>0.0008804337981538911</v>
       </c>
+      <c r="H161" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I161" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="14" t="n">
@@ -5233,6 +6348,12 @@
       <c r="G162" s="15" t="n">
         <v>0.0008995736633311495</v>
       </c>
+      <c r="H162" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I162" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="14" t="n">
@@ -5256,6 +6377,12 @@
       <c r="G163" s="15" t="n">
         <v>0.0007273148767358231</v>
       </c>
+      <c r="H163" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I163" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="14" t="n">
@@ -5279,6 +6406,12 @@
       <c r="G164" s="15" t="n">
         <v>0.0008038743374448571</v>
       </c>
+      <c r="H164" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I164" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="14" t="n">
@@ -5302,6 +6435,12 @@
       <c r="G165" s="15" t="n">
         <v>0.0007464547419130816</v>
       </c>
+      <c r="H165" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I165" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="14" t="n">
@@ -5325,6 +6464,12 @@
       <c r="G166" s="15" t="n">
         <v>0.0009378533936856665</v>
       </c>
+      <c r="H166" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="I166" s="15" t="n">
+        <v>0.001201213019227188</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="14" t="n">
@@ -5348,6 +6493,12 @@
       <c r="G167" s="15" t="n">
         <v>0.0007081750115585646</v>
       </c>
+      <c r="H167" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I167" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="14" t="n">
@@ -5371,6 +6522,12 @@
       <c r="G168" s="15" t="n">
         <v>0.0005550560901404966</v>
       </c>
+      <c r="H168" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I168" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="14" t="n">
@@ -5394,6 +6551,12 @@
       <c r="G169" s="15" t="n">
         <v>0.0006698952812040476</v>
       </c>
+      <c r="H169" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I169" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="14" t="n">
@@ -5417,6 +6580,12 @@
       <c r="G170" s="15" t="n">
         <v>0.0008230142026221155</v>
       </c>
+      <c r="H170" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I170" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="14" t="n">
@@ -5440,6 +6609,12 @@
       <c r="G171" s="15" t="n">
         <v>0.0008230142026221155</v>
       </c>
+      <c r="H171" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I171" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="14" t="n">
@@ -5463,6 +6638,12 @@
       <c r="G172" s="15" t="n">
         <v>0.000689035146381306</v>
       </c>
+      <c r="H172" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I172" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="14" t="n">
@@ -5486,6 +6667,12 @@
       <c r="G173" s="15" t="n">
         <v>0.0009187135285084081</v>
       </c>
+      <c r="H173" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I173" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="14" t="n">
@@ -5509,6 +6696,12 @@
       <c r="G174" s="15" t="n">
         <v>0.000650755416026789</v>
       </c>
+      <c r="H174" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I174" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="14" t="n">
@@ -5532,6 +6725,12 @@
       <c r="G175" s="15" t="n">
         <v>0.0006698952812040476</v>
       </c>
+      <c r="H175" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I175" s="15" t="n">
+        <v>0.0009152099194111905</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="14" t="n">
@@ -5555,6 +6754,12 @@
       <c r="G176" s="15" t="n">
         <v>0.0008995736633311495</v>
       </c>
+      <c r="H176" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I176" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="14" t="n">
@@ -5578,6 +6783,12 @@
       <c r="G177" s="15" t="n">
         <v>0.0008038743374448571</v>
       </c>
+      <c r="H177" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I177" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="14" t="n">
@@ -5601,6 +6812,12 @@
       <c r="G178" s="15" t="n">
         <v>0.000612475685672272</v>
       </c>
+      <c r="H178" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I178" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="14" t="n">
@@ -5624,6 +6841,12 @@
       <c r="G179" s="15" t="n">
         <v>0.0005933358204950136</v>
       </c>
+      <c r="H179" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I179" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="14" t="n">
@@ -5647,6 +6870,12 @@
       <c r="G180" s="15" t="n">
         <v>0.0006698952812040476</v>
       </c>
+      <c r="H180" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I180" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="14" t="n">
@@ -5670,6 +6899,12 @@
       <c r="G181" s="15" t="n">
         <v>0.0007655946070903401</v>
       </c>
+      <c r="H181" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I181" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="14" t="n">
@@ -5693,6 +6928,12 @@
       <c r="G182" s="15" t="n">
         <v>0.000612475685672272</v>
       </c>
+      <c r="H182" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I182" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="14" t="n">
@@ -5716,6 +6957,12 @@
       <c r="G183" s="15" t="n">
         <v>0.0008995736633311495</v>
       </c>
+      <c r="H183" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I183" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="14" t="n">
@@ -5739,6 +6986,12 @@
       <c r="G184" s="15" t="n">
         <v>0.0007081750115585646</v>
       </c>
+      <c r="H184" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I184" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="14" t="n">
@@ -5762,6 +7015,12 @@
       <c r="G185" s="15" t="n">
         <v>0.0005933358204950136</v>
       </c>
+      <c r="H185" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I185" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="14" t="n">
@@ -5785,6 +7044,12 @@
       <c r="G186" s="15" t="n">
         <v>0.0008230142026221155</v>
       </c>
+      <c r="H186" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I186" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="14" t="n">
@@ -5808,6 +7073,12 @@
       <c r="G187" s="15" t="n">
         <v>0.0005933358204950136</v>
       </c>
+      <c r="H187" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I187" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="14" t="n">
@@ -5831,6 +7102,12 @@
       <c r="G188" s="15" t="n">
         <v>0.0007081750115585646</v>
       </c>
+      <c r="H188" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I188" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="14" t="n">
@@ -5854,6 +7131,12 @@
       <c r="G189" s="15" t="n">
         <v>0.0004784966294314625</v>
       </c>
+      <c r="H189" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I189" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="14" t="n">
@@ -5877,6 +7160,12 @@
       <c r="G190" s="15" t="n">
         <v>0.000535916224963238</v>
       </c>
+      <c r="H190" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I190" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="14" t="n">
@@ -5900,6 +7189,12 @@
       <c r="G191" s="15" t="n">
         <v>0.0007464547419130816</v>
       </c>
+      <c r="H191" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I191" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="14" t="n">
@@ -5923,6 +7218,12 @@
       <c r="G192" s="15" t="n">
         <v>0.0009187135285084081</v>
       </c>
+      <c r="H192" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I192" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="14" t="n">
@@ -5946,6 +7247,12 @@
       <c r="G193" s="15" t="n">
         <v>0.0008804337981538911</v>
       </c>
+      <c r="H193" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I193" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="14" t="n">
@@ -5969,6 +7276,12 @@
       <c r="G194" s="15" t="n">
         <v>0.000689035146381306</v>
       </c>
+      <c r="H194" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I194" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="14" t="n">
@@ -5992,6 +7305,12 @@
       <c r="G195" s="15" t="n">
         <v>0.000689035146381306</v>
       </c>
+      <c r="H195" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I195" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="14" t="n">
@@ -6015,6 +7334,12 @@
       <c r="G196" s="15" t="n">
         <v>0.000689035146381306</v>
       </c>
+      <c r="H196" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I196" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="14" t="n">
@@ -6038,6 +7363,12 @@
       <c r="G197" s="15" t="n">
         <v>0.0005933358204950136</v>
       </c>
+      <c r="H197" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I197" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="14" t="n">
@@ -6061,6 +7392,12 @@
       <c r="G198" s="15" t="n">
         <v>0.0007847344722675985</v>
       </c>
+      <c r="H198" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I198" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="14" t="n">
@@ -6084,6 +7421,12 @@
       <c r="G199" s="15" t="n">
         <v>0.0008230142026221155</v>
       </c>
+      <c r="H199" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I199" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="14" t="n">
@@ -6107,6 +7450,12 @@
       <c r="G200" s="15" t="n">
         <v>0.000574195955317755</v>
       </c>
+      <c r="H200" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I200" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="14" t="n">
@@ -6130,6 +7479,12 @@
       <c r="G201" s="15" t="n">
         <v>0.0005167763597859796</v>
       </c>
+      <c r="H201" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I201" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="14" t="n">
@@ -6153,6 +7508,12 @@
       <c r="G202" s="15" t="n">
         <v>0.0006316155508495306</v>
       </c>
+      <c r="H202" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I202" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="14" t="n">
@@ -6176,6 +7537,12 @@
       <c r="G203" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H203" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I203" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="14" t="n">
@@ -6199,6 +7566,12 @@
       <c r="G204" s="15" t="n">
         <v>0.000574195955317755</v>
       </c>
+      <c r="H204" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I204" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="14" t="n">
@@ -6222,6 +7595,12 @@
       <c r="G205" s="15" t="n">
         <v>0.000689035146381306</v>
       </c>
+      <c r="H205" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I205" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="14" t="n">
@@ -6245,6 +7624,12 @@
       <c r="G206" s="15" t="n">
         <v>0.000612475685672272</v>
       </c>
+      <c r="H206" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I206" s="15" t="n">
+        <v>5.72006199631994e-05</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="14" t="n">
@@ -6268,6 +7653,12 @@
       <c r="G207" s="15" t="n">
         <v>0.0008421540677993741</v>
       </c>
+      <c r="H207" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I207" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="14" t="n">
@@ -6291,6 +7682,12 @@
       <c r="G208" s="15" t="n">
         <v>0.0007464547419130816</v>
       </c>
+      <c r="H208" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I208" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="14" t="n">
@@ -6314,6 +7711,12 @@
       <c r="G209" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H209" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I209" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="14" t="n">
@@ -6337,6 +7740,12 @@
       <c r="G210" s="15" t="n">
         <v>0.0004402168990769455</v>
       </c>
+      <c r="H210" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I210" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="14" t="n">
@@ -6360,6 +7769,12 @@
       <c r="G211" s="15" t="n">
         <v>0.000535916224963238</v>
       </c>
+      <c r="H211" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I211" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="14" t="n">
@@ -6383,6 +7798,12 @@
       <c r="G212" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H212" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I212" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="14" t="n">
@@ -6406,6 +7827,12 @@
       <c r="G213" s="15" t="n">
         <v>0.0003827973035451701</v>
       </c>
+      <c r="H213" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I213" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="14" t="n">
@@ -6429,6 +7856,12 @@
       <c r="G214" s="15" t="n">
         <v>0.0005167763597859796</v>
       </c>
+      <c r="H214" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I214" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="14" t="n">
@@ -6452,6 +7885,12 @@
       <c r="G215" s="15" t="n">
         <v>0.0005550560901404966</v>
       </c>
+      <c r="H215" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I215" s="15" t="n">
+        <v>0.0008008086794847916</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="14" t="n">
@@ -6475,6 +7914,12 @@
       <c r="G216" s="15" t="n">
         <v>0.000535916224963238</v>
       </c>
+      <c r="H216" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I216" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="14" t="n">
@@ -6498,6 +7943,12 @@
       <c r="G217" s="15" t="n">
         <v>0.000535916224963238</v>
       </c>
+      <c r="H217" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I217" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="14" t="n">
@@ -6521,6 +7972,12 @@
       <c r="G218" s="15" t="n">
         <v>0.0005167763597859796</v>
       </c>
+      <c r="H218" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I218" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="14" t="n">
@@ -6544,6 +8001,12 @@
       <c r="G219" s="15" t="n">
         <v>0.0004402168990769455</v>
       </c>
+      <c r="H219" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I219" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="14" t="n">
@@ -6567,6 +8030,12 @@
       <c r="G220" s="15" t="n">
         <v>0.0007273148767358231</v>
       </c>
+      <c r="H220" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I220" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="14" t="n">
@@ -6590,6 +8059,12 @@
       <c r="G221" s="15" t="n">
         <v>0.0005550560901404966</v>
       </c>
+      <c r="H221" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I221" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="14" t="n">
@@ -6613,6 +8088,12 @@
       <c r="G222" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H222" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I222" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="14" t="n">
@@ -6636,6 +8117,12 @@
       <c r="G223" s="15" t="n">
         <v>0.0005167763597859796</v>
       </c>
+      <c r="H223" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I223" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="14" t="n">
@@ -6659,6 +8146,12 @@
       <c r="G224" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H224" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I224" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="14" t="n">
@@ -6682,6 +8175,12 @@
       <c r="G225" s="15" t="n">
         <v>0.000612475685672272</v>
       </c>
+      <c r="H225" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I225" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="14" t="n">
@@ -6705,6 +8204,12 @@
       <c r="G226" s="15" t="n">
         <v>0.0005550560901404966</v>
       </c>
+      <c r="H226" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I226" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="14" t="n">
@@ -6728,6 +8233,12 @@
       <c r="G227" s="15" t="n">
         <v>0.000689035146381306</v>
       </c>
+      <c r="H227" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I227" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="14" t="n">
@@ -6751,6 +8262,12 @@
       <c r="G228" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H228" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I228" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="14" t="n">
@@ -6774,6 +8291,12 @@
       <c r="G229" s="15" t="n">
         <v>0.000689035146381306</v>
       </c>
+      <c r="H229" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I229" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="14" t="n">
@@ -6797,6 +8320,12 @@
       <c r="G230" s="15" t="n">
         <v>0.000344517573190653</v>
       </c>
+      <c r="H230" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I230" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="14" t="n">
@@ -6820,6 +8349,12 @@
       <c r="G231" s="15" t="n">
         <v>0.0004784966294314625</v>
       </c>
+      <c r="H231" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I231" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="14" t="n">
@@ -6843,6 +8378,12 @@
       <c r="G232" s="15" t="n">
         <v>0.0005933358204950136</v>
       </c>
+      <c r="H232" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I232" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="14" t="n">
@@ -6866,6 +8407,12 @@
       <c r="G233" s="15" t="n">
         <v>0.000650755416026789</v>
       </c>
+      <c r="H233" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I233" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="14" t="n">
@@ -6889,6 +8436,12 @@
       <c r="G234" s="15" t="n">
         <v>0.000459356764254204</v>
       </c>
+      <c r="H234" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I234" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="14" t="n">
@@ -6912,6 +8465,12 @@
       <c r="G235" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H235" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I235" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="14" t="n">
@@ -6935,6 +8494,12 @@
       <c r="G236" s="15" t="n">
         <v>0.0004784966294314625</v>
       </c>
+      <c r="H236" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I236" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="14" t="n">
@@ -6958,6 +8523,12 @@
       <c r="G237" s="15" t="n">
         <v>0.0003827973035451701</v>
       </c>
+      <c r="H237" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I237" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="14" t="n">
@@ -6981,6 +8552,12 @@
       <c r="G238" s="15" t="n">
         <v>0.000650755416026789</v>
       </c>
+      <c r="H238" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I238" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="14" t="n">
@@ -7004,6 +8581,12 @@
       <c r="G239" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H239" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I239" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="14" t="n">
@@ -7027,6 +8610,12 @@
       <c r="G240" s="15" t="n">
         <v>0.0005167763597859796</v>
       </c>
+      <c r="H240" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I240" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="14" t="n">
@@ -7050,6 +8639,12 @@
       <c r="G241" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H241" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I241" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="14" t="n">
@@ -7073,6 +8668,12 @@
       <c r="G242" s="15" t="n">
         <v>0.000535916224963238</v>
       </c>
+      <c r="H242" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I242" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="14" t="n">
@@ -7096,6 +8697,12 @@
       <c r="G243" s="15" t="n">
         <v>0.000574195955317755</v>
       </c>
+      <c r="H243" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I243" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="14" t="n">
@@ -7119,6 +8726,12 @@
       <c r="G244" s="15" t="n">
         <v>0.0004402168990769455</v>
       </c>
+      <c r="H244" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I244" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="14" t="n">
@@ -7142,6 +8755,12 @@
       <c r="G245" s="15" t="n">
         <v>0.000689035146381306</v>
       </c>
+      <c r="H245" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I245" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="14" t="n">
@@ -7165,6 +8784,12 @@
       <c r="G246" s="15" t="n">
         <v>0.0005933358204950136</v>
       </c>
+      <c r="H246" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I246" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="14" t="n">
@@ -7188,6 +8813,12 @@
       <c r="G247" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H247" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I247" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="14" t="n">
@@ -7211,6 +8842,12 @@
       <c r="G248" s="15" t="n">
         <v>0.000574195955317755</v>
       </c>
+      <c r="H248" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I248" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="14" t="n">
@@ -7234,6 +8871,12 @@
       <c r="G249" s="15" t="n">
         <v>0.0006698952812040476</v>
       </c>
+      <c r="H249" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I249" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="14" t="n">
@@ -7257,6 +8900,12 @@
       <c r="G250" s="15" t="n">
         <v>0.0004784966294314625</v>
       </c>
+      <c r="H250" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I250" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="14" t="n">
@@ -7280,6 +8929,12 @@
       <c r="G251" s="15" t="n">
         <v>0.0002870979776588775</v>
       </c>
+      <c r="H251" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I251" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="14" t="n">
@@ -7303,6 +8958,12 @@
       <c r="G252" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H252" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I252" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="14" t="n">
@@ -7326,6 +8987,12 @@
       <c r="G253" s="15" t="n">
         <v>0.000574195955317755</v>
       </c>
+      <c r="H253" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I253" s="15" t="n">
+        <v>0.0001144012399263988</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="14" t="n">
@@ -7349,6 +9016,12 @@
       <c r="G254" s="15" t="n">
         <v>0.0005933358204950136</v>
       </c>
+      <c r="H254" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I254" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="14" t="n">
@@ -7372,6 +9045,12 @@
       <c r="G255" s="15" t="n">
         <v>0.0005933358204950136</v>
       </c>
+      <c r="H255" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I255" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="14" t="n">
@@ -7395,6 +9074,12 @@
       <c r="G256" s="15" t="n">
         <v>0.0006698952812040476</v>
       </c>
+      <c r="H256" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I256" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="14" t="n">
@@ -7418,6 +9103,12 @@
       <c r="G257" s="15" t="n">
         <v>0.000650755416026789</v>
       </c>
+      <c r="H257" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I257" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="14" t="n">
@@ -7441,6 +9132,12 @@
       <c r="G258" s="15" t="n">
         <v>0.0007081750115585646</v>
       </c>
+      <c r="H258" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I258" s="15" t="n">
+        <v>0.0008008086794847916</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="14" t="n">
@@ -7464,6 +9161,12 @@
       <c r="G259" s="15" t="n">
         <v>0.0007081750115585646</v>
       </c>
+      <c r="H259" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I259" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="14" t="n">
@@ -7487,6 +9190,12 @@
       <c r="G260" s="15" t="n">
         <v>0.000459356764254204</v>
       </c>
+      <c r="H260" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I260" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="14" t="n">
@@ -7510,6 +9219,12 @@
       <c r="G261" s="15" t="n">
         <v>0.000689035146381306</v>
       </c>
+      <c r="H261" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I261" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="14" t="n">
@@ -7533,6 +9248,12 @@
       <c r="G262" s="15" t="n">
         <v>0.0007464547419130816</v>
       </c>
+      <c r="H262" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I262" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="14" t="n">
@@ -7556,6 +9277,12 @@
       <c r="G263" s="15" t="n">
         <v>0.0006316155508495306</v>
       </c>
+      <c r="H263" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I263" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="14" t="n">
@@ -7579,6 +9306,12 @@
       <c r="G264" s="15" t="n">
         <v>0.0008612939329766325</v>
       </c>
+      <c r="H264" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I264" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="14" t="n">
@@ -7602,6 +9335,12 @@
       <c r="G265" s="15" t="n">
         <v>0.0007464547419130816</v>
       </c>
+      <c r="H265" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I265" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="14" t="n">
@@ -7625,6 +9364,12 @@
       <c r="G266" s="15" t="n">
         <v>0.0009761331240401836</v>
       </c>
+      <c r="H266" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I266" s="15" t="n">
+        <v>0.0008008086794847916</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="14" t="n">
@@ -7648,6 +9393,12 @@
       <c r="G267" s="15" t="n">
         <v>0.0007464547419130816</v>
       </c>
+      <c r="H267" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I267" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="14" t="n">
@@ -7671,6 +9422,12 @@
       <c r="G268" s="15" t="n">
         <v>0.0008612939329766325</v>
       </c>
+      <c r="H268" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I268" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="14" t="n">
@@ -7694,6 +9451,12 @@
       <c r="G269" s="15" t="n">
         <v>0.0009378533936856665</v>
       </c>
+      <c r="H269" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I269" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="14" t="n">
@@ -7717,6 +9480,12 @@
       <c r="G270" s="15" t="n">
         <v>0.0009569932588629251</v>
       </c>
+      <c r="H270" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="I270" s="15" t="n">
+        <v>0.0009152099194111905</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="14" t="n">
@@ -7740,6 +9509,12 @@
       <c r="G271" s="15" t="n">
         <v>0.0009378533936856665</v>
       </c>
+      <c r="H271" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I271" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="14" t="n">
@@ -7763,6 +9538,12 @@
       <c r="G272" s="15" t="n">
         <v>0.001052692584749218</v>
       </c>
+      <c r="H272" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="I272" s="15" t="n">
+        <v>0.001258413639190387</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="14" t="n">
@@ -7786,6 +9567,12 @@
       <c r="G273" s="15" t="n">
         <v>0.0008421540677993741</v>
       </c>
+      <c r="H273" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I273" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="14" t="n">
@@ -7809,6 +9596,12 @@
       <c r="G274" s="15" t="n">
         <v>0.0008995736633311495</v>
       </c>
+      <c r="H274" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I274" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="14" t="n">
@@ -7832,6 +9625,12 @@
       <c r="G275" s="15" t="n">
         <v>0.0007655946070903401</v>
       </c>
+      <c r="H275" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I275" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="14" t="n">
@@ -7855,6 +9654,12 @@
       <c r="G276" s="15" t="n">
         <v>0.0006316155508495306</v>
       </c>
+      <c r="H276" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I276" s="15" t="n">
+        <v>0.0008580092994479911</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="14" t="n">
@@ -7878,6 +9683,12 @@
       <c r="G277" s="15" t="n">
         <v>0.0008612939329766325</v>
       </c>
+      <c r="H277" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I277" s="15" t="n">
+        <v>0.0008008086794847916</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="14" t="n">
@@ -7901,6 +9712,12 @@
       <c r="G278" s="15" t="n">
         <v>0.000689035146381306</v>
       </c>
+      <c r="H278" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I278" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="14" t="n">
@@ -7924,6 +9741,12 @@
       <c r="G279" s="15" t="n">
         <v>0.001014412854394701</v>
       </c>
+      <c r="H279" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I279" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="14" t="n">
@@ -7947,6 +9770,12 @@
       <c r="G280" s="15" t="n">
         <v>0.000612475685672272</v>
       </c>
+      <c r="H280" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I280" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="14" t="n">
@@ -7970,6 +9799,12 @@
       <c r="G281" s="15" t="n">
         <v>0.0008230142026221155</v>
       </c>
+      <c r="H281" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I281" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="14" t="n">
@@ -7993,6 +9828,12 @@
       <c r="G282" s="15" t="n">
         <v>0.001110112180280993</v>
       </c>
+      <c r="H282" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I282" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="14" t="n">
@@ -8016,6 +9857,12 @@
       <c r="G283" s="15" t="n">
         <v>0.0008421540677993741</v>
       </c>
+      <c r="H283" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I283" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="14" t="n">
@@ -8039,6 +9886,12 @@
       <c r="G284" s="15" t="n">
         <v>0.0008421540677993741</v>
       </c>
+      <c r="H284" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I284" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="14" t="n">
@@ -8062,6 +9915,12 @@
       <c r="G285" s="15" t="n">
         <v>0.0008612939329766325</v>
       </c>
+      <c r="H285" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I285" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="14" t="n">
@@ -8085,6 +9944,12 @@
       <c r="G286" s="15" t="n">
         <v>0.0008230142026221155</v>
       </c>
+      <c r="H286" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I286" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="14" t="n">
@@ -8108,6 +9973,12 @@
       <c r="G287" s="15" t="n">
         <v>0.0008995736633311495</v>
       </c>
+      <c r="H287" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I287" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="14" t="n">
@@ -8131,6 +10002,12 @@
       <c r="G288" s="15" t="n">
         <v>0.001014412854394701</v>
       </c>
+      <c r="H288" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I288" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="14" t="n">
@@ -8154,6 +10031,12 @@
       <c r="G289" s="15" t="n">
         <v>0.0009952729892174421</v>
       </c>
+      <c r="H289" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I289" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="14" t="n">
@@ -8177,6 +10060,12 @@
       <c r="G290" s="15" t="n">
         <v>0.0007655946070903401</v>
       </c>
+      <c r="H290" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I290" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="14" t="n">
@@ -8200,6 +10089,12 @@
       <c r="G291" s="15" t="n">
         <v>0.00114839191063551</v>
       </c>
+      <c r="H291" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I291" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="14" t="n">
@@ -8223,6 +10118,12 @@
       <c r="G292" s="15" t="n">
         <v>0.001014412854394701</v>
       </c>
+      <c r="H292" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I292" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="14" t="n">
@@ -8246,6 +10147,12 @@
       <c r="G293" s="15" t="n">
         <v>0.0007847344722675985</v>
       </c>
+      <c r="H293" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I293" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="14" t="n">
@@ -8269,6 +10176,12 @@
       <c r="G294" s="15" t="n">
         <v>0.0008230142026221155</v>
       </c>
+      <c r="H294" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I294" s="15" t="n">
+        <v>0.0008580092994479911</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="14" t="n">
@@ -8292,6 +10205,12 @@
       <c r="G295" s="15" t="n">
         <v>0.0009761331240401836</v>
       </c>
+      <c r="H295" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="I295" s="15" t="n">
+        <v>0.001029611159337589</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="14" t="n">
@@ -8315,6 +10234,12 @@
       <c r="G296" s="15" t="n">
         <v>0.001090972315103735</v>
       </c>
+      <c r="H296" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I296" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="14" t="n">
@@ -8338,6 +10263,12 @@
       <c r="G297" s="15" t="n">
         <v>0.0009569932588629251</v>
       </c>
+      <c r="H297" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I297" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="14" t="n">
@@ -8361,6 +10292,12 @@
       <c r="G298" s="15" t="n">
         <v>0.0007081750115585646</v>
       </c>
+      <c r="H298" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I298" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="14" t="n">
@@ -8384,6 +10321,12 @@
       <c r="G299" s="15" t="n">
         <v>0.0008230142026221155</v>
       </c>
+      <c r="H299" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I299" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="14" t="n">
@@ -8407,6 +10350,12 @@
       <c r="G300" s="15" t="n">
         <v>0.001052692584749218</v>
       </c>
+      <c r="H300" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I300" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="14" t="n">
@@ -8430,6 +10379,12 @@
       <c r="G301" s="15" t="n">
         <v>0.001090972315103735</v>
       </c>
+      <c r="H301" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I301" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="14" t="n">
@@ -8453,6 +10408,12 @@
       <c r="G302" s="15" t="n">
         <v>0.0008804337981538911</v>
       </c>
+      <c r="H302" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I302" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="14" t="n">
@@ -8476,6 +10437,12 @@
       <c r="G303" s="15" t="n">
         <v>0.0007847344722675985</v>
       </c>
+      <c r="H303" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I303" s="15" t="n">
+        <v>0.0008008086794847916</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="14" t="n">
@@ -8499,6 +10466,12 @@
       <c r="G304" s="15" t="n">
         <v>0.0009761331240401836</v>
       </c>
+      <c r="H304" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I304" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="14" t="n">
@@ -8522,6 +10495,12 @@
       <c r="G305" s="15" t="n">
         <v>0.0008038743374448571</v>
       </c>
+      <c r="H305" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I305" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="14" t="n">
@@ -8545,6 +10524,12 @@
       <c r="G306" s="15" t="n">
         <v>0.0008804337981538911</v>
       </c>
+      <c r="H306" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I306" s="15" t="n">
+        <v>0.0008580092994479911</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="14" t="n">
@@ -8568,6 +10553,12 @@
       <c r="G307" s="15" t="n">
         <v>0.0008804337981538911</v>
       </c>
+      <c r="H307" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I307" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="14" t="n">
@@ -8591,6 +10582,12 @@
       <c r="G308" s="15" t="n">
         <v>0.001014412854394701</v>
       </c>
+      <c r="H308" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="I308" s="15" t="n">
+        <v>0.0009724105393743899</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="14" t="n">
@@ -8614,6 +10611,12 @@
       <c r="G309" s="15" t="n">
         <v>0.0008804337981538911</v>
       </c>
+      <c r="H309" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I309" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="14" t="n">
@@ -8637,6 +10640,12 @@
       <c r="G310" s="15" t="n">
         <v>0.001052692584749218</v>
       </c>
+      <c r="H310" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I310" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="14" t="n">
@@ -8660,6 +10669,12 @@
       <c r="G311" s="15" t="n">
         <v>0.0009378533936856665</v>
       </c>
+      <c r="H311" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I311" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="14" t="n">
@@ -8683,6 +10698,12 @@
       <c r="G312" s="15" t="n">
         <v>0.001090972315103735</v>
       </c>
+      <c r="H312" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I312" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="14" t="n">
@@ -8706,6 +10727,12 @@
       <c r="G313" s="15" t="n">
         <v>0.001052692584749218</v>
       </c>
+      <c r="H313" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="I313" s="15" t="n">
+        <v>0.001086811779300789</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="14" t="n">
@@ -8729,6 +10756,12 @@
       <c r="G314" s="15" t="n">
         <v>0.001033552719571959</v>
       </c>
+      <c r="H314" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I314" s="15" t="n">
+        <v>0.0007436080595215923</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="14" t="n">
@@ -8752,6 +10785,12 @@
       <c r="G315" s="15" t="n">
         <v>0.001033552719571959</v>
       </c>
+      <c r="H315" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I315" s="15" t="n">
+        <v>0.001144012399263988</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="14" t="n">
@@ -8775,6 +10814,12 @@
       <c r="G316" s="15" t="n">
         <v>0.001071832449926476</v>
       </c>
+      <c r="H316" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="I316" s="15" t="n">
+        <v>0.0009724105393743899</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="14" t="n">
@@ -8798,6 +10843,12 @@
       <c r="G317" s="15" t="n">
         <v>0.00166516827042149</v>
       </c>
+      <c r="H317" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I317" s="15" t="n">
+        <v>0.001144012399263988</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="14" t="n">
@@ -8821,6 +10872,12 @@
       <c r="G318" s="15" t="n">
         <v>0.002105385169498435</v>
       </c>
+      <c r="H318" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="I318" s="15" t="n">
+        <v>0.001315614259153586</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="14" t="n">
@@ -8844,6 +10901,12 @@
       <c r="G319" s="15" t="n">
         <v>0.00153118921418068</v>
       </c>
+      <c r="H319" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="I319" s="15" t="n">
+        <v>0.001601617358969583</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="14" t="n">
@@ -8867,6 +10930,12 @@
       <c r="G320" s="15" t="n">
         <v>0.002067105439143918</v>
       </c>
+      <c r="H320" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="I320" s="15" t="n">
+        <v>0.002059222318675179</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="14" t="n">
@@ -8890,6 +10959,12 @@
       <c r="G321" s="15" t="n">
         <v>0.002488182473043605</v>
       </c>
+      <c r="H321" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I321" s="15" t="n">
+        <v>0.002288024798527976</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="14" t="n">
@@ -8913,6 +10988,12 @@
       <c r="G322" s="15" t="n">
         <v>0.002775280450702483</v>
       </c>
+      <c r="H322" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="I322" s="15" t="n">
+        <v>0.002459626658417574</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="14" t="n">
@@ -8936,6 +11017,12 @@
       <c r="G323" s="15" t="n">
         <v>0.003004958832829585</v>
       </c>
+      <c r="H323" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="I323" s="15" t="n">
+        <v>0.003260435337902366</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="14" t="n">
@@ -8959,6 +11046,12 @@
       <c r="G324" s="15" t="n">
         <v>0.003483455462261047</v>
       </c>
+      <c r="H324" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="I324" s="15" t="n">
+        <v>0.003203234717939167</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="14" t="n">
@@ -8982,6 +11075,12 @@
       <c r="G325" s="15" t="n">
         <v>0.004823246024669142</v>
       </c>
+      <c r="H325" s="14" t="n">
+        <v>69</v>
+      </c>
+      <c r="I325" s="15" t="n">
+        <v>0.003946842777460759</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="14" t="n">
@@ -9005,6 +11104,12 @@
       <c r="G326" s="15" t="n">
         <v>0.005512281171050448</v>
       </c>
+      <c r="H326" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="I326" s="15" t="n">
+        <v>0.004290046497239955</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="14" t="n">
@@ -9028,6 +11133,12 @@
       <c r="G327" s="15" t="n">
         <v>0.006277875778140788</v>
       </c>
+      <c r="H327" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="I327" s="15" t="n">
+        <v>0.004347247117203155</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="14" t="n">
@@ -9051,6 +11162,12 @@
       <c r="G328" s="15" t="n">
         <v>0.006488414295090632</v>
       </c>
+      <c r="H328" s="14" t="n">
+        <v>97</v>
+      </c>
+      <c r="I328" s="15" t="n">
+        <v>0.005548460136430343</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="14" t="n">
@@ -9074,6 +11191,12 @@
       <c r="G329" s="15" t="n">
         <v>0.007713365666435176</v>
       </c>
+      <c r="H329" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="I329" s="15" t="n">
+        <v>0.006806873775620729</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="14" t="n">
@@ -9097,6 +11220,12 @@
       <c r="G330" s="15" t="n">
         <v>0.009359394071679407</v>
       </c>
+      <c r="H330" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="I330" s="15" t="n">
+        <v>0.007150077495399925</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="14" t="n">
@@ -9120,6 +11249,12 @@
       <c r="G331" s="15" t="n">
         <v>0.01117768126351897</v>
       </c>
+      <c r="H331" s="14" t="n">
+        <v>127</v>
+      </c>
+      <c r="I331" s="15" t="n">
+        <v>0.007264478735326325</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="14" t="n">
@@ -9143,6 +11278,12 @@
       <c r="G332" s="15" t="n">
         <v>0.01213467452238189</v>
       </c>
+      <c r="H332" s="14" t="n">
+        <v>174</v>
+      </c>
+      <c r="I332" s="15" t="n">
+        <v>0.009952907873596697</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="14" t="n">
@@ -9166,6 +11307,12 @@
       <c r="G333" s="15" t="n">
         <v>0.01393382184904419</v>
       </c>
+      <c r="H333" s="14" t="n">
+        <v>169</v>
+      </c>
+      <c r="I333" s="15" t="n">
+        <v>0.0096669047737807</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="14" t="n">
@@ -9189,6 +11336,12 @@
       <c r="G334" s="15" t="n">
         <v>0.01517791308556599</v>
       </c>
+      <c r="H334" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="I334" s="15" t="n">
+        <v>0.01155452523256628</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="14" t="n">
@@ -9212,6 +11365,12 @@
       <c r="G335" s="15" t="n">
         <v>0.01580952863641552</v>
       </c>
+      <c r="H335" s="14" t="n">
+        <v>184</v>
+      </c>
+      <c r="I335" s="15" t="n">
+        <v>0.01052491407322869</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="14" t="n">
@@ -9235,6 +11394,12 @@
       <c r="G336" s="15" t="n">
         <v>0.01707275973811458</v>
       </c>
+      <c r="H336" s="14" t="n">
+        <v>229</v>
+      </c>
+      <c r="I336" s="15" t="n">
+        <v>0.01309894197157266</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="14" t="n">
@@ -9258,6 +11423,12 @@
       <c r="G337" s="15" t="n">
         <v>0.01845083003087719</v>
       </c>
+      <c r="H337" s="14" t="n">
+        <v>254</v>
+      </c>
+      <c r="I337" s="15" t="n">
+        <v>0.01452895747065265</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="14" t="n">
@@ -9281,6 +11452,12 @@
       <c r="G338" s="15" t="n">
         <v>0.02051793547002111</v>
       </c>
+      <c r="H338" s="14" t="n">
+        <v>297</v>
+      </c>
+      <c r="I338" s="15" t="n">
+        <v>0.01698858412907022</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="14" t="n">
@@ -9304,6 +11481,12 @@
       <c r="G339" s="15" t="n">
         <v>0.02143664899852952</v>
       </c>
+      <c r="H339" s="14" t="n">
+        <v>328</v>
+      </c>
+      <c r="I339" s="15" t="n">
+        <v>0.0187618033479294</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="14" t="n">
@@ -9327,6 +11510,12 @@
       <c r="G340" s="15" t="n">
         <v>0.02222138347079712</v>
       </c>
+      <c r="H340" s="14" t="n">
+        <v>311</v>
+      </c>
+      <c r="I340" s="15" t="n">
+        <v>0.01778939280855502</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="14" t="n">
@@ -9350,6 +11539,12 @@
       <c r="G341" s="15" t="n">
         <v>0.02405881052781393</v>
       </c>
+      <c r="H341" s="14" t="n">
+        <v>278</v>
+      </c>
+      <c r="I341" s="15" t="n">
+        <v>0.01590177234976943</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="14" t="n">
@@ -9373,6 +11568,12 @@
       <c r="G342" s="15" t="n">
         <v>0.02593451731518527</v>
       </c>
+      <c r="H342" s="14" t="n">
+        <v>332</v>
+      </c>
+      <c r="I342" s="15" t="n">
+        <v>0.0189906058277822</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="14" t="n">
@@ -9396,6 +11597,12 @@
       <c r="G343" s="15" t="n">
         <v>0.0260110767758943</v>
       </c>
+      <c r="H343" s="14" t="n">
+        <v>317</v>
+      </c>
+      <c r="I343" s="15" t="n">
+        <v>0.01813259652833421</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="14" t="n">
@@ -9419,6 +11626,12 @@
       <c r="G344" s="15" t="n">
         <v>0.02526462203398122</v>
       </c>
+      <c r="H344" s="14" t="n">
+        <v>321</v>
+      </c>
+      <c r="I344" s="15" t="n">
+        <v>0.01836139900818701</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="14" t="n">
@@ -9442,6 +11655,12 @@
       <c r="G345" s="15" t="n">
         <v>0.02603021664107156</v>
       </c>
+      <c r="H345" s="14" t="n">
+        <v>293</v>
+      </c>
+      <c r="I345" s="15" t="n">
+        <v>0.01675978164921742</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="14" t="n">
@@ -9465,6 +11684,12 @@
       <c r="G346" s="15" t="n">
         <v>0.02553258014646284</v>
       </c>
+      <c r="H346" s="14" t="n">
+        <v>296</v>
+      </c>
+      <c r="I346" s="15" t="n">
+        <v>0.01693138350910703</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="14" t="n">
@@ -9488,6 +11713,12 @@
       <c r="G347" s="15" t="n">
         <v>0.02421192944923201</v>
       </c>
+      <c r="H347" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="I347" s="15" t="n">
+        <v>0.01716018598895982</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="14" t="n">
@@ -9511,6 +11742,12 @@
       <c r="G348" s="15" t="n">
         <v>0.0221831037404426</v>
       </c>
+      <c r="H348" s="14" t="n">
+        <v>284</v>
+      </c>
+      <c r="I348" s="15" t="n">
+        <v>0.01624497606954863</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="14" t="n">
@@ -9534,6 +11771,12 @@
       <c r="G349" s="15" t="n">
         <v>0.02063277466108467</v>
       </c>
+      <c r="H349" s="14" t="n">
+        <v>244</v>
+      </c>
+      <c r="I349" s="15" t="n">
+        <v>0.01395695127102065</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="14" t="n">
@@ -9557,6 +11800,12 @@
       <c r="G350" s="15" t="n">
         <v>0.02168546724583388</v>
       </c>
+      <c r="H350" s="14" t="n">
+        <v>268</v>
+      </c>
+      <c r="I350" s="15" t="n">
+        <v>0.01532976615013744</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="14" t="n">
@@ -9580,6 +11829,12 @@
       <c r="G351" s="15" t="n">
         <v>0.02051793547002111</v>
       </c>
+      <c r="H351" s="14" t="n">
+        <v>228</v>
+      </c>
+      <c r="I351" s="15" t="n">
+        <v>0.01304174135160946</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="14" t="n">
@@ -9603,6 +11858,12 @@
       <c r="G352" s="15" t="n">
         <v>0.01915900504243576</v>
       </c>
+      <c r="H352" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="I352" s="15" t="n">
+        <v>0.01144012399263988</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="14" t="n">
@@ -9626,6 +11887,12 @@
       <c r="G353" s="15" t="n">
         <v>0.0148525353775526</v>
       </c>
+      <c r="H353" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="I353" s="15" t="n">
+        <v>0.01029611159337589</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="14" t="n">
@@ -9649,6 +11916,12 @@
       <c r="G354" s="15" t="n">
         <v>0.01179015694919124</v>
       </c>
+      <c r="H354" s="14" t="n">
+        <v>146</v>
+      </c>
+      <c r="I354" s="15" t="n">
+        <v>0.008351290514627113</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="14" t="n">
@@ -9672,6 +11945,12 @@
       <c r="G355" s="15" t="n">
         <v>0.01108198193763267</v>
       </c>
+      <c r="H355" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="I355" s="15" t="n">
+        <v>0.006692472535694331</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="14" t="n">
@@ -9695,6 +11974,12 @@
       <c r="G356" s="15" t="n">
         <v>0.008727778520829876</v>
       </c>
+      <c r="H356" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="I356" s="15" t="n">
+        <v>0.004404447737166355</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="14" t="n">
@@ -9718,6 +12003,12 @@
       <c r="G357" s="15" t="n">
         <v>0.006966910924522095</v>
       </c>
+      <c r="H357" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="I357" s="15" t="n">
+        <v>0.003546438437718363</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="14" t="n">
@@ -9741,6 +12032,12 @@
       <c r="G358" s="15" t="n">
         <v>0.005225183193391571</v>
       </c>
+      <c r="H358" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="I358" s="15" t="n">
+        <v>0.003775240917571161</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="14" t="n">
@@ -9764,6 +12061,12 @@
       <c r="G359" s="15" t="n">
         <v>0.004574427777364782</v>
       </c>
+      <c r="H359" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="I359" s="15" t="n">
+        <v>0.003203234717939167</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="14" t="n">
@@ -9787,6 +12090,12 @@
       <c r="G360" s="15" t="n">
         <v>0.003674854114033632</v>
       </c>
+      <c r="H360" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="I360" s="15" t="n">
+        <v>0.002173623558601577</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="14" t="n">
@@ -9810,6 +12119,12 @@
       <c r="G361" s="15" t="n">
         <v>0.003751413574742666</v>
       </c>
+      <c r="H361" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="I361" s="15" t="n">
+        <v>0.003260435337902366</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="14" t="n">
@@ -9833,6 +12148,12 @@
       <c r="G362" s="15" t="n">
         <v>0.002890119641766034</v>
       </c>
+      <c r="H362" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="I362" s="15" t="n">
+        <v>0.001487216119043185</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="14" t="n">
@@ -9856,6 +12177,12 @@
       <c r="G363" s="15" t="n">
         <v>0.00319635748460217</v>
       </c>
+      <c r="H363" s="14" t="n">
+        <v>37</v>
+      </c>
+      <c r="I363" s="15" t="n">
+        <v>0.002116422938638378</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="14" t="n">
@@ -9879,6 +12206,12 @@
       <c r="G364" s="15" t="n">
         <v>0.00306237842836136</v>
       </c>
+      <c r="H364" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I364" s="15" t="n">
+        <v>0.002288024798527976</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="14" t="n">
@@ -9902,6 +12235,12 @@
       <c r="G365" s="15" t="n">
         <v>0.002737000720347966</v>
       </c>
+      <c r="H365" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="I365" s="15" t="n">
+        <v>0.002059222318675179</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="14" t="n">
@@ -9925,6 +12264,12 @@
       <c r="G366" s="15" t="n">
         <v>0.002603021664107156</v>
       </c>
+      <c r="H366" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="I366" s="15" t="n">
+        <v>0.002402426038454375</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="14" t="n">
@@ -9948,6 +12293,12 @@
       <c r="G367" s="15" t="n">
         <v>0.002909259506943292</v>
       </c>
+      <c r="H367" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="I367" s="15" t="n">
+        <v>0.002059222318675179</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="14" t="n">
@@ -9971,6 +12322,12 @@
       <c r="G368" s="15" t="n">
         <v>0.002315923686448279</v>
       </c>
+      <c r="H368" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="I368" s="15" t="n">
+        <v>0.001430015499079985</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="14" t="n">
@@ -9994,6 +12351,12 @@
       <c r="G369" s="15" t="n">
         <v>0.002315923686448279</v>
       </c>
+      <c r="H369" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="I369" s="15" t="n">
+        <v>0.001544416739006384</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="14" t="n">
@@ -10017,6 +12380,12 @@
       <c r="G370" s="15" t="n">
         <v>0.002181944630207469</v>
       </c>
+      <c r="H370" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="I370" s="15" t="n">
+        <v>0.00194482107874878</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="14" t="n">
@@ -10040,6 +12409,12 @@
       <c r="G371" s="15" t="n">
         <v>0.001741727731130524</v>
       </c>
+      <c r="H371" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="I371" s="15" t="n">
+        <v>0.002059222318675179</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="14" t="n">
@@ -10063,6 +12438,12 @@
       <c r="G372" s="15" t="n">
         <v>0.002067105439143918</v>
       </c>
+      <c r="H372" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="I372" s="15" t="n">
+        <v>0.001487216119043185</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="14" t="n">
@@ -10086,6 +12467,12 @@
       <c r="G373" s="15" t="n">
         <v>0.001780007461485041</v>
       </c>
+      <c r="H373" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="I373" s="15" t="n">
+        <v>0.001029611159337589</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="14" t="n">
@@ -10109,6 +12496,12 @@
       <c r="G374" s="15" t="n">
         <v>0.001703448000776007</v>
       </c>
+      <c r="H374" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I374" s="15" t="n">
+        <v>0.001144012399263988</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="14" t="n">
@@ -10132,6 +12525,12 @@
       <c r="G375" s="15" t="n">
         <v>0.00166516827042149</v>
       </c>
+      <c r="H375" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="I375" s="15" t="n">
+        <v>0.001658817978932783</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="14" t="n">
@@ -10155,6 +12554,12 @@
       <c r="G376" s="15" t="n">
         <v>0.001626888540066973</v>
       </c>
+      <c r="H376" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I376" s="15" t="n">
+        <v>0.0008580092994479911</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="14" t="n">
@@ -10178,6 +12583,12 @@
       <c r="G377" s="15" t="n">
         <v>0.001263231101699061</v>
       </c>
+      <c r="H377" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="I377" s="15" t="n">
+        <v>0.001029611159337589</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="14" t="n">
@@ -10201,6 +12612,12 @@
       <c r="G378" s="15" t="n">
         <v>0.001569468944535197</v>
       </c>
+      <c r="H378" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="I378" s="15" t="n">
+        <v>0.001029611159337589</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="14" t="n">
@@ -10224,6 +12641,12 @@
       <c r="G379" s="15" t="n">
         <v>0.001186671640990027</v>
       </c>
+      <c r="H379" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I379" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="14" t="n">
@@ -10247,6 +12670,12 @@
       <c r="G380" s="15" t="n">
         <v>0.001244091236521803</v>
       </c>
+      <c r="H380" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I380" s="15" t="n">
+        <v>0.001144012399263988</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="14" t="n">
@@ -10270,6 +12699,12 @@
       <c r="G381" s="15" t="n">
         <v>0.0009569932588629251</v>
       </c>
+      <c r="H381" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I381" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="14" t="n">
@@ -10293,6 +12728,12 @@
       <c r="G382" s="15" t="n">
         <v>0.0009187135285084081</v>
       </c>
+      <c r="H382" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I382" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="14" t="n">
@@ -10316,6 +12757,12 @@
       <c r="G383" s="15" t="n">
         <v>0.0009187135285084081</v>
       </c>
+      <c r="H383" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I383" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="14" t="n">
@@ -10339,6 +12786,12 @@
       <c r="G384" s="15" t="n">
         <v>0.0009569932588629251</v>
       </c>
+      <c r="H384" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I384" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="14" t="n">
@@ -10362,6 +12815,12 @@
       <c r="G385" s="15" t="n">
         <v>0.0008995736633311495</v>
       </c>
+      <c r="H385" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I385" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="14" t="n">
@@ -10385,6 +12844,12 @@
       <c r="G386" s="15" t="n">
         <v>0.0008038743374448571</v>
       </c>
+      <c r="H386" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I386" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="14" t="n">
@@ -10408,6 +12873,12 @@
       <c r="G387" s="15" t="n">
         <v>0.000650755416026789</v>
       </c>
+      <c r="H387" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I387" s="15" t="n">
+        <v>0.0006864074395583928</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="14" t="n">
@@ -10431,6 +12902,12 @@
       <c r="G388" s="15" t="n">
         <v>0.000650755416026789</v>
       </c>
+      <c r="H388" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I388" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="14" t="n">
@@ -10454,6 +12931,12 @@
       <c r="G389" s="15" t="n">
         <v>0.0008804337981538911</v>
       </c>
+      <c r="H389" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I389" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="14" t="n">
@@ -10477,6 +12960,12 @@
       <c r="G390" s="15" t="n">
         <v>0.000459356764254204</v>
       </c>
+      <c r="H390" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I390" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="14" t="n">
@@ -10500,6 +12989,12 @@
       <c r="G391" s="15" t="n">
         <v>0.000459356764254204</v>
       </c>
+      <c r="H391" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I391" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="14" t="n">
@@ -10523,6 +13018,12 @@
       <c r="G392" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H392" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I392" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="14" t="n">
@@ -10546,6 +13047,12 @@
       <c r="G393" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H393" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I393" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="14" t="n">
@@ -10569,6 +13076,12 @@
       <c r="G394" s="15" t="n">
         <v>0.0007464547419130816</v>
       </c>
+      <c r="H394" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I394" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="14" t="n">
@@ -10592,6 +13105,12 @@
       <c r="G395" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H395" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I395" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="14" t="n">
@@ -10615,6 +13134,12 @@
       <c r="G396" s="15" t="n">
         <v>0.0006316155508495306</v>
       </c>
+      <c r="H396" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I396" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="14" t="n">
@@ -10638,6 +13163,12 @@
       <c r="G397" s="15" t="n">
         <v>0.0003636574383679116</v>
       </c>
+      <c r="H397" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I397" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="14" t="n">
@@ -10661,6 +13192,12 @@
       <c r="G398" s="15" t="n">
         <v>0.0004402168990769455</v>
       </c>
+      <c r="H398" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I398" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="14" t="n">
@@ -10684,6 +13221,12 @@
       <c r="G399" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H399" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I399" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="14" t="n">
@@ -10707,6 +13250,12 @@
       <c r="G400" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H400" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I400" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="14" t="n">
@@ -10730,6 +13279,12 @@
       <c r="G401" s="15" t="n">
         <v>0.0005167763597859796</v>
       </c>
+      <c r="H401" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I401" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="14" t="n">
@@ -10753,6 +13308,12 @@
       <c r="G402" s="15" t="n">
         <v>0.0003636574383679116</v>
       </c>
+      <c r="H402" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I402" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="14" t="n">
@@ -10776,6 +13337,12 @@
       <c r="G403" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H403" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I403" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="14" t="n">
@@ -10799,6 +13366,12 @@
       <c r="G404" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H404" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I404" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="14" t="n">
@@ -10822,6 +13395,12 @@
       <c r="G405" s="15" t="n">
         <v>0.0003827973035451701</v>
       </c>
+      <c r="H405" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I405" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="14" t="n">
@@ -10845,6 +13424,12 @@
       <c r="G406" s="15" t="n">
         <v>0.000459356764254204</v>
       </c>
+      <c r="H406" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I406" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="14" t="n">
@@ -10868,6 +13453,12 @@
       <c r="G407" s="15" t="n">
         <v>0.0003827973035451701</v>
       </c>
+      <c r="H407" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I407" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="14" t="n">
@@ -10891,6 +13482,12 @@
       <c r="G408" s="15" t="n">
         <v>0.0004402168990769455</v>
       </c>
+      <c r="H408" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I408" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="14" t="n">
@@ -10914,6 +13511,12 @@
       <c r="G409" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H409" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I409" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="14" t="n">
@@ -10937,6 +13540,12 @@
       <c r="G410" s="15" t="n">
         <v>0.000344517573190653</v>
       </c>
+      <c r="H410" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I410" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="14" t="n">
@@ -10960,6 +13569,12 @@
       <c r="G411" s="15" t="n">
         <v>0.000574195955317755</v>
       </c>
+      <c r="H411" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I411" s="15" t="n">
+        <v>0.0001144012399263988</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="14" t="n">
@@ -10983,6 +13598,12 @@
       <c r="G412" s="15" t="n">
         <v>0.0003827973035451701</v>
       </c>
+      <c r="H412" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I412" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="14" t="n">
@@ -11006,6 +13627,12 @@
       <c r="G413" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H413" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I413" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="14" t="n">
@@ -11029,6 +13656,12 @@
       <c r="G414" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H414" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I414" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="14" t="n">
@@ -11052,6 +13685,12 @@
       <c r="G415" s="15" t="n">
         <v>0.0004402168990769455</v>
       </c>
+      <c r="H415" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I415" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="14" t="n">
@@ -11075,6 +13714,12 @@
       <c r="G416" s="15" t="n">
         <v>0.0005550560901404966</v>
       </c>
+      <c r="H416" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I416" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="14" t="n">
@@ -11098,6 +13743,12 @@
       <c r="G417" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H417" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I417" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="14" t="n">
@@ -11121,6 +13772,12 @@
       <c r="G418" s="15" t="n">
         <v>0.000267958112481619</v>
       </c>
+      <c r="H418" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I418" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="14" t="n">
@@ -11144,6 +13801,12 @@
       <c r="G419" s="15" t="n">
         <v>0.0004402168990769455</v>
       </c>
+      <c r="H419" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I419" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="14" t="n">
@@ -11167,6 +13830,12 @@
       <c r="G420" s="15" t="n">
         <v>0.000306237842836136</v>
       </c>
+      <c r="H420" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I420" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="14" t="n">
@@ -11190,6 +13859,12 @@
       <c r="G421" s="15" t="n">
         <v>0.000306237842836136</v>
       </c>
+      <c r="H421" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I421" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="14" t="n">
@@ -11213,6 +13888,12 @@
       <c r="G422" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H422" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I422" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="14" t="n">
@@ -11236,6 +13917,12 @@
       <c r="G423" s="15" t="n">
         <v>0.000306237842836136</v>
       </c>
+      <c r="H423" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I423" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="14" t="n">
@@ -11259,6 +13946,12 @@
       <c r="G424" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H424" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I424" s="15" t="n">
+        <v>0.0001144012399263988</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="14" t="n">
@@ -11282,6 +13975,12 @@
       <c r="G425" s="15" t="n">
         <v>0.0005167763597859796</v>
       </c>
+      <c r="H425" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I425" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="14" t="n">
@@ -11305,6 +14004,12 @@
       <c r="G426" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H426" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I426" s="15" t="n">
+        <v>5.72006199631994e-05</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="14" t="n">
@@ -11328,6 +14033,12 @@
       <c r="G427" s="15" t="n">
         <v>0.000535916224963238</v>
       </c>
+      <c r="H427" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I427" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="14" t="n">
@@ -11351,6 +14062,12 @@
       <c r="G428" s="15" t="n">
         <v>0.0003827973035451701</v>
       </c>
+      <c r="H428" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I428" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="14" t="n">
@@ -11374,6 +14091,12 @@
       <c r="G429" s="15" t="n">
         <v>0.0003636574383679116</v>
       </c>
+      <c r="H429" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I429" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="14" t="n">
@@ -11397,6 +14120,12 @@
       <c r="G430" s="15" t="n">
         <v>0.0004784966294314625</v>
       </c>
+      <c r="H430" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I430" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="14" t="n">
@@ -11420,6 +14149,12 @@
       <c r="G431" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H431" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I431" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="14" t="n">
@@ -11443,6 +14178,12 @@
       <c r="G432" s="15" t="n">
         <v>0.0004402168990769455</v>
       </c>
+      <c r="H432" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I432" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="14" t="n">
@@ -11466,6 +14207,12 @@
       <c r="G433" s="15" t="n">
         <v>0.0005933358204950136</v>
       </c>
+      <c r="H433" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I433" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="14" t="n">
@@ -11489,6 +14236,12 @@
       <c r="G434" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H434" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I434" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="14" t="n">
@@ -11512,6 +14265,12 @@
       <c r="G435" s="15" t="n">
         <v>0.0004402168990769455</v>
       </c>
+      <c r="H435" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I435" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="14" t="n">
@@ -11535,6 +14294,12 @@
       <c r="G436" s="15" t="n">
         <v>0.0002105385169498435</v>
       </c>
+      <c r="H436" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I436" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="14" t="n">
@@ -11558,6 +14323,12 @@
       <c r="G437" s="15" t="n">
         <v>0.0003827973035451701</v>
       </c>
+      <c r="H437" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I437" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="14" t="n">
@@ -11581,6 +14352,12 @@
       <c r="G438" s="15" t="n">
         <v>0.000229678382127102</v>
       </c>
+      <c r="H438" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I438" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="14" t="n">
@@ -11604,6 +14381,12 @@
       <c r="G439" s="15" t="n">
         <v>0.0003827973035451701</v>
       </c>
+      <c r="H439" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I439" s="15" t="n">
+        <v>0.0001144012399263988</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="14" t="n">
@@ -11627,6 +14410,12 @@
       <c r="G440" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H440" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I440" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="14" t="n">
@@ -11650,6 +14439,12 @@
       <c r="G441" s="15" t="n">
         <v>0.0003636574383679116</v>
       </c>
+      <c r="H441" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I441" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="14" t="n">
@@ -11673,6 +14468,12 @@
       <c r="G442" s="15" t="n">
         <v>0.000574195955317755</v>
       </c>
+      <c r="H442" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I442" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="14" t="n">
@@ -11696,6 +14497,12 @@
       <c r="G443" s="15" t="n">
         <v>0.000344517573190653</v>
       </c>
+      <c r="H443" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I443" s="15" t="n">
+        <v>5.72006199631994e-05</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="14" t="n">
@@ -11719,6 +14526,12 @@
       <c r="G444" s="15" t="n">
         <v>0.000459356764254204</v>
       </c>
+      <c r="H444" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I444" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="14" t="n">
@@ -11742,6 +14555,12 @@
       <c r="G445" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H445" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I445" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="14" t="n">
@@ -11765,6 +14584,12 @@
       <c r="G446" s="15" t="n">
         <v>0.0003636574383679116</v>
       </c>
+      <c r="H446" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I446" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="14" t="n">
@@ -11788,6 +14613,12 @@
       <c r="G447" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H447" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I447" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="14" t="n">
@@ -11811,6 +14642,12 @@
       <c r="G448" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H448" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I448" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="14" t="n">
@@ -11834,6 +14671,12 @@
       <c r="G449" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H449" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I449" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="14" t="n">
@@ -11857,6 +14700,12 @@
       <c r="G450" s="15" t="n">
         <v>0.0006316155508495306</v>
       </c>
+      <c r="H450" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="I450" s="15" t="n">
+        <v>0.0005148055796687946</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="14" t="n">
@@ -11880,6 +14729,12 @@
       <c r="G451" s="15" t="n">
         <v>0.0005167763597859796</v>
       </c>
+      <c r="H451" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I451" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="14" t="n">
@@ -11903,6 +14758,12 @@
       <c r="G452" s="15" t="n">
         <v>0.0005550560901404966</v>
       </c>
+      <c r="H452" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I452" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="14" t="n">
@@ -11926,6 +14787,12 @@
       <c r="G453" s="15" t="n">
         <v>0.0003827973035451701</v>
       </c>
+      <c r="H453" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I453" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="14" t="n">
@@ -11949,6 +14816,12 @@
       <c r="G454" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H454" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I454" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="14" t="n">
@@ -11972,6 +14845,12 @@
       <c r="G455" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H455" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I455" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="14" t="n">
@@ -11995,6 +14874,12 @@
       <c r="G456" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H456" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I456" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="14" t="n">
@@ -12018,6 +14903,12 @@
       <c r="G457" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H457" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I457" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="14" t="n">
@@ -12041,6 +14932,12 @@
       <c r="G458" s="15" t="n">
         <v>0.000344517573190653</v>
       </c>
+      <c r="H458" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I458" s="15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="14" t="n">
@@ -12064,6 +14961,12 @@
       <c r="G459" s="15" t="n">
         <v>0.000344517573190653</v>
       </c>
+      <c r="H459" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I459" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="14" t="n">
@@ -12087,6 +14990,12 @@
       <c r="G460" s="15" t="n">
         <v>0.000459356764254204</v>
       </c>
+      <c r="H460" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I460" s="15" t="n">
+        <v>5.72006199631994e-05</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="14" t="n">
@@ -12110,6 +15019,12 @@
       <c r="G461" s="15" t="n">
         <v>0.0004402168990769455</v>
       </c>
+      <c r="H461" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I461" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="14" t="n">
@@ -12133,6 +15048,12 @@
       <c r="G462" s="15" t="n">
         <v>0.0004784966294314625</v>
       </c>
+      <c r="H462" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I462" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="14" t="n">
@@ -12156,6 +15077,12 @@
       <c r="G463" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H463" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I463" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="14" t="n">
@@ -12179,6 +15106,12 @@
       <c r="G464" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H464" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I464" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="14" t="n">
@@ -12202,6 +15135,12 @@
       <c r="G465" s="15" t="n">
         <v>0.0004784966294314625</v>
       </c>
+      <c r="H465" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I465" s="15" t="n">
+        <v>0.0006292068195951935</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="14" t="n">
@@ -12225,6 +15164,12 @@
       <c r="G466" s="15" t="n">
         <v>0.000344517573190653</v>
       </c>
+      <c r="H466" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I466" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="14" t="n">
@@ -12248,6 +15193,12 @@
       <c r="G467" s="15" t="n">
         <v>0.0003636574383679116</v>
       </c>
+      <c r="H467" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I467" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="14" t="n">
@@ -12271,6 +15222,12 @@
       <c r="G468" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H468" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I468" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="14" t="n">
@@ -12294,6 +15251,12 @@
       <c r="G469" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H469" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I469" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="14" t="n">
@@ -12317,6 +15280,12 @@
       <c r="G470" s="15" t="n">
         <v>0.000267958112481619</v>
       </c>
+      <c r="H470" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I470" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="14" t="n">
@@ -12340,6 +15309,12 @@
       <c r="G471" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H471" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I471" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="14" t="n">
@@ -12363,6 +15338,12 @@
       <c r="G472" s="15" t="n">
         <v>0.0003636574383679116</v>
       </c>
+      <c r="H472" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I472" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="14" t="n">
@@ -12386,6 +15367,12 @@
       <c r="G473" s="15" t="n">
         <v>0.000497636494608721</v>
       </c>
+      <c r="H473" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I473" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="14" t="n">
@@ -12409,6 +15396,12 @@
       <c r="G474" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H474" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I474" s="15" t="n">
+        <v>0.0001144012399263988</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="14" t="n">
@@ -12432,6 +15425,12 @@
       <c r="G475" s="15" t="n">
         <v>0.000344517573190653</v>
       </c>
+      <c r="H475" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I475" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="14" t="n">
@@ -12455,6 +15454,12 @@
       <c r="G476" s="15" t="n">
         <v>0.0003636574383679116</v>
       </c>
+      <c r="H476" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I476" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="14" t="n">
@@ -12478,6 +15483,12 @@
       <c r="G477" s="15" t="n">
         <v>0.000574195955317755</v>
       </c>
+      <c r="H477" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I477" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="14" t="n">
@@ -12501,6 +15512,12 @@
       <c r="G478" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H478" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I478" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="14" t="n">
@@ -12524,6 +15541,12 @@
       <c r="G479" s="15" t="n">
         <v>0.0005550560901404966</v>
       </c>
+      <c r="H479" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I479" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="14" t="n">
@@ -12547,6 +15570,12 @@
       <c r="G480" s="15" t="n">
         <v>0.0004784966294314625</v>
       </c>
+      <c r="H480" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I480" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="14" t="n">
@@ -12570,6 +15599,12 @@
       <c r="G481" s="15" t="n">
         <v>0.0003827973035451701</v>
       </c>
+      <c r="H481" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I481" s="15" t="n">
+        <v>0.0001144012399263988</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="14" t="n">
@@ -12593,6 +15628,12 @@
       <c r="G482" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H482" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I482" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="14" t="n">
@@ -12616,6 +15657,12 @@
       <c r="G483" s="15" t="n">
         <v>0.0005550560901404966</v>
       </c>
+      <c r="H483" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I483" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="14" t="n">
@@ -12639,6 +15686,12 @@
       <c r="G484" s="15" t="n">
         <v>0.000459356764254204</v>
       </c>
+      <c r="H484" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I484" s="15" t="n">
+        <v>0.0001144012399263988</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="14" t="n">
@@ -12662,6 +15715,12 @@
       <c r="G485" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H485" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I485" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="14" t="n">
@@ -12685,6 +15744,12 @@
       <c r="G486" s="15" t="n">
         <v>0.000267958112481619</v>
       </c>
+      <c r="H486" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I486" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="14" t="n">
@@ -12708,6 +15773,12 @@
       <c r="G487" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H487" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I487" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="14" t="n">
@@ -12731,6 +15802,12 @@
       <c r="G488" s="15" t="n">
         <v>0.0002105385169498435</v>
       </c>
+      <c r="H488" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I488" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="14" t="n">
@@ -12754,6 +15831,12 @@
       <c r="G489" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H489" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I489" s="15" t="n">
+        <v>0.0002288024798527976</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="14" t="n">
@@ -12777,6 +15860,12 @@
       <c r="G490" s="15" t="n">
         <v>0.0005167763597859796</v>
       </c>
+      <c r="H490" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I490" s="15" t="n">
+        <v>0.0004004043397423958</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="14" t="n">
@@ -12800,6 +15889,12 @@
       <c r="G491" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H491" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I491" s="15" t="n">
+        <v>0.000572006199631994</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="14" t="n">
@@ -12823,6 +15918,12 @@
       <c r="G492" s="15" t="n">
         <v>0.000306237842836136</v>
       </c>
+      <c r="H492" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I492" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="14" t="n">
@@ -12846,6 +15947,12 @@
       <c r="G493" s="15" t="n">
         <v>0.000344517573190653</v>
       </c>
+      <c r="H493" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I493" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="14" t="n">
@@ -12869,6 +15976,12 @@
       <c r="G494" s="15" t="n">
         <v>0.000344517573190653</v>
       </c>
+      <c r="H494" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I494" s="15" t="n">
+        <v>0.0004576049597055952</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="14" t="n">
@@ -12892,6 +16005,12 @@
       <c r="G495" s="15" t="n">
         <v>0.0005550560901404966</v>
       </c>
+      <c r="H495" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I495" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="14" t="n">
@@ -12915,6 +16034,12 @@
       <c r="G496" s="15" t="n">
         <v>0.000421077033899687</v>
       </c>
+      <c r="H496" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I496" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="14" t="n">
@@ -12938,6 +16063,12 @@
       <c r="G497" s="15" t="n">
         <v>0.000306237842836136</v>
       </c>
+      <c r="H497" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I497" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="14" t="n">
@@ -12961,6 +16092,12 @@
       <c r="G498" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H498" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I498" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="14" t="n">
@@ -12984,6 +16121,12 @@
       <c r="G499" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H499" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I499" s="15" t="n">
+        <v>0.0001144012399263988</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="14" t="n">
@@ -13007,6 +16150,12 @@
       <c r="G500" s="15" t="n">
         <v>0.000306237842836136</v>
       </c>
+      <c r="H500" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I500" s="15" t="n">
+        <v>0.0001144012399263988</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="14" t="n">
@@ -13030,6 +16179,12 @@
       <c r="G501" s="15" t="n">
         <v>0.0004019371687224285</v>
       </c>
+      <c r="H501" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I501" s="15" t="n">
+        <v>5.72006199631994e-05</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="14" t="n">
@@ -13053,6 +16208,12 @@
       <c r="G502" s="15" t="n">
         <v>0.000344517573190653</v>
       </c>
+      <c r="H502" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I502" s="15" t="n">
+        <v>0.0003432037197791964</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="14" t="n">
@@ -13076,6 +16237,12 @@
       <c r="G503" s="15" t="n">
         <v>0.0001722587865953265</v>
       </c>
+      <c r="H503" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I503" s="15" t="n">
+        <v>0.0001716018598895982</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="14" t="n">
@@ -13099,6 +16266,12 @@
       <c r="G504" s="15" t="n">
         <v>0.0002870979776588775</v>
       </c>
+      <c r="H504" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I504" s="15" t="n">
+        <v>0.0001144012399263988</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="14" t="n">
@@ -13122,6 +16295,12 @@
       <c r="G505" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H505" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I505" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="14" t="n">
@@ -13145,6 +16324,12 @@
       <c r="G506" s="15" t="n">
         <v>0.000344517573190653</v>
       </c>
+      <c r="H506" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I506" s="15" t="n">
+        <v>5.72006199631994e-05</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="14" t="n">
@@ -13168,6 +16353,12 @@
       <c r="G507" s="15" t="n">
         <v>0.000267958112481619</v>
       </c>
+      <c r="H507" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I507" s="15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="14" t="n">
@@ -13191,6 +16382,12 @@
       <c r="G508" s="15" t="n">
         <v>0.0001722587865953265</v>
       </c>
+      <c r="H508" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I508" s="15" t="n">
+        <v>0.000286003099815997</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="14" t="n">
@@ -13214,6 +16411,12 @@
       <c r="G509" s="15" t="n">
         <v>0.000267958112481619</v>
       </c>
+      <c r="H509" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I509" s="15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="14" t="n">
@@ -13237,6 +16440,12 @@
       <c r="G510" s="15" t="n">
         <v>0.000229678382127102</v>
       </c>
+      <c r="H510" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I510" s="15" t="n">
+        <v>5.72006199631994e-05</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="14" t="n">
@@ -13260,6 +16469,12 @@
       <c r="G511" s="15" t="n">
         <v>0.0003253777080133945</v>
       </c>
+      <c r="H511" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I511" s="15" t="n">
+        <v>5.72006199631994e-05</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="14" t="n">
@@ -13283,6 +16498,12 @@
       <c r="G512" s="15" t="n">
         <v>0.000153118921418068</v>
       </c>
+      <c r="H512" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I512" s="15" t="n">
+        <v>5.72006199631994e-05</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="14" t="n">
@@ -13306,9 +16527,15 @@
       <c r="G513" s="15" t="n">
         <v>9.569932588629251e-05</v>
       </c>
+      <c r="H513" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I513" s="15" t="n">
+        <v>5.72006199631994e-05</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G513"/>
+  <autoFilter ref="A1:I513"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13319,7 +16546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13332,6 +16559,9 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13392,6 +16622,21 @@
           <t>管理棟2階_0819 [%]</t>
         </is>
       </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>管理棟1階_0819 カウント</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>管理棟1階_0819 [s⁻¹]</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>管理棟1階_0819 [%]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -13426,6 +16671,15 @@
       <c r="J4" s="9" t="n">
         <v>49.26829170465113</v>
       </c>
+      <c r="K4" s="5" t="n">
+        <v>555620</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>31.78180846395285</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>49.09513917299405</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -13460,6 +16714,15 @@
       <c r="J5" s="9" t="n">
         <v>38.82248252523591</v>
       </c>
+      <c r="K5" s="5" t="n">
+        <v>441144</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>25.23371029304564</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>38.97992526426566</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -13494,6 +16757,15 @@
       <c r="J6" s="9" t="n">
         <v>10.71838054675857</v>
       </c>
+      <c r="K6" s="5" t="n">
+        <v>124871</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>7.142698615424673</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>11.03372651033249</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -13528,6 +16800,15 @@
       <c r="J7" s="9" t="n">
         <v>0.8979327091943703</v>
       </c>
+      <c r="K7" s="5" t="n">
+        <v>7578</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>0.4334662980811251</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>0.6695996628144216</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -13562,6 +16843,15 @@
       <c r="J8" s="9" t="n">
         <v>0.03337667048087044</v>
       </c>
+      <c r="K8" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>0.01544416739006384</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>0.02385747017153521</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -13596,6 +16886,15 @@
       <c r="J9" s="9" t="n">
         <v>100</v>
       </c>
+      <c r="K9" s="5" t="n">
+        <v>1131721</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>64.73514282537199</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
@@ -13629,6 +16928,15 @@
       </c>
       <c r="J10" s="20" t="n">
         <v>50.73170829534887</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>576101</v>
+      </c>
+      <c r="L10" s="19" t="n">
+        <v>32.95333436141914</v>
+      </c>
+      <c r="M10" s="20" t="n">
+        <v>50.90486082700595</v>
       </c>
     </row>
   </sheetData>
